--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -28,10 +28,10 @@
     <t>U. x Caja</t>
   </si>
   <si>
-    <t>Stock VES</t>
-  </si>
-  <si>
-    <t>Alerta</t>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Estado</t>
   </si>
   <si>
     <t>16763</t>
@@ -43,7 +43,7 @@
     <t>FUTBOL PU FUTURE #5</t>
   </si>
   <si>
-    <t>🟢</t>
+    <t>✓ OK</t>
   </si>
   <si>
     <t>16725</t>
@@ -76,7 +76,7 @@
     <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
   </si>
   <si>
-    <t>🔴</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>16757</t>
@@ -127,7 +127,7 @@
     <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
   </si>
   <si>
-    <t>🟡</t>
+    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>14375</t>
@@ -1238,7 +1238,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1252,6 +1252,22 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1294,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1302,13 +1318,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1653,13 +1675,12 @@
   <dimension ref="A1:G199"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1819,7 +1840,7 @@
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2000,10 +2021,10 @@
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2072,7 +2093,7 @@
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2187,7 +2208,7 @@
       <c r="F23" s="4">
         <v>0</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2210,7 +2231,7 @@
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2233,7 +2254,7 @@
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2253,10 +2274,10 @@
       <c r="E26">
         <v>48</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="6">
         <v>1</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2279,7 +2300,7 @@
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2299,10 +2320,10 @@
       <c r="E28">
         <v>36</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="6">
         <v>1</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2348,7 +2369,7 @@
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2371,7 +2392,7 @@
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2555,7 +2576,7 @@
       <c r="F39" s="4">
         <v>0</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2578,7 +2599,7 @@
       <c r="F40" s="4">
         <v>0</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2598,10 +2619,10 @@
       <c r="E41">
         <v>48</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="6">
         <v>5</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2647,7 +2668,7 @@
       <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2693,7 +2714,7 @@
       <c r="F45" s="4">
         <v>0</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2716,7 +2737,7 @@
       <c r="F46" s="4">
         <v>0</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2762,7 +2783,7 @@
       <c r="F48" s="4">
         <v>0</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2782,10 +2803,10 @@
       <c r="E49">
         <v>48</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="6">
         <v>6</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2831,7 +2852,7 @@
       <c r="F51" s="4">
         <v>0</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2874,10 +2895,10 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="6">
         <v>1</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2992,7 +3013,7 @@
       <c r="F58" s="4">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3015,7 +3036,7 @@
       <c r="F59" s="4">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3061,7 +3082,7 @@
       <c r="F61" s="4">
         <v>0</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3314,7 +3335,7 @@
       <c r="F72" s="4">
         <v>0</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3518,10 +3539,10 @@
       <c r="E81">
         <v>60</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="6">
         <v>5</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3590,7 +3611,7 @@
       <c r="F84" s="4">
         <v>0</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3682,7 +3703,7 @@
       <c r="F88" s="4">
         <v>0</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3705,7 +3726,7 @@
       <c r="F89" s="4">
         <v>0</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3843,7 +3864,7 @@
       <c r="F95" s="4">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4073,7 +4094,7 @@
       <c r="F105" s="4">
         <v>0</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="G105" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4395,7 +4416,7 @@
       <c r="F119" s="4">
         <v>0</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4441,7 +4462,7 @@
       <c r="F121" s="4">
         <v>0</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4760,10 +4781,10 @@
       <c r="E135">
         <v>120</v>
       </c>
-      <c r="F135" s="5">
+      <c r="F135" s="6">
         <v>2</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4875,10 +4896,10 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140" s="6">
         <v>3</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="G140" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4970,7 +4991,7 @@
       <c r="F144" s="4">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4990,10 +5011,10 @@
       <c r="E145">
         <v>120</v>
       </c>
-      <c r="F145" s="5">
+      <c r="F145" s="6">
         <v>1</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G145" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5082,10 +5103,10 @@
       <c r="E149">
         <v>120</v>
       </c>
-      <c r="F149" s="5">
+      <c r="F149" s="6">
         <v>1</v>
       </c>
-      <c r="G149" s="3" t="s">
+      <c r="G149" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5151,10 +5172,10 @@
       <c r="E152">
         <v>120</v>
       </c>
-      <c r="F152" s="5">
+      <c r="F152" s="6">
         <v>2</v>
       </c>
-      <c r="G152" s="3" t="s">
+      <c r="G152" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5177,7 +5198,7 @@
       <c r="F153" s="4">
         <v>0</v>
       </c>
-      <c r="G153" s="3" t="s">
+      <c r="G153" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5335,10 +5356,10 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="5">
+      <c r="F160" s="6">
         <v>6</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="G160" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5568,7 +5589,7 @@
       <c r="F170" s="4">
         <v>0</v>
       </c>
-      <c r="G170" s="3" t="s">
+      <c r="G170" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5706,7 +5727,7 @@
       <c r="F176" s="4">
         <v>0</v>
       </c>
-      <c r="G176" s="3" t="s">
+      <c r="G176" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5729,7 +5750,7 @@
       <c r="F177" s="4">
         <v>0</v>
       </c>
-      <c r="G177" s="3" t="s">
+      <c r="G177" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5772,10 +5793,10 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="5">
+      <c r="F179" s="6">
         <v>1</v>
       </c>
-      <c r="G179" s="3" t="s">
+      <c r="G179" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5798,7 +5819,7 @@
       <c r="F180" s="4">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5821,7 +5842,7 @@
       <c r="F181" s="4">
         <v>0</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6002,10 +6023,10 @@
       <c r="E189">
         <v>18</v>
       </c>
-      <c r="F189" s="5">
+      <c r="F189" s="6">
         <v>4</v>
       </c>
-      <c r="G189" s="3" t="s">
+      <c r="G189" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6212,7 +6233,7 @@
       <c r="F198" s="4">
         <v>0</v>
       </c>
-      <c r="G198" s="3" t="s">
+      <c r="G198" s="5" t="s">
         <v>21</v>
       </c>
     </row>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2379,11 +2379,11 @@
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>180</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>15</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2425,11 +2425,11 @@
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>168</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>15</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2448,11 +2448,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>182</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>15</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2908,11 +2908,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>263</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>15</v>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3414,11 +3414,11 @@
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>196</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>15</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3598,11 +3598,11 @@
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>418</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>15</v>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4104,11 +4104,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="2">
         <v>333</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>15</v>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4518,11 +4518,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="2">
         <v>368</v>
       </c>
-      <c r="G104" s="5" t="s">
-        <v>15</v>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4886,11 +4886,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="2">
         <v>261</v>
       </c>
-      <c r="G120" s="5" t="s">
-        <v>15</v>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5093,11 +5093,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="2">
         <v>1067</v>
       </c>
-      <c r="G129" s="5" t="s">
-        <v>15</v>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5116,11 +5116,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="2">
         <v>884</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>15</v>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5208,11 +5208,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>1017</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>15</v>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5691,11 +5691,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="2">
         <v>908</v>
       </c>
-      <c r="G155" s="5" t="s">
-        <v>15</v>
+      <c r="G155" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5760,11 +5760,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="4">
+      <c r="F158" s="2">
         <v>1101</v>
       </c>
-      <c r="G158" s="5" t="s">
-        <v>15</v>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5967,11 +5967,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="2">
         <v>764</v>
       </c>
-      <c r="G167" s="5" t="s">
-        <v>15</v>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6013,11 +6013,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="4">
+      <c r="F169" s="2">
         <v>703</v>
       </c>
-      <c r="G169" s="5" t="s">
-        <v>15</v>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -52,475 +52,475 @@
     <t>FUTBOL CUERO TERMOSELLADA PRECISION #5</t>
   </si>
   <si>
+    <t>✗ AGOTADO</t>
+  </si>
+  <si>
     <t>016726</t>
   </si>
   <si>
     <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
   </si>
   <si>
+    <t>016727</t>
+  </si>
+  <si>
+    <t>7754807167277</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
+  </si>
+  <si>
+    <t>016756</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
+  </si>
+  <si>
+    <t>016755</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
+  </si>
+  <si>
+    <t>016757</t>
+  </si>
+  <si>
+    <t>7754807167574</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
+  </si>
+  <si>
+    <t>016760</t>
+  </si>
+  <si>
+    <t>7754807167604</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
+  </si>
+  <si>
+    <t>016758</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #5</t>
+  </si>
+  <si>
+    <t>016761</t>
+  </si>
+  <si>
+    <t>7754807167611</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #4</t>
+  </si>
+  <si>
+    <t>016759</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BRASIL #5</t>
+  </si>
+  <si>
+    <t>016762</t>
+  </si>
+  <si>
+    <t>7754807167628</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BRASIL #4</t>
+  </si>
+  <si>
+    <t>016706</t>
+  </si>
+  <si>
+    <t>7754807167062</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BLANQUIRROJA #5</t>
+  </si>
+  <si>
+    <t>016708</t>
+  </si>
+  <si>
+    <t>7754807167086</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
+  </si>
+  <si>
+    <t>014375</t>
+  </si>
+  <si>
+    <t>7754807143752</t>
+  </si>
+  <si>
+    <t>FUTSAL CUERO VULC #3.5</t>
+  </si>
+  <si>
+    <t>016766</t>
+  </si>
+  <si>
+    <t>FUTSAL TERMOSELLADA ALEGRO</t>
+  </si>
+  <si>
+    <t>016767</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER1 #5</t>
+  </si>
+  <si>
+    <t>016768</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER2 #5</t>
+  </si>
+  <si>
+    <t>016769</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER3 #5</t>
+  </si>
+  <si>
+    <t>016770</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER4 #5</t>
+  </si>
+  <si>
+    <t>016771</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER1 #4</t>
+  </si>
+  <si>
+    <t>016743</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU PER2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016744</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU BRA2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016745</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU ARG2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016746</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU FLAGS CUP24 #5</t>
+  </si>
+  <si>
+    <t>016747</t>
+  </si>
+  <si>
+    <t>VOLEY PU LIGA1</t>
+  </si>
+  <si>
+    <t>016748</t>
+  </si>
+  <si>
+    <t>VOLEY PU LIGA2</t>
+  </si>
+  <si>
+    <t>016729</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FLORES</t>
+  </si>
+  <si>
+    <t>016731</t>
+  </si>
+  <si>
+    <t>VOLEY CUP CUERO COSIDO CELESTE AMARILLO ROSADO</t>
+  </si>
+  <si>
+    <t>016728</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FOLK</t>
+  </si>
+  <si>
+    <t>016730</t>
+  </si>
+  <si>
+    <t>7754807167307</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FOLK GRAFITTI</t>
+  </si>
+  <si>
+    <t>016788</t>
+  </si>
+  <si>
+    <t>7754807167888</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO CREW</t>
+  </si>
+  <si>
+    <t>016737</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR1</t>
+  </si>
+  <si>
+    <t>016738</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR2</t>
+  </si>
+  <si>
+    <t>016739</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR3</t>
+  </si>
+  <si>
+    <t>016004</t>
+  </si>
+  <si>
+    <t>7754807160049</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA SPARTANO #3</t>
+  </si>
+  <si>
+    <t>015938</t>
+  </si>
+  <si>
+    <t>7754807159388</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA FREE #5</t>
+  </si>
+  <si>
+    <t>016678</t>
+  </si>
+  <si>
+    <t>7754807166782</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA URBAN #5</t>
+  </si>
+  <si>
+    <t>016724</t>
+  </si>
+  <si>
+    <t>7754807167246</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA SPECTRE #5</t>
+  </si>
+  <si>
+    <t>016783</t>
+  </si>
+  <si>
+    <t>7754807167833</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA INVICTUS  #5</t>
+  </si>
+  <si>
+    <t>014323</t>
+  </si>
+  <si>
+    <t>7754807143233</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA PAISES BLANCO #5</t>
+  </si>
+  <si>
+    <t>014796</t>
+  </si>
+  <si>
+    <t>7754807147965</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA TEAM #5</t>
+  </si>
+  <si>
+    <t>011883</t>
+  </si>
+  <si>
+    <t>7754807118835</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA PAISES COLORES #5</t>
+  </si>
+  <si>
+    <t>016657</t>
+  </si>
+  <si>
+    <t>7754807166577</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA BUTTERFLY</t>
+  </si>
+  <si>
+    <t>015936</t>
+  </si>
+  <si>
+    <t>7754807159364</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA MULTICOLOR</t>
+  </si>
+  <si>
+    <t>014268</t>
+  </si>
+  <si>
+    <t>7754807142687</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA TRICOLOR</t>
+  </si>
+  <si>
+    <t>016784</t>
+  </si>
+  <si>
+    <t>7754807167840</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA FLORES2</t>
+  </si>
+  <si>
+    <t>016786</t>
+  </si>
+  <si>
+    <t>7754807167864</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA FRUTAS2</t>
+  </si>
+  <si>
+    <t>015939</t>
+  </si>
+  <si>
+    <t>7754807159395</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA FOLK</t>
+  </si>
+  <si>
+    <t>016785</t>
+  </si>
+  <si>
+    <t>7754807167857</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA MARIPOSAS</t>
+  </si>
+  <si>
+    <t>016787</t>
+  </si>
+  <si>
+    <t>7754807167871</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA URBANA</t>
+  </si>
+  <si>
+    <t>016672</t>
+  </si>
+  <si>
+    <t>7754807166720</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #3 SONRISAS</t>
+  </si>
+  <si>
+    <t>014271</t>
+  </si>
+  <si>
+    <t>7754807142717</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #3 NARANJA</t>
+  </si>
+  <si>
+    <t>014270</t>
+  </si>
+  <si>
+    <t>7754807111638</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 NARANJA</t>
+  </si>
+  <si>
+    <t>014277</t>
+  </si>
+  <si>
+    <t>7754807142779</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 NARANJA</t>
+  </si>
+  <si>
+    <t>015933</t>
+  </si>
+  <si>
+    <t>7754807159333</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 PERU</t>
+  </si>
+  <si>
+    <t>016676</t>
+  </si>
+  <si>
+    <t>7754807166768</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 GALAXY</t>
+  </si>
+  <si>
+    <t>016675</t>
+  </si>
+  <si>
+    <t>7754807166751</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 GALAXY</t>
+  </si>
+  <si>
+    <t>016752</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 LEGACY</t>
+  </si>
+  <si>
+    <t>016750</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 LEGACY</t>
+  </si>
+  <si>
+    <t>016751</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 JAM</t>
+  </si>
+  <si>
+    <t>016749</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 JAM</t>
+  </si>
+  <si>
+    <t>016764</t>
+  </si>
+  <si>
+    <t>BALONMANO GOMA #1</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
-  </si>
-  <si>
-    <t>016727</t>
-  </si>
-  <si>
-    <t>7754807167277</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
-  </si>
-  <si>
-    <t>016756</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
-  </si>
-  <si>
-    <t>016755</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>016757</t>
-  </si>
-  <si>
-    <t>7754807167574</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
-  </si>
-  <si>
-    <t>016760</t>
-  </si>
-  <si>
-    <t>7754807167604</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
-  </si>
-  <si>
-    <t>016758</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #5</t>
-  </si>
-  <si>
-    <t>016761</t>
-  </si>
-  <si>
-    <t>7754807167611</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #4</t>
-  </si>
-  <si>
-    <t>016759</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BRASIL #5</t>
-  </si>
-  <si>
-    <t>016762</t>
-  </si>
-  <si>
-    <t>7754807167628</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BRASIL #4</t>
-  </si>
-  <si>
-    <t>016706</t>
-  </si>
-  <si>
-    <t>7754807167062</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BLANQUIRROJA #5</t>
-  </si>
-  <si>
-    <t>016708</t>
-  </si>
-  <si>
-    <t>7754807167086</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
-  </si>
-  <si>
-    <t>014375</t>
-  </si>
-  <si>
-    <t>7754807143752</t>
-  </si>
-  <si>
-    <t>FUTSAL CUERO VULC #3.5</t>
-  </si>
-  <si>
-    <t>016766</t>
-  </si>
-  <si>
-    <t>FUTSAL TERMOSELLADA ALEGRO</t>
-  </si>
-  <si>
-    <t>016767</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER1 #5</t>
-  </si>
-  <si>
-    <t>016768</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER2 #5</t>
-  </si>
-  <si>
-    <t>016769</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER3 #5</t>
-  </si>
-  <si>
-    <t>016770</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER4 #5</t>
-  </si>
-  <si>
-    <t>016771</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER1 #4</t>
-  </si>
-  <si>
-    <t>016743</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU PER2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016744</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU BRA2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016745</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU ARG2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016746</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU FLAGS CUP24 #5</t>
-  </si>
-  <si>
-    <t>016747</t>
-  </si>
-  <si>
-    <t>VOLEY PU LIGA1</t>
-  </si>
-  <si>
-    <t>016748</t>
-  </si>
-  <si>
-    <t>VOLEY PU LIGA2</t>
-  </si>
-  <si>
-    <t>016729</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FLORES</t>
-  </si>
-  <si>
-    <t>016731</t>
-  </si>
-  <si>
-    <t>VOLEY CUP CUERO COSIDO CELESTE AMARILLO ROSADO</t>
-  </si>
-  <si>
-    <t>016728</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FOLK</t>
-  </si>
-  <si>
-    <t>016730</t>
-  </si>
-  <si>
-    <t>7754807167307</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FOLK GRAFITTI</t>
-  </si>
-  <si>
-    <t>016788</t>
-  </si>
-  <si>
-    <t>7754807167888</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO CREW</t>
-  </si>
-  <si>
-    <t>016737</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR1</t>
-  </si>
-  <si>
-    <t>016738</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR2</t>
-  </si>
-  <si>
-    <t>016739</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR3</t>
-  </si>
-  <si>
-    <t>016004</t>
-  </si>
-  <si>
-    <t>7754807160049</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA SPARTANO #3</t>
-  </si>
-  <si>
-    <t>015938</t>
-  </si>
-  <si>
-    <t>7754807159388</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA FREE #5</t>
-  </si>
-  <si>
-    <t>016678</t>
-  </si>
-  <si>
-    <t>7754807166782</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA URBAN #5</t>
-  </si>
-  <si>
-    <t>016724</t>
-  </si>
-  <si>
-    <t>7754807167246</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA SPECTRE #5</t>
-  </si>
-  <si>
-    <t>016783</t>
-  </si>
-  <si>
-    <t>7754807167833</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA INVICTUS  #5</t>
-  </si>
-  <si>
-    <t>014323</t>
-  </si>
-  <si>
-    <t>7754807143233</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA PAISES BLANCO #5</t>
-  </si>
-  <si>
-    <t>014796</t>
-  </si>
-  <si>
-    <t>7754807147965</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA TEAM #5</t>
-  </si>
-  <si>
-    <t>011883</t>
-  </si>
-  <si>
-    <t>7754807118835</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA PAISES COLORES #5</t>
-  </si>
-  <si>
-    <t>016657</t>
-  </si>
-  <si>
-    <t>7754807166577</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA BUTTERFLY</t>
-  </si>
-  <si>
-    <t>015936</t>
-  </si>
-  <si>
-    <t>7754807159364</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA MULTICOLOR</t>
-  </si>
-  <si>
-    <t>014268</t>
-  </si>
-  <si>
-    <t>7754807142687</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA TRICOLOR</t>
-  </si>
-  <si>
-    <t>016784</t>
-  </si>
-  <si>
-    <t>7754807167840</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA FLORES2</t>
-  </si>
-  <si>
-    <t>016786</t>
-  </si>
-  <si>
-    <t>7754807167864</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA FRUTAS2</t>
-  </si>
-  <si>
-    <t>015939</t>
-  </si>
-  <si>
-    <t>7754807159395</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA FOLK</t>
-  </si>
-  <si>
-    <t>016785</t>
-  </si>
-  <si>
-    <t>7754807167857</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA MARIPOSAS</t>
-  </si>
-  <si>
-    <t>016787</t>
-  </si>
-  <si>
-    <t>7754807167871</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA URBANA</t>
-  </si>
-  <si>
-    <t>016672</t>
-  </si>
-  <si>
-    <t>7754807166720</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #3 SONRISAS</t>
-  </si>
-  <si>
-    <t>014271</t>
-  </si>
-  <si>
-    <t>7754807142717</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #3 NARANJA</t>
-  </si>
-  <si>
-    <t>014270</t>
-  </si>
-  <si>
-    <t>7754807111638</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 NARANJA</t>
-  </si>
-  <si>
-    <t>014277</t>
-  </si>
-  <si>
-    <t>7754807142779</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 NARANJA</t>
-  </si>
-  <si>
-    <t>015933</t>
-  </si>
-  <si>
-    <t>7754807159333</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 PERU</t>
-  </si>
-  <si>
-    <t>016676</t>
-  </si>
-  <si>
-    <t>7754807166768</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 GALAXY</t>
-  </si>
-  <si>
-    <t>016675</t>
-  </si>
-  <si>
-    <t>7754807166751</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 GALAXY</t>
-  </si>
-  <si>
-    <t>016752</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 LEGACY</t>
-  </si>
-  <si>
-    <t>016750</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 LEGACY</t>
-  </si>
-  <si>
-    <t>016751</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 JAM</t>
-  </si>
-  <si>
-    <t>016749</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 JAM</t>
-  </si>
-  <si>
-    <t>016764</t>
-  </si>
-  <si>
-    <t>BALONMANO GOMA #1</t>
   </si>
   <si>
     <t>016765</t>
@@ -1712,12 +1712,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1740,12 +1740,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -2196,11 +2196,11 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="2">
-        <v>2050</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2208,22 +2208,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>24</v>
       </c>
       <c r="F4" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2242,11 +2242,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="2">
-        <v>3800</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2265,11 +2265,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="2">
-        <v>606</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2288,11 +2288,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2300,22 +2300,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
       </c>
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="2">
-        <v>4742</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2323,22 +2323,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
       </c>
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="2">
-        <v>1463</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2346,22 +2346,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>24</v>
       </c>
-      <c r="F10" s="2">
-        <v>1496</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2369,22 +2369,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="2">
-        <v>180</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2392,22 +2392,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
-      <c r="F12" s="2">
-        <v>1426</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2415,22 +2415,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
       </c>
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="2">
-        <v>168</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2438,22 +2438,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
       </c>
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="2">
-        <v>182</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2461,22 +2461,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
       </c>
       <c r="E15">
         <v>36</v>
       </c>
       <c r="F15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2484,22 +2484,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>48</v>
       </c>
       <c r="E16">
         <v>36</v>
       </c>
-      <c r="F16" s="2">
-        <v>1012</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2507,22 +2507,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>24</v>
       </c>
       <c r="F17" s="4">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2530,22 +2530,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>36</v>
       </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>23</v>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2553,22 +2553,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="2">
-        <v>3828</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2576,22 +2576,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="2">
-        <v>3206</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2599,22 +2599,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21">
         <v>36</v>
       </c>
-      <c r="F21" s="2">
-        <v>8229</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2622,22 +2622,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="2">
-        <v>1330</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2645,22 +2645,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>48</v>
       </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2668,22 +2668,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2691,22 +2691,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2714,22 +2714,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26">
         <v>48</v>
       </c>
       <c r="F26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2737,22 +2737,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>23</v>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2760,22 +2760,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28">
         <v>36</v>
       </c>
       <c r="F28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2783,22 +2783,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="2">
-        <v>3043</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,22 +2806,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>23</v>
+      <c r="F30" s="4">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2829,22 +2829,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>23</v>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2852,22 +2852,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>81</v>
       </c>
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="2">
-        <v>3505</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,22 +2875,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
         <v>82</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>83</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="2">
-        <v>2922</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,22 +2898,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="2">
-        <v>263</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2921,22 +2921,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="2">
-        <v>518</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,22 +2944,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="2">
-        <v>873</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" t="s">
         <v>91</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>93</v>
       </c>
       <c r="E37">
         <v>48</v>
       </c>
-      <c r="F37" s="2">
-        <v>7641</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,22 +2990,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
         <v>94</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>95</v>
-      </c>
-      <c r="D38" t="s">
-        <v>96</v>
       </c>
       <c r="E38">
         <v>48</v>
       </c>
-      <c r="F38" s="2">
-        <v>1483</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,22 +3013,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
         <v>97</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>98</v>
-      </c>
-      <c r="D39" t="s">
-        <v>99</v>
       </c>
       <c r="E39">
         <v>48</v>
       </c>
-      <c r="F39" s="6">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>23</v>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,22 +3036,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
         <v>100</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>102</v>
       </c>
       <c r="E40">
         <v>48</v>
       </c>
-      <c r="F40" s="6">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>23</v>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" t="s">
         <v>103</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>105</v>
       </c>
       <c r="E41">
         <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,22 +3082,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" t="s">
         <v>106</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>107</v>
-      </c>
-      <c r="D42" t="s">
-        <v>108</v>
       </c>
       <c r="E42">
         <v>48</v>
       </c>
       <c r="F42" s="4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3105,22 +3105,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" t="s">
         <v>109</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>111</v>
       </c>
       <c r="E43">
         <v>48</v>
       </c>
-      <c r="F43" s="6">
-        <v>0</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>23</v>
+      <c r="F43" s="4">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3128,22 +3128,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s">
         <v>112</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>114</v>
       </c>
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="2">
-        <v>6524</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3151,22 +3151,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
         <v>115</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>116</v>
-      </c>
-      <c r="D45" t="s">
-        <v>117</v>
       </c>
       <c r="E45">
         <v>48</v>
       </c>
-      <c r="F45" s="6">
-        <v>0</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>23</v>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3174,22 +3174,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" t="s">
         <v>118</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>119</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
       </c>
       <c r="E46">
         <v>48</v>
       </c>
-      <c r="F46" s="6">
-        <v>0</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>23</v>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3197,22 +3197,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" t="s">
         <v>121</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>122</v>
-      </c>
-      <c r="D47" t="s">
-        <v>123</v>
       </c>
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="2">
-        <v>11965</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="4">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,22 +3220,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" t="s">
         <v>124</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>125</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
       </c>
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="6">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>23</v>
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3243,22 +3243,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s">
         <v>127</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>128</v>
-      </c>
-      <c r="D49" t="s">
-        <v>129</v>
       </c>
       <c r="E49">
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3266,22 +3266,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
         <v>130</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>131</v>
-      </c>
-      <c r="D50" t="s">
-        <v>132</v>
       </c>
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="2">
-        <v>5578</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3289,22 +3289,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
         <v>133</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>134</v>
-      </c>
-      <c r="D51" t="s">
-        <v>135</v>
       </c>
       <c r="E51">
         <v>48</v>
       </c>
-      <c r="F51" s="6">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>23</v>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3312,22 +3312,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" t="s">
         <v>136</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>137</v>
-      </c>
-      <c r="D52" t="s">
-        <v>138</v>
       </c>
       <c r="E52">
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3335,22 +3335,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" t="s">
         <v>139</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>140</v>
-      </c>
-      <c r="D53" t="s">
-        <v>141</v>
       </c>
       <c r="E53">
         <v>48</v>
       </c>
       <c r="F53" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,22 +3358,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" t="s">
         <v>142</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>143</v>
-      </c>
-      <c r="D54" t="s">
-        <v>144</v>
       </c>
       <c r="E54">
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3381,22 +3381,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" t="s">
         <v>145</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>146</v>
-      </c>
-      <c r="D55" t="s">
-        <v>147</v>
       </c>
       <c r="E55">
         <v>36</v>
       </c>
-      <c r="F55" s="2">
-        <v>1955</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="F55" s="4">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3404,22 +3404,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" t="s">
         <v>148</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>149</v>
-      </c>
-      <c r="D56" t="s">
-        <v>150</v>
       </c>
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="2">
-        <v>196</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3427,22 +3427,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
         <v>151</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>152</v>
-      </c>
-      <c r="D57" t="s">
-        <v>153</v>
       </c>
       <c r="E57">
         <v>36</v>
       </c>
-      <c r="F57" s="2">
-        <v>2190</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3450,22 +3450,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" t="s">
         <v>154</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>155</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
       </c>
       <c r="E58">
         <v>36</v>
       </c>
-      <c r="F58" s="6">
-        <v>0</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>23</v>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3473,22 +3473,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" t="s">
         <v>157</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>158</v>
-      </c>
-      <c r="D59" t="s">
-        <v>159</v>
       </c>
       <c r="E59">
         <v>36</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>23</v>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3496,22 +3496,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E60">
         <v>36</v>
       </c>
-      <c r="F60" s="2">
-        <v>1377</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3519,22 +3519,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E61">
         <v>36</v>
       </c>
-      <c r="F61" s="6">
-        <v>0</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>23</v>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,22 +3542,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E62">
         <v>36</v>
       </c>
-      <c r="F62" s="2">
-        <v>915</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3565,22 +3565,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E63">
         <v>36</v>
       </c>
-      <c r="F63" s="2">
-        <v>798</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3588,22 +3588,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="2">
-        <v>418</v>
-      </c>
-      <c r="G64" s="3" t="s">
+      <c r="F64" s="6">
         <v>10</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3622,11 +3622,11 @@
       <c r="E65">
         <v>48</v>
       </c>
-      <c r="F65" s="2">
-        <v>1218</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3645,11 +3645,11 @@
       <c r="E66">
         <v>60</v>
       </c>
-      <c r="F66" s="2">
-        <v>5188</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3668,11 +3668,11 @@
       <c r="E67">
         <v>60</v>
       </c>
-      <c r="F67" s="2">
-        <v>1226</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3691,11 +3691,11 @@
       <c r="E68">
         <v>60</v>
       </c>
-      <c r="F68" s="2">
-        <v>2119</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3714,11 +3714,11 @@
       <c r="E69">
         <v>60</v>
       </c>
-      <c r="F69" s="2">
-        <v>1118</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>10</v>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3737,11 +3737,11 @@
       <c r="E70">
         <v>60</v>
       </c>
-      <c r="F70" s="2">
-        <v>4180</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3760,11 +3760,11 @@
       <c r="E71">
         <v>60</v>
       </c>
-      <c r="F71" s="2">
-        <v>5085</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3783,11 +3783,11 @@
       <c r="E72">
         <v>60</v>
       </c>
-      <c r="F72" s="6">
-        <v>0</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>23</v>
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3806,11 +3806,11 @@
       <c r="E73">
         <v>60</v>
       </c>
-      <c r="F73" s="2">
-        <v>3198</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3829,11 +3829,11 @@
       <c r="E74">
         <v>60</v>
       </c>
-      <c r="F74" s="2">
-        <v>1302</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3852,11 +3852,11 @@
       <c r="E75">
         <v>60</v>
       </c>
-      <c r="F75" s="2">
-        <v>4399</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3875,11 +3875,11 @@
       <c r="E76">
         <v>60</v>
       </c>
-      <c r="F76" s="2">
-        <v>8596</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3898,11 +3898,11 @@
       <c r="E77">
         <v>60</v>
       </c>
-      <c r="F77" s="2">
-        <v>3977</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3921,11 +3921,11 @@
       <c r="E78">
         <v>60</v>
       </c>
-      <c r="F78" s="2">
-        <v>6465</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3944,11 +3944,11 @@
       <c r="E79">
         <v>60</v>
       </c>
-      <c r="F79" s="2">
-        <v>5202</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3968,10 +3968,10 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3991,10 +3991,10 @@
         <v>60</v>
       </c>
       <c r="F81" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="2">
-        <v>1124</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>10</v>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4036,11 +4036,11 @@
       <c r="E83">
         <v>60</v>
       </c>
-      <c r="F83" s="2">
-        <v>1037</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4059,11 +4059,11 @@
       <c r="E84">
         <v>60</v>
       </c>
-      <c r="F84" s="6">
-        <v>0</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>23</v>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4083,10 +4083,10 @@
         <v>60</v>
       </c>
       <c r="F85" s="4">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4105,11 +4105,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="2">
-        <v>333</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4128,11 +4128,11 @@
       <c r="E87">
         <v>60</v>
       </c>
-      <c r="F87" s="2">
-        <v>1531</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>23</v>
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,11 +4174,11 @@
       <c r="E89">
         <v>60</v>
       </c>
-      <c r="F89" s="6">
-        <v>0</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>23</v>
+      <c r="F89" s="4">
+        <v>0</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,11 +4197,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="2">
-        <v>734</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="F90" s="4">
+        <v>0</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="2">
-        <v>1518</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4243,11 +4243,11 @@
       <c r="E92">
         <v>60</v>
       </c>
-      <c r="F92" s="2">
-        <v>1372</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="F92" s="4">
+        <v>0</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="2">
-        <v>1251</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>10</v>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="2">
-        <v>1399</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>10</v>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4312,11 +4312,11 @@
       <c r="E95">
         <v>60</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>23</v>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4335,11 +4335,11 @@
       <c r="E96">
         <v>60</v>
       </c>
-      <c r="F96" s="2">
-        <v>2485</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="F96" s="4">
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4358,11 +4358,11 @@
       <c r="E97">
         <v>60</v>
       </c>
-      <c r="F97" s="2">
-        <v>5025</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="F97" s="4">
+        <v>0</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4381,11 +4381,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="2">
-        <v>3434</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4404,11 +4404,11 @@
       <c r="E99">
         <v>60</v>
       </c>
-      <c r="F99" s="2">
-        <v>3915</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="F99" s="4">
+        <v>0</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4427,11 +4427,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="2">
-        <v>1544</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>10</v>
+      <c r="F100" s="4">
+        <v>0</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4450,11 +4450,11 @@
       <c r="E101">
         <v>60</v>
       </c>
-      <c r="F101" s="2">
-        <v>5802</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>10</v>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -4473,11 +4473,11 @@
       <c r="E102">
         <v>60</v>
       </c>
-      <c r="F102" s="2">
-        <v>3253</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>10</v>
+      <c r="F102" s="4">
+        <v>0</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4496,11 +4496,11 @@
       <c r="E103">
         <v>60</v>
       </c>
-      <c r="F103" s="2">
-        <v>1816</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>10</v>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4519,11 +4519,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="2">
-        <v>368</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4542,11 +4542,11 @@
       <c r="E105">
         <v>60</v>
       </c>
-      <c r="F105" s="6">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>23</v>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="2">
-        <v>852</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4588,11 +4588,11 @@
       <c r="E107">
         <v>60</v>
       </c>
-      <c r="F107" s="2">
-        <v>5594</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4611,11 +4611,11 @@
       <c r="E108">
         <v>60</v>
       </c>
-      <c r="F108" s="2">
-        <v>1998</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4634,11 +4634,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="2">
-        <v>1725</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4657,11 +4657,11 @@
       <c r="E110">
         <v>60</v>
       </c>
-      <c r="F110" s="2">
-        <v>1887</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4680,11 +4680,11 @@
       <c r="E111">
         <v>60</v>
       </c>
-      <c r="F111" s="2">
-        <v>6130</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4703,11 +4703,11 @@
       <c r="E112">
         <v>60</v>
       </c>
-      <c r="F112" s="2">
-        <v>7112</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4726,11 +4726,11 @@
       <c r="E113">
         <v>60</v>
       </c>
-      <c r="F113" s="2">
-        <v>6610</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4749,11 +4749,11 @@
       <c r="E114">
         <v>60</v>
       </c>
-      <c r="F114" s="2">
-        <v>11151</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4772,11 +4772,11 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115" s="2">
-        <v>239</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4795,11 +4795,11 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" s="2">
-        <v>85</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4818,11 +4818,11 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117" s="2">
-        <v>273</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4841,11 +4841,11 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="2">
-        <v>272</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>10</v>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -4864,11 +4864,11 @@
       <c r="E119">
         <v>12</v>
       </c>
-      <c r="F119" s="6">
-        <v>0</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>23</v>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,11 +4887,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="2">
-        <v>261</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,11 +4910,11 @@
       <c r="E121">
         <v>36</v>
       </c>
-      <c r="F121" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>23</v>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4933,11 +4933,11 @@
       <c r="E122">
         <v>12</v>
       </c>
-      <c r="F122" s="2">
-        <v>2925</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>36</v>
       </c>
       <c r="F123" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4979,11 +4979,11 @@
       <c r="E124">
         <v>12</v>
       </c>
-      <c r="F124" s="2">
-        <v>2515</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>10</v>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5002,11 +5002,11 @@
       <c r="E125">
         <v>36</v>
       </c>
-      <c r="F125" s="2">
-        <v>969</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="F125" s="4">
+        <v>0</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="2">
-        <v>2200</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4">
+        <v>0</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5049,10 +5049,10 @@
         <v>120</v>
       </c>
       <c r="F127" s="4">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,10 +5072,10 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5094,11 +5094,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="2">
-        <v>1067</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="F129" s="4">
+        <v>0</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="2">
-        <v>884</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="F130" s="4">
+        <v>0</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5141,10 +5141,10 @@
         <v>120</v>
       </c>
       <c r="F131" s="4">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5164,10 +5164,10 @@
         <v>120</v>
       </c>
       <c r="F132" s="4">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5186,11 +5186,11 @@
       <c r="E133">
         <v>120</v>
       </c>
-      <c r="F133" s="2">
-        <v>6592</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="F133" s="4">
+        <v>0</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5209,11 +5209,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="2">
-        <v>1017</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>10</v>
+      <c r="F134" s="4">
+        <v>0</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5233,10 +5233,10 @@
         <v>120</v>
       </c>
       <c r="F135" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5255,11 +5255,11 @@
       <c r="E136">
         <v>120</v>
       </c>
-      <c r="F136" s="2">
-        <v>4015</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>10</v>
+      <c r="F136" s="4">
+        <v>0</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5278,11 +5278,11 @@
       <c r="E137">
         <v>120</v>
       </c>
-      <c r="F137" s="2">
-        <v>1904</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>10</v>
+      <c r="F137" s="4">
+        <v>0</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5302,10 +5302,10 @@
         <v>120</v>
       </c>
       <c r="F138" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,11 +5324,11 @@
       <c r="E139">
         <v>120</v>
       </c>
-      <c r="F139" s="2">
-        <v>4463</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="F139" s="4">
+        <v>0</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5348,10 +5348,10 @@
         <v>120</v>
       </c>
       <c r="F140" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,11 +5370,11 @@
       <c r="E141">
         <v>120</v>
       </c>
-      <c r="F141" s="2">
-        <v>4217</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="F141" s="4">
+        <v>0</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5393,11 +5393,11 @@
       <c r="E142">
         <v>120</v>
       </c>
-      <c r="F142" s="2">
-        <v>3364</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="F142" s="4">
+        <v>0</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5417,10 +5417,10 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,11 +5439,11 @@
       <c r="E144">
         <v>120</v>
       </c>
-      <c r="F144" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>23</v>
+      <c r="F144" s="4">
+        <v>0</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5463,10 +5463,10 @@
         <v>120</v>
       </c>
       <c r="F145" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="2">
-        <v>752</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="4">
+        <v>0</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,11 +5508,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="2">
-        <v>1964</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="F147" s="4">
+        <v>0</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5532,10 +5532,10 @@
         <v>120</v>
       </c>
       <c r="F148" s="4">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5555,10 +5555,10 @@
         <v>120</v>
       </c>
       <c r="F149" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5578,10 +5578,10 @@
         <v>120</v>
       </c>
       <c r="F150" s="4">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -5600,11 +5600,11 @@
       <c r="E151">
         <v>120</v>
       </c>
-      <c r="F151" s="2">
-        <v>2007</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>10</v>
+      <c r="F151" s="4">
+        <v>0</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -5624,10 +5624,10 @@
         <v>120</v>
       </c>
       <c r="F152" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,11 +5646,11 @@
       <c r="E153">
         <v>120</v>
       </c>
-      <c r="F153" s="6">
-        <v>0</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>23</v>
+      <c r="F153" s="4">
+        <v>0</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5669,11 +5669,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
-        <v>3277</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="F154" s="4">
+        <v>0</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5692,11 +5692,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="2">
-        <v>908</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>10</v>
+      <c r="F155" s="4">
+        <v>0</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5716,10 +5716,10 @@
         <v>120</v>
       </c>
       <c r="F156" s="4">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5738,11 +5738,11 @@
       <c r="E157">
         <v>120</v>
       </c>
-      <c r="F157" s="2">
-        <v>3114</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="F157" s="4">
+        <v>0</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="2">
-        <v>1101</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="4">
+        <v>0</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5784,11 +5784,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
-        <v>3978</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="4">
+        <v>0</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5808,10 +5808,10 @@
         <v>120</v>
       </c>
       <c r="F160" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="2">
-        <v>1926</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="F161" s="4">
+        <v>0</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5853,11 +5853,11 @@
       <c r="E162">
         <v>120</v>
       </c>
-      <c r="F162" s="2">
-        <v>4672</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="F162" s="4">
+        <v>0</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5876,11 +5876,11 @@
       <c r="E163">
         <v>120</v>
       </c>
-      <c r="F163" s="2">
-        <v>4562</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="F163" s="4">
+        <v>0</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5900,10 +5900,10 @@
         <v>120</v>
       </c>
       <c r="F164" s="4">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5922,11 +5922,11 @@
       <c r="E165">
         <v>120</v>
       </c>
-      <c r="F165" s="2">
-        <v>1260</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="F165" s="4">
+        <v>0</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5945,11 +5945,11 @@
       <c r="E166">
         <v>120</v>
       </c>
-      <c r="F166" s="2">
-        <v>3735</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="F166" s="4">
+        <v>0</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5968,11 +5968,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="2">
-        <v>764</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="F167" s="4">
+        <v>0</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,10 +5992,10 @@
         <v>120</v>
       </c>
       <c r="F168" s="4">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6014,11 +6014,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="2">
-        <v>703</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="F169" s="4">
+        <v>0</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6037,11 +6037,11 @@
       <c r="E170">
         <v>120</v>
       </c>
-      <c r="F170" s="6">
-        <v>0</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>23</v>
+      <c r="F170" s="4">
+        <v>0</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6060,11 +6060,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="2">
-        <v>7702</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>10</v>
+      <c r="F171" s="4">
+        <v>0</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6083,11 +6083,11 @@
       <c r="E172">
         <v>120</v>
       </c>
-      <c r="F172" s="2">
-        <v>2089</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="F172" s="4">
+        <v>0</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6106,11 +6106,11 @@
       <c r="E173">
         <v>1</v>
       </c>
-      <c r="F173" s="2">
-        <v>232</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="F173" s="4">
+        <v>0</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6129,11 +6129,11 @@
       <c r="E174">
         <v>1</v>
       </c>
-      <c r="F174" s="2">
-        <v>147</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="F174" s="4">
+        <v>0</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6153,10 +6153,10 @@
         <v>12</v>
       </c>
       <c r="F175" s="4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6175,11 +6175,11 @@
       <c r="E176">
         <v>12</v>
       </c>
-      <c r="F176" s="6">
-        <v>0</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>23</v>
+      <c r="F176" s="4">
+        <v>0</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6198,11 +6198,11 @@
       <c r="E177">
         <v>12</v>
       </c>
-      <c r="F177" s="6">
-        <v>0</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>23</v>
+      <c r="F177" s="4">
+        <v>0</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6221,11 +6221,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="2">
-        <v>163</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>10</v>
+      <c r="F178" s="4">
+        <v>0</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6245,10 +6245,10 @@
         <v>12</v>
       </c>
       <c r="F179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6267,11 +6267,11 @@
       <c r="E180">
         <v>12</v>
       </c>
-      <c r="F180" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>23</v>
+      <c r="F180" s="4">
+        <v>0</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6290,11 +6290,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="6">
-        <v>0</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>23</v>
+      <c r="F181" s="4">
+        <v>0</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6313,11 +6313,11 @@
       <c r="E182">
         <v>12</v>
       </c>
-      <c r="F182" s="2">
-        <v>211</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="F182" s="4">
+        <v>0</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6337,10 +6337,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -6360,10 +6360,10 @@
         <v>12</v>
       </c>
       <c r="F184" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -6382,11 +6382,11 @@
       <c r="E185">
         <v>12</v>
       </c>
-      <c r="F185" s="2">
-        <v>3022</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>10</v>
+      <c r="F185" s="4">
+        <v>0</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="2">
-        <v>286</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="F186" s="4">
+        <v>0</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="2">
-        <v>157</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="4">
+        <v>0</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6451,11 +6451,11 @@
       <c r="E188">
         <v>12</v>
       </c>
-      <c r="F188" s="2">
-        <v>654</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="F188" s="4">
+        <v>0</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6475,10 +6475,10 @@
         <v>18</v>
       </c>
       <c r="F189" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6497,11 +6497,11 @@
       <c r="E190">
         <v>12</v>
       </c>
-      <c r="F190" s="2">
-        <v>1156</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>10</v>
+      <c r="F190" s="4">
+        <v>0</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -6520,11 +6520,11 @@
       <c r="E191">
         <v>18</v>
       </c>
-      <c r="F191" s="2">
-        <v>1901</v>
-      </c>
-      <c r="G191" s="3" t="s">
-        <v>10</v>
+      <c r="F191" s="4">
+        <v>0</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -6543,11 +6543,11 @@
       <c r="E192">
         <v>12</v>
       </c>
-      <c r="F192" s="2">
-        <v>1913</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>10</v>
+      <c r="F192" s="4">
+        <v>0</v>
+      </c>
+      <c r="G192" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -6566,11 +6566,11 @@
       <c r="E193">
         <v>400</v>
       </c>
-      <c r="F193" s="2">
-        <v>76950</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>10</v>
+      <c r="F193" s="4">
+        <v>0</v>
+      </c>
+      <c r="G193" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -6589,11 +6589,11 @@
       <c r="E194">
         <v>400</v>
       </c>
-      <c r="F194" s="2">
-        <v>72165</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>10</v>
+      <c r="F194" s="4">
+        <v>0</v>
+      </c>
+      <c r="G194" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -6612,11 +6612,11 @@
       <c r="E195">
         <v>120</v>
       </c>
-      <c r="F195" s="2">
-        <v>3620</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>10</v>
+      <c r="F195" s="4">
+        <v>0</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="2">
-        <v>1816</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>10</v>
+      <c r="F196" s="4">
+        <v>0</v>
+      </c>
+      <c r="G196" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6658,11 +6658,11 @@
       <c r="E197">
         <v>120</v>
       </c>
-      <c r="F197" s="2">
-        <v>8964</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>10</v>
+      <c r="F197" s="4">
+        <v>0</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="6">
-        <v>0</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>23</v>
+      <c r="F198" s="4">
+        <v>0</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -6704,11 +6704,11 @@
       <c r="E199">
         <v>120</v>
       </c>
-      <c r="F199" s="2">
-        <v>8040</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>10</v>
+      <c r="F199" s="4">
+        <v>0</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4312,11 +4312,11 @@
       <c r="E95">
         <v>60</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>23</v>
+      <c r="F95" s="4">
+        <v>1</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1483</v>
+        <v>1435</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3071,7 +3071,7 @@
         <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>15</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>6499</v>
+        <v>6450</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11847</v>
+        <v>11798</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>5570</v>
+        <v>5474</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3324,7 +3324,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
@@ -3346,11 +3346,11 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="4">
-        <v>5</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>15</v>
+      <c r="F53" s="2">
+        <v>294</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>2218</v>
+        <v>2182</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>1299</v>
+        <v>1269</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>4399</v>
+        <v>4369</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5202</v>
+        <v>5172</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -4014,7 +4014,7 @@
         <v>60</v>
       </c>
       <c r="F82" s="2">
-        <v>1124</v>
+        <v>1094</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>1369</v>
+        <v>1349</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1394</v>
+        <v>1374</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>2485</v>
+        <v>2455</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>3432</v>
+        <v>3401</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>1543</v>
+        <v>1513</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>2999</v>
+        <v>2969</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>1728</v>
+        <v>1668</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>7097</v>
+        <v>7067</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>6609</v>
+        <v>6549</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>11106</v>
+        <v>11076</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5347,11 +5347,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="6">
-        <v>0</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>23</v>
+      <c r="F140" s="2">
+        <v>870</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5486,7 +5486,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="2">
-        <v>743</v>
+        <v>683</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>10</v>
@@ -6037,11 +6037,11 @@
       <c r="E170">
         <v>120</v>
       </c>
-      <c r="F170" s="6">
-        <v>0</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>23</v>
+      <c r="F170" s="4">
+        <v>43</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>76950</v>
+        <v>76550</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>72165</v>
+        <v>71765</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11798</v>
+        <v>11797</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>6450</v>
+        <v>6447</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>6447</v>
+        <v>6183</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3416,7 +3416,7 @@
         <v>36</v>
       </c>
       <c r="F56" s="4">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>15</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1375</v>
+        <v>1351</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3967,11 +3967,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="4">
-        <v>11</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>15</v>
+      <c r="F80" s="6">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4014,7 +4014,7 @@
         <v>60</v>
       </c>
       <c r="F82" s="2">
-        <v>1094</v>
+        <v>938</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>1517</v>
+        <v>1433</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4566,7 +4566,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="2">
-        <v>1458</v>
+        <v>1386</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>1668</v>
+        <v>1644</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -6406,7 +6406,7 @@
         <v>12</v>
       </c>
       <c r="F186" s="2">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>10</v>
@@ -6521,7 +6521,7 @@
         <v>18</v>
       </c>
       <c r="F191" s="2">
-        <v>1901</v>
+        <v>1865</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>76550</v>
+        <v>75750</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>71765</v>
+        <v>70965</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2050</v>
+        <v>2044</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5341</v>
+        <v>5335</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2922</v>
+        <v>2916</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1435</v>
+        <v>1387</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11797</v>
+        <v>11773</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3324,7 +3324,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>3194</v>
+        <v>3182</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8593</v>
+        <v>8545</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3967,11 +3967,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="6">
-        <v>0</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>23</v>
+      <c r="F80" s="4">
+        <v>72</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3914</v>
+        <v>3854</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>5577</v>
+        <v>5517</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>11076</v>
+        <v>11016</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>519</v>
+        <v>483</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>4217</v>
+        <v>4133</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5854,7 +5854,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="2">
-        <v>4672</v>
+        <v>4660</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>7702</v>
+        <v>7678</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2044</v>
+        <v>2038</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5335</v>
+        <v>5329</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2679,11 +2679,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2702,11 +2702,11 @@
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
+      <c r="F25" s="4">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2916</v>
+        <v>2910</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11773</v>
+        <v>11761</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3324,7 +3324,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8545</v>
+        <v>8533</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>15</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3854</v>
+        <v>3842</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>5517</v>
+        <v>5505</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>11016</v>
+        <v>11004</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>4133</v>
+        <v>4127</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5854,7 +5854,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="2">
-        <v>4660</v>
+        <v>4648</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>2065</v>
+        <v>2053</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5323</v>
+        <v>5320</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3504</v>
+        <v>3498</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2904</v>
+        <v>2901</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11737</v>
+        <v>11731</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>5474</v>
+        <v>5468</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>2190</v>
+        <v>2181</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>3170</v>
+        <v>3152</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>1221</v>
+        <v>1203</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8509</v>
+        <v>8491</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>15</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>1513</v>
+        <v>1495</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>10980</v>
+        <v>10968</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="2">
-        <v>2508</v>
+        <v>2460</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5578,7 +5578,7 @@
         <v>120</v>
       </c>
       <c r="F150" s="4">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="G150" s="5" t="s">
         <v>15</v>
@@ -5601,7 +5601,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="2">
-        <v>2007</v>
+        <v>1995</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>3277</v>
+        <v>3265</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5807,11 +5807,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="4">
-        <v>6</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>15</v>
+      <c r="F160" s="6">
+        <v>0</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5831,7 +5831,7 @@
         <v>120</v>
       </c>
       <c r="F161" s="2">
-        <v>1926</v>
+        <v>1914</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>7666</v>
+        <v>7654</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -6130,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="2">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -4888,7 +4888,7 @@
         <v>36</v>
       </c>
       <c r="F120" s="2">
-        <v>262</v>
+        <v>202</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -52,475 +52,475 @@
     <t>FUTBOL CUERO TERMOSELLADA PRECISION #5</t>
   </si>
   <si>
+    <t>✗ AGOTADO</t>
+  </si>
+  <si>
     <t>016726</t>
   </si>
   <si>
     <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
   </si>
   <si>
+    <t>016727</t>
+  </si>
+  <si>
+    <t>7754807167277</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
+  </si>
+  <si>
+    <t>016756</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
+  </si>
+  <si>
+    <t>016755</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
+  </si>
+  <si>
+    <t>016757</t>
+  </si>
+  <si>
+    <t>7754807167574</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
+  </si>
+  <si>
+    <t>016760</t>
+  </si>
+  <si>
+    <t>7754807167604</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
+  </si>
+  <si>
+    <t>016758</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #5</t>
+  </si>
+  <si>
+    <t>016761</t>
+  </si>
+  <si>
+    <t>7754807167611</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #4</t>
+  </si>
+  <si>
+    <t>016759</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BRASIL #5</t>
+  </si>
+  <si>
+    <t>016762</t>
+  </si>
+  <si>
+    <t>7754807167628</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BRASIL #4</t>
+  </si>
+  <si>
+    <t>016706</t>
+  </si>
+  <si>
+    <t>7754807167062</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BLANQUIRROJA #5</t>
+  </si>
+  <si>
+    <t>016708</t>
+  </si>
+  <si>
+    <t>7754807167086</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
+  </si>
+  <si>
+    <t>014375</t>
+  </si>
+  <si>
+    <t>7754807143752</t>
+  </si>
+  <si>
+    <t>FUTSAL CUERO VULC #3.5</t>
+  </si>
+  <si>
+    <t>016766</t>
+  </si>
+  <si>
+    <t>FUTSAL TERMOSELLADA ALEGRO</t>
+  </si>
+  <si>
+    <t>016767</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER1 #5</t>
+  </si>
+  <si>
+    <t>016768</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER2 #5</t>
+  </si>
+  <si>
+    <t>016769</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER3 #5</t>
+  </si>
+  <si>
+    <t>016770</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER4 #5</t>
+  </si>
+  <si>
+    <t>016771</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER1 #4</t>
+  </si>
+  <si>
+    <t>016743</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU PER2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016744</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU BRA2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016745</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU ARG2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016746</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU FLAGS CUP24 #5</t>
+  </si>
+  <si>
+    <t>016747</t>
+  </si>
+  <si>
+    <t>VOLEY PU LIGA1</t>
+  </si>
+  <si>
+    <t>016748</t>
+  </si>
+  <si>
+    <t>VOLEY PU LIGA2</t>
+  </si>
+  <si>
+    <t>016729</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FLORES</t>
+  </si>
+  <si>
+    <t>016731</t>
+  </si>
+  <si>
+    <t>VOLEY CUP CUERO COSIDO CELESTE AMARILLO ROSADO</t>
+  </si>
+  <si>
+    <t>016728</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FOLK</t>
+  </si>
+  <si>
+    <t>016730</t>
+  </si>
+  <si>
+    <t>7754807167307</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FOLK GRAFITTI</t>
+  </si>
+  <si>
+    <t>016788</t>
+  </si>
+  <si>
+    <t>7754807167888</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO CREW</t>
+  </si>
+  <si>
+    <t>016737</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR1</t>
+  </si>
+  <si>
+    <t>016738</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR2</t>
+  </si>
+  <si>
+    <t>016739</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR3</t>
+  </si>
+  <si>
+    <t>016004</t>
+  </si>
+  <si>
+    <t>7754807160049</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA SPARTANO #3</t>
+  </si>
+  <si>
+    <t>015938</t>
+  </si>
+  <si>
+    <t>7754807159388</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA FREE #5</t>
+  </si>
+  <si>
+    <t>016678</t>
+  </si>
+  <si>
+    <t>7754807166782</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA URBAN #5</t>
+  </si>
+  <si>
+    <t>016724</t>
+  </si>
+  <si>
+    <t>7754807167246</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA SPECTRE #5</t>
+  </si>
+  <si>
+    <t>016783</t>
+  </si>
+  <si>
+    <t>7754807167833</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA INVICTUS  #5</t>
+  </si>
+  <si>
+    <t>014323</t>
+  </si>
+  <si>
+    <t>7754807143233</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA PAISES BLANCO #5</t>
+  </si>
+  <si>
+    <t>014796</t>
+  </si>
+  <si>
+    <t>7754807147965</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA TEAM #5</t>
+  </si>
+  <si>
+    <t>011883</t>
+  </si>
+  <si>
+    <t>7754807118835</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA PAISES COLORES #5</t>
+  </si>
+  <si>
+    <t>016657</t>
+  </si>
+  <si>
+    <t>7754807166577</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA BUTTERFLY</t>
+  </si>
+  <si>
+    <t>015936</t>
+  </si>
+  <si>
+    <t>7754807159364</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA MULTICOLOR</t>
+  </si>
+  <si>
+    <t>014268</t>
+  </si>
+  <si>
+    <t>7754807142687</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA TRICOLOR</t>
+  </si>
+  <si>
+    <t>016784</t>
+  </si>
+  <si>
+    <t>7754807167840</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA FLORES2</t>
+  </si>
+  <si>
+    <t>016786</t>
+  </si>
+  <si>
+    <t>7754807167864</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA FRUTAS2</t>
+  </si>
+  <si>
+    <t>015939</t>
+  </si>
+  <si>
+    <t>7754807159395</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA FOLK</t>
+  </si>
+  <si>
+    <t>016785</t>
+  </si>
+  <si>
+    <t>7754807167857</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA MARIPOSAS</t>
+  </si>
+  <si>
+    <t>016787</t>
+  </si>
+  <si>
+    <t>7754807167871</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA URBANA</t>
+  </si>
+  <si>
+    <t>016672</t>
+  </si>
+  <si>
+    <t>7754807166720</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #3 SONRISAS</t>
+  </si>
+  <si>
+    <t>014271</t>
+  </si>
+  <si>
+    <t>7754807142717</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #3 NARANJA</t>
+  </si>
+  <si>
+    <t>014270</t>
+  </si>
+  <si>
+    <t>7754807111638</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 NARANJA</t>
+  </si>
+  <si>
+    <t>014277</t>
+  </si>
+  <si>
+    <t>7754807142779</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 NARANJA</t>
+  </si>
+  <si>
+    <t>015933</t>
+  </si>
+  <si>
+    <t>7754807159333</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 PERU</t>
+  </si>
+  <si>
+    <t>016676</t>
+  </si>
+  <si>
+    <t>7754807166768</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 GALAXY</t>
+  </si>
+  <si>
+    <t>016675</t>
+  </si>
+  <si>
+    <t>7754807166751</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 GALAXY</t>
+  </si>
+  <si>
+    <t>016752</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 LEGACY</t>
+  </si>
+  <si>
+    <t>016750</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 LEGACY</t>
+  </si>
+  <si>
+    <t>016751</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 JAM</t>
+  </si>
+  <si>
+    <t>016749</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 JAM</t>
+  </si>
+  <si>
+    <t>016764</t>
+  </si>
+  <si>
+    <t>BALONMANO GOMA #1</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
-  </si>
-  <si>
-    <t>016727</t>
-  </si>
-  <si>
-    <t>7754807167277</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
-  </si>
-  <si>
-    <t>016756</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
-  </si>
-  <si>
-    <t>016755</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>016757</t>
-  </si>
-  <si>
-    <t>7754807167574</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
-  </si>
-  <si>
-    <t>016760</t>
-  </si>
-  <si>
-    <t>7754807167604</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
-  </si>
-  <si>
-    <t>016758</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #5</t>
-  </si>
-  <si>
-    <t>016761</t>
-  </si>
-  <si>
-    <t>7754807167611</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #4</t>
-  </si>
-  <si>
-    <t>016759</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BRASIL #5</t>
-  </si>
-  <si>
-    <t>016762</t>
-  </si>
-  <si>
-    <t>7754807167628</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BRASIL #4</t>
-  </si>
-  <si>
-    <t>016706</t>
-  </si>
-  <si>
-    <t>7754807167062</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BLANQUIRROJA #5</t>
-  </si>
-  <si>
-    <t>016708</t>
-  </si>
-  <si>
-    <t>7754807167086</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
-  </si>
-  <si>
-    <t>014375</t>
-  </si>
-  <si>
-    <t>7754807143752</t>
-  </si>
-  <si>
-    <t>FUTSAL CUERO VULC #3.5</t>
-  </si>
-  <si>
-    <t>016766</t>
-  </si>
-  <si>
-    <t>FUTSAL TERMOSELLADA ALEGRO</t>
-  </si>
-  <si>
-    <t>016767</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER1 #5</t>
-  </si>
-  <si>
-    <t>016768</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER2 #5</t>
-  </si>
-  <si>
-    <t>016769</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER3 #5</t>
-  </si>
-  <si>
-    <t>016770</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER4 #5</t>
-  </si>
-  <si>
-    <t>016771</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER1 #4</t>
-  </si>
-  <si>
-    <t>016743</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU PER2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016744</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU BRA2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016745</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU ARG2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016746</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU FLAGS CUP24 #5</t>
-  </si>
-  <si>
-    <t>016747</t>
-  </si>
-  <si>
-    <t>VOLEY PU LIGA1</t>
-  </si>
-  <si>
-    <t>016748</t>
-  </si>
-  <si>
-    <t>VOLEY PU LIGA2</t>
-  </si>
-  <si>
-    <t>016729</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FLORES</t>
-  </si>
-  <si>
-    <t>016731</t>
-  </si>
-  <si>
-    <t>VOLEY CUP CUERO COSIDO CELESTE AMARILLO ROSADO</t>
-  </si>
-  <si>
-    <t>016728</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FOLK</t>
-  </si>
-  <si>
-    <t>016730</t>
-  </si>
-  <si>
-    <t>7754807167307</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FOLK GRAFITTI</t>
-  </si>
-  <si>
-    <t>016788</t>
-  </si>
-  <si>
-    <t>7754807167888</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO CREW</t>
-  </si>
-  <si>
-    <t>016737</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR1</t>
-  </si>
-  <si>
-    <t>016738</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR2</t>
-  </si>
-  <si>
-    <t>016739</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR3</t>
-  </si>
-  <si>
-    <t>016004</t>
-  </si>
-  <si>
-    <t>7754807160049</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA SPARTANO #3</t>
-  </si>
-  <si>
-    <t>015938</t>
-  </si>
-  <si>
-    <t>7754807159388</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA FREE #5</t>
-  </si>
-  <si>
-    <t>016678</t>
-  </si>
-  <si>
-    <t>7754807166782</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA URBAN #5</t>
-  </si>
-  <si>
-    <t>016724</t>
-  </si>
-  <si>
-    <t>7754807167246</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA SPECTRE #5</t>
-  </si>
-  <si>
-    <t>016783</t>
-  </si>
-  <si>
-    <t>7754807167833</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA INVICTUS  #5</t>
-  </si>
-  <si>
-    <t>014323</t>
-  </si>
-  <si>
-    <t>7754807143233</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA PAISES BLANCO #5</t>
-  </si>
-  <si>
-    <t>014796</t>
-  </si>
-  <si>
-    <t>7754807147965</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA TEAM #5</t>
-  </si>
-  <si>
-    <t>011883</t>
-  </si>
-  <si>
-    <t>7754807118835</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA PAISES COLORES #5</t>
-  </si>
-  <si>
-    <t>016657</t>
-  </si>
-  <si>
-    <t>7754807166577</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA BUTTERFLY</t>
-  </si>
-  <si>
-    <t>015936</t>
-  </si>
-  <si>
-    <t>7754807159364</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA MULTICOLOR</t>
-  </si>
-  <si>
-    <t>014268</t>
-  </si>
-  <si>
-    <t>7754807142687</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA TRICOLOR</t>
-  </si>
-  <si>
-    <t>016784</t>
-  </si>
-  <si>
-    <t>7754807167840</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA FLORES2</t>
-  </si>
-  <si>
-    <t>016786</t>
-  </si>
-  <si>
-    <t>7754807167864</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA FRUTAS2</t>
-  </si>
-  <si>
-    <t>015939</t>
-  </si>
-  <si>
-    <t>7754807159395</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA FOLK</t>
-  </si>
-  <si>
-    <t>016785</t>
-  </si>
-  <si>
-    <t>7754807167857</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA MARIPOSAS</t>
-  </si>
-  <si>
-    <t>016787</t>
-  </si>
-  <si>
-    <t>7754807167871</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA URBANA</t>
-  </si>
-  <si>
-    <t>016672</t>
-  </si>
-  <si>
-    <t>7754807166720</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #3 SONRISAS</t>
-  </si>
-  <si>
-    <t>014271</t>
-  </si>
-  <si>
-    <t>7754807142717</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #3 NARANJA</t>
-  </si>
-  <si>
-    <t>014270</t>
-  </si>
-  <si>
-    <t>7754807111638</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 NARANJA</t>
-  </si>
-  <si>
-    <t>014277</t>
-  </si>
-  <si>
-    <t>7754807142779</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 NARANJA</t>
-  </si>
-  <si>
-    <t>015933</t>
-  </si>
-  <si>
-    <t>7754807159333</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 PERU</t>
-  </si>
-  <si>
-    <t>016676</t>
-  </si>
-  <si>
-    <t>7754807166768</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 GALAXY</t>
-  </si>
-  <si>
-    <t>016675</t>
-  </si>
-  <si>
-    <t>7754807166751</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 GALAXY</t>
-  </si>
-  <si>
-    <t>016752</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 LEGACY</t>
-  </si>
-  <si>
-    <t>016750</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 LEGACY</t>
-  </si>
-  <si>
-    <t>016751</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 JAM</t>
-  </si>
-  <si>
-    <t>016749</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 JAM</t>
-  </si>
-  <si>
-    <t>016764</t>
-  </si>
-  <si>
-    <t>BALONMANO GOMA #1</t>
   </si>
   <si>
     <t>016765</t>
@@ -1712,12 +1712,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1740,12 +1740,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -2196,11 +2196,11 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="2">
-        <v>2029</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2208,22 +2208,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>24</v>
       </c>
       <c r="F4" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2242,11 +2242,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="2">
-        <v>3800</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2265,11 +2265,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="2">
-        <v>606</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2288,11 +2288,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2300,22 +2300,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
       </c>
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="2">
-        <v>5320</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2323,22 +2323,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
       </c>
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="2">
-        <v>1463</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2346,22 +2346,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>24</v>
       </c>
-      <c r="F10" s="2">
-        <v>1492</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2369,22 +2369,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="2">
-        <v>179</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2392,22 +2392,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
-      <c r="F12" s="2">
-        <v>1422</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2415,22 +2415,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
       </c>
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="2">
-        <v>167</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2438,22 +2438,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
       </c>
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="2">
-        <v>182</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2461,22 +2461,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
       </c>
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2484,22 +2484,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>48</v>
       </c>
       <c r="E16">
         <v>36</v>
       </c>
-      <c r="F16" s="2">
-        <v>1012</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2507,22 +2507,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>24</v>
       </c>
       <c r="F17" s="4">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2530,22 +2530,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>36</v>
       </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>23</v>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2553,22 +2553,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="2">
-        <v>3828</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2576,22 +2576,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="2">
-        <v>3206</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2599,22 +2599,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21">
         <v>36</v>
       </c>
-      <c r="F21" s="2">
-        <v>8227</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2622,22 +2622,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="2">
-        <v>1326</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2645,22 +2645,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>48</v>
       </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2668,22 +2668,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2691,22 +2691,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2714,22 +2714,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26">
         <v>48</v>
       </c>
       <c r="F26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2737,22 +2737,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27">
         <v>36</v>
       </c>
       <c r="F27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2760,22 +2760,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28">
         <v>36</v>
       </c>
       <c r="F28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2783,22 +2783,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="2">
-        <v>3043</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,22 +2806,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>23</v>
+      <c r="F30" s="4">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2829,22 +2829,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>23</v>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2852,22 +2852,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>81</v>
       </c>
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="2">
-        <v>3498</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,22 +2875,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
         <v>82</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>83</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="2">
-        <v>2901</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,22 +2898,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="2">
-        <v>257</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2921,22 +2921,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="2">
-        <v>514</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,22 +2944,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="2">
-        <v>868</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" t="s">
         <v>91</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>93</v>
       </c>
       <c r="E37">
         <v>48</v>
       </c>
-      <c r="F37" s="2">
-        <v>7641</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,22 +2990,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
         <v>94</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>95</v>
-      </c>
-      <c r="D38" t="s">
-        <v>96</v>
       </c>
       <c r="E38">
         <v>48</v>
       </c>
-      <c r="F38" s="2">
-        <v>1351</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,22 +3013,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
         <v>97</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>98</v>
-      </c>
-      <c r="D39" t="s">
-        <v>99</v>
       </c>
       <c r="E39">
         <v>48</v>
       </c>
-      <c r="F39" s="6">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>23</v>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,22 +3036,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
         <v>100</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>102</v>
       </c>
       <c r="E40">
         <v>48</v>
       </c>
-      <c r="F40" s="6">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>23</v>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" t="s">
         <v>103</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>105</v>
       </c>
       <c r="E41">
         <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,22 +3082,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" t="s">
         <v>106</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>107</v>
-      </c>
-      <c r="D42" t="s">
-        <v>108</v>
       </c>
       <c r="E42">
         <v>48</v>
       </c>
       <c r="F42" s="4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3105,22 +3105,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" t="s">
         <v>109</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>111</v>
       </c>
       <c r="E43">
         <v>48</v>
       </c>
-      <c r="F43" s="6">
-        <v>0</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>23</v>
+      <c r="F43" s="4">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3128,22 +3128,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s">
         <v>112</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>114</v>
       </c>
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="2">
-        <v>6183</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3151,22 +3151,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
         <v>115</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>116</v>
-      </c>
-      <c r="D45" t="s">
-        <v>117</v>
       </c>
       <c r="E45">
         <v>48</v>
       </c>
-      <c r="F45" s="6">
-        <v>0</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>23</v>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3174,22 +3174,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" t="s">
         <v>118</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>119</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
       </c>
       <c r="E46">
         <v>48</v>
       </c>
-      <c r="F46" s="6">
-        <v>0</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>23</v>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3197,22 +3197,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" t="s">
         <v>121</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>122</v>
-      </c>
-      <c r="D47" t="s">
-        <v>123</v>
       </c>
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="2">
-        <v>11731</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="4">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,22 +3220,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" t="s">
         <v>124</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>125</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
       </c>
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="6">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>23</v>
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3243,22 +3243,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s">
         <v>127</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>128</v>
-      </c>
-      <c r="D49" t="s">
-        <v>129</v>
       </c>
       <c r="E49">
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3266,22 +3266,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
         <v>130</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>131</v>
-      </c>
-      <c r="D50" t="s">
-        <v>132</v>
       </c>
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="2">
-        <v>5468</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3289,22 +3289,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
         <v>133</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>134</v>
-      </c>
-      <c r="D51" t="s">
-        <v>135</v>
       </c>
       <c r="E51">
         <v>48</v>
       </c>
-      <c r="F51" s="6">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>23</v>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3312,22 +3312,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" t="s">
         <v>136</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>137</v>
-      </c>
-      <c r="D52" t="s">
-        <v>138</v>
       </c>
       <c r="E52">
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3335,22 +3335,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" t="s">
         <v>139</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>140</v>
-      </c>
-      <c r="D53" t="s">
-        <v>141</v>
       </c>
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="2">
-        <v>294</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="F53" s="4">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,22 +3358,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" t="s">
         <v>142</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>143</v>
-      </c>
-      <c r="D54" t="s">
-        <v>144</v>
       </c>
       <c r="E54">
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3381,22 +3381,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" t="s">
         <v>145</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>146</v>
-      </c>
-      <c r="D55" t="s">
-        <v>147</v>
       </c>
       <c r="E55">
         <v>36</v>
       </c>
-      <c r="F55" s="2">
-        <v>2182</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="F55" s="4">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3404,22 +3404,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" t="s">
         <v>148</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>149</v>
-      </c>
-      <c r="D56" t="s">
-        <v>150</v>
       </c>
       <c r="E56">
         <v>36</v>
       </c>
       <c r="F56" s="4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3427,22 +3427,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
         <v>151</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>152</v>
-      </c>
-      <c r="D57" t="s">
-        <v>153</v>
       </c>
       <c r="E57">
         <v>36</v>
       </c>
-      <c r="F57" s="2">
-        <v>2181</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3450,22 +3450,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" t="s">
         <v>154</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>155</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
       </c>
       <c r="E58">
         <v>36</v>
       </c>
-      <c r="F58" s="6">
-        <v>0</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>23</v>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3473,22 +3473,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" t="s">
         <v>157</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>158</v>
-      </c>
-      <c r="D59" t="s">
-        <v>159</v>
       </c>
       <c r="E59">
         <v>36</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>23</v>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3496,22 +3496,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E60">
         <v>36</v>
       </c>
-      <c r="F60" s="2">
-        <v>1351</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3519,22 +3519,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E61">
         <v>36</v>
       </c>
-      <c r="F61" s="6">
-        <v>0</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>23</v>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,22 +3542,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E62">
         <v>36</v>
       </c>
-      <c r="F62" s="2">
-        <v>915</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3565,22 +3565,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E63">
         <v>36</v>
       </c>
-      <c r="F63" s="2">
-        <v>797</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3588,22 +3588,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="2">
-        <v>418</v>
-      </c>
-      <c r="G64" s="3" t="s">
+      <c r="F64" s="6">
         <v>10</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3622,11 +3622,11 @@
       <c r="E65">
         <v>48</v>
       </c>
-      <c r="F65" s="2">
-        <v>1218</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3645,11 +3645,11 @@
       <c r="E66">
         <v>60</v>
       </c>
-      <c r="F66" s="2">
-        <v>5188</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3668,11 +3668,11 @@
       <c r="E67">
         <v>60</v>
       </c>
-      <c r="F67" s="2">
-        <v>1224</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3691,11 +3691,11 @@
       <c r="E68">
         <v>60</v>
       </c>
-      <c r="F68" s="2">
-        <v>2119</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3714,11 +3714,11 @@
       <c r="E69">
         <v>60</v>
       </c>
-      <c r="F69" s="2">
-        <v>1118</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>10</v>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3737,11 +3737,11 @@
       <c r="E70">
         <v>60</v>
       </c>
-      <c r="F70" s="2">
-        <v>4179</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3760,11 +3760,11 @@
       <c r="E71">
         <v>60</v>
       </c>
-      <c r="F71" s="2">
-        <v>5084</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3783,11 +3783,11 @@
       <c r="E72">
         <v>60</v>
       </c>
-      <c r="F72" s="6">
-        <v>0</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>23</v>
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3806,11 +3806,11 @@
       <c r="E73">
         <v>60</v>
       </c>
-      <c r="F73" s="2">
-        <v>3152</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3829,11 +3829,11 @@
       <c r="E74">
         <v>60</v>
       </c>
-      <c r="F74" s="2">
-        <v>1203</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3852,11 +3852,11 @@
       <c r="E75">
         <v>60</v>
       </c>
-      <c r="F75" s="2">
-        <v>4369</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3875,11 +3875,11 @@
       <c r="E76">
         <v>60</v>
       </c>
-      <c r="F76" s="2">
-        <v>8491</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3898,11 +3898,11 @@
       <c r="E77">
         <v>60</v>
       </c>
-      <c r="F77" s="2">
-        <v>3977</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3921,11 +3921,11 @@
       <c r="E78">
         <v>60</v>
       </c>
-      <c r="F78" s="2">
-        <v>6449</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3944,11 +3944,11 @@
       <c r="E79">
         <v>60</v>
       </c>
-      <c r="F79" s="2">
-        <v>5172</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3968,10 +3968,10 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3991,10 +3991,10 @@
         <v>60</v>
       </c>
       <c r="F81" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="2">
-        <v>938</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>10</v>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4036,11 +4036,11 @@
       <c r="E83">
         <v>60</v>
       </c>
-      <c r="F83" s="2">
-        <v>1013</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4059,11 +4059,11 @@
       <c r="E84">
         <v>60</v>
       </c>
-      <c r="F84" s="6">
-        <v>0</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>23</v>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4083,10 +4083,10 @@
         <v>60</v>
       </c>
       <c r="F85" s="4">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4105,11 +4105,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="2">
-        <v>333</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4128,11 +4128,11 @@
       <c r="E87">
         <v>60</v>
       </c>
-      <c r="F87" s="2">
-        <v>1522</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>23</v>
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,11 +4174,11 @@
       <c r="E89">
         <v>60</v>
       </c>
-      <c r="F89" s="6">
-        <v>0</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>23</v>
+      <c r="F89" s="4">
+        <v>0</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,11 +4197,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="2">
-        <v>727</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="F90" s="4">
+        <v>0</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="2">
-        <v>1433</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4243,11 +4243,11 @@
       <c r="E92">
         <v>60</v>
       </c>
-      <c r="F92" s="2">
-        <v>1349</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="F92" s="4">
+        <v>0</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="2">
-        <v>1219</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>10</v>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="2">
-        <v>1374</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>10</v>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4313,10 +4313,10 @@
         <v>60</v>
       </c>
       <c r="F95" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4335,11 +4335,11 @@
       <c r="E96">
         <v>60</v>
       </c>
-      <c r="F96" s="2">
-        <v>2455</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="F96" s="4">
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4358,11 +4358,11 @@
       <c r="E97">
         <v>60</v>
       </c>
-      <c r="F97" s="2">
-        <v>5025</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="F97" s="4">
+        <v>0</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4381,11 +4381,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="2">
-        <v>3401</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4404,11 +4404,11 @@
       <c r="E99">
         <v>60</v>
       </c>
-      <c r="F99" s="2">
-        <v>3818</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="F99" s="4">
+        <v>0</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4427,11 +4427,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="2">
-        <v>1495</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>10</v>
+      <c r="F100" s="4">
+        <v>0</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4450,11 +4450,11 @@
       <c r="E101">
         <v>60</v>
       </c>
-      <c r="F101" s="2">
-        <v>5801</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>10</v>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -4473,11 +4473,11 @@
       <c r="E102">
         <v>60</v>
       </c>
-      <c r="F102" s="2">
-        <v>3252</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>10</v>
+      <c r="F102" s="4">
+        <v>0</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4496,11 +4496,11 @@
       <c r="E103">
         <v>60</v>
       </c>
-      <c r="F103" s="2">
-        <v>1816</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>10</v>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4519,11 +4519,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="2">
-        <v>368</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4542,11 +4542,11 @@
       <c r="E105">
         <v>60</v>
       </c>
-      <c r="F105" s="6">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>23</v>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="2">
-        <v>1386</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4588,11 +4588,11 @@
       <c r="E107">
         <v>60</v>
       </c>
-      <c r="F107" s="2">
-        <v>5481</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4611,11 +4611,11 @@
       <c r="E108">
         <v>60</v>
       </c>
-      <c r="F108" s="2">
-        <v>2969</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4634,11 +4634,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="2">
-        <v>1644</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4657,11 +4657,11 @@
       <c r="E110">
         <v>60</v>
       </c>
-      <c r="F110" s="2">
-        <v>1889</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4680,11 +4680,11 @@
       <c r="E111">
         <v>60</v>
       </c>
-      <c r="F111" s="2">
-        <v>6114</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4703,11 +4703,11 @@
       <c r="E112">
         <v>60</v>
       </c>
-      <c r="F112" s="2">
-        <v>7067</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4726,11 +4726,11 @@
       <c r="E113">
         <v>60</v>
       </c>
-      <c r="F113" s="2">
-        <v>6549</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4749,11 +4749,11 @@
       <c r="E114">
         <v>60</v>
       </c>
-      <c r="F114" s="2">
-        <v>10968</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4772,11 +4772,11 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115" s="2">
-        <v>239</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4795,11 +4795,11 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" s="2">
-        <v>85</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4818,11 +4818,11 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117" s="2">
-        <v>273</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4841,11 +4841,11 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="2">
-        <v>272</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>10</v>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -4864,11 +4864,11 @@
       <c r="E119">
         <v>12</v>
       </c>
-      <c r="F119" s="6">
-        <v>0</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>23</v>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,11 +4887,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="2">
-        <v>262</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,11 +4910,11 @@
       <c r="E121">
         <v>36</v>
       </c>
-      <c r="F121" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>23</v>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4933,11 +4933,11 @@
       <c r="E122">
         <v>12</v>
       </c>
-      <c r="F122" s="2">
-        <v>2925</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>36</v>
       </c>
       <c r="F123" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4979,11 +4979,11 @@
       <c r="E124">
         <v>12</v>
       </c>
-      <c r="F124" s="2">
-        <v>2460</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>10</v>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5002,11 +5002,11 @@
       <c r="E125">
         <v>36</v>
       </c>
-      <c r="F125" s="2">
-        <v>969</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="F125" s="4">
+        <v>0</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="2">
-        <v>2188</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4">
+        <v>0</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5049,10 +5049,10 @@
         <v>120</v>
       </c>
       <c r="F127" s="4">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,10 +5072,10 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5094,11 +5094,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="2">
-        <v>1061</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="F129" s="4">
+        <v>0</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="2">
-        <v>884</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="F130" s="4">
+        <v>0</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5141,10 +5141,10 @@
         <v>120</v>
       </c>
       <c r="F131" s="4">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5164,10 +5164,10 @@
         <v>120</v>
       </c>
       <c r="F132" s="4">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5186,11 +5186,11 @@
       <c r="E133">
         <v>120</v>
       </c>
-      <c r="F133" s="2">
-        <v>6592</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="F133" s="4">
+        <v>0</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5209,11 +5209,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="2">
-        <v>1017</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>10</v>
+      <c r="F134" s="4">
+        <v>0</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5233,10 +5233,10 @@
         <v>120</v>
       </c>
       <c r="F135" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5255,11 +5255,11 @@
       <c r="E136">
         <v>120</v>
       </c>
-      <c r="F136" s="2">
-        <v>4015</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>10</v>
+      <c r="F136" s="4">
+        <v>0</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5278,11 +5278,11 @@
       <c r="E137">
         <v>120</v>
       </c>
-      <c r="F137" s="2">
-        <v>1904</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>10</v>
+      <c r="F137" s="4">
+        <v>0</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5302,10 +5302,10 @@
         <v>120</v>
       </c>
       <c r="F138" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,11 +5324,11 @@
       <c r="E139">
         <v>120</v>
       </c>
-      <c r="F139" s="2">
-        <v>4463</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="F139" s="4">
+        <v>0</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,11 +5347,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="2">
-        <v>870</v>
-      </c>
-      <c r="G140" s="3" t="s">
-        <v>10</v>
+      <c r="F140" s="4">
+        <v>0</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,11 +5370,11 @@
       <c r="E141">
         <v>120</v>
       </c>
-      <c r="F141" s="2">
-        <v>4091</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="F141" s="4">
+        <v>0</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5393,11 +5393,11 @@
       <c r="E142">
         <v>120</v>
       </c>
-      <c r="F142" s="2">
-        <v>3358</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="F142" s="4">
+        <v>0</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5417,10 +5417,10 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,11 +5439,11 @@
       <c r="E144">
         <v>120</v>
       </c>
-      <c r="F144" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>23</v>
+      <c r="F144" s="4">
+        <v>0</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5463,10 +5463,10 @@
         <v>120</v>
       </c>
       <c r="F145" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="2">
-        <v>683</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="4">
+        <v>0</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,11 +5508,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="2">
-        <v>1964</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="F147" s="4">
+        <v>0</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5532,10 +5532,10 @@
         <v>120</v>
       </c>
       <c r="F148" s="4">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5555,10 +5555,10 @@
         <v>120</v>
       </c>
       <c r="F149" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5578,10 +5578,10 @@
         <v>120</v>
       </c>
       <c r="F150" s="4">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -5600,11 +5600,11 @@
       <c r="E151">
         <v>120</v>
       </c>
-      <c r="F151" s="2">
-        <v>1995</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>10</v>
+      <c r="F151" s="4">
+        <v>0</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -5624,10 +5624,10 @@
         <v>120</v>
       </c>
       <c r="F152" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,11 +5646,11 @@
       <c r="E153">
         <v>120</v>
       </c>
-      <c r="F153" s="6">
-        <v>0</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>23</v>
+      <c r="F153" s="4">
+        <v>0</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5669,11 +5669,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
-        <v>3265</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="F154" s="4">
+        <v>0</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5692,11 +5692,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="2">
-        <v>908</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>10</v>
+      <c r="F155" s="4">
+        <v>0</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5716,10 +5716,10 @@
         <v>120</v>
       </c>
       <c r="F156" s="4">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5738,11 +5738,11 @@
       <c r="E157">
         <v>120</v>
       </c>
-      <c r="F157" s="2">
-        <v>3114</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="F157" s="4">
+        <v>0</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="2">
-        <v>1101</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="4">
+        <v>0</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5784,11 +5784,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
-        <v>3978</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="4">
+        <v>0</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5807,11 +5807,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="6">
-        <v>0</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>23</v>
+      <c r="F160" s="4">
+        <v>0</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="2">
-        <v>1914</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="F161" s="4">
+        <v>0</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5853,11 +5853,11 @@
       <c r="E162">
         <v>120</v>
       </c>
-      <c r="F162" s="2">
-        <v>4636</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="F162" s="4">
+        <v>0</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5876,11 +5876,11 @@
       <c r="E163">
         <v>120</v>
       </c>
-      <c r="F163" s="2">
-        <v>4562</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="F163" s="4">
+        <v>0</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5900,10 +5900,10 @@
         <v>120</v>
       </c>
       <c r="F164" s="4">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5922,11 +5922,11 @@
       <c r="E165">
         <v>120</v>
       </c>
-      <c r="F165" s="2">
-        <v>1260</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="F165" s="4">
+        <v>0</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5945,11 +5945,11 @@
       <c r="E166">
         <v>120</v>
       </c>
-      <c r="F166" s="2">
-        <v>3735</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="F166" s="4">
+        <v>0</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5968,11 +5968,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="2">
-        <v>764</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="F167" s="4">
+        <v>0</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,10 +5992,10 @@
         <v>120</v>
       </c>
       <c r="F168" s="4">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6014,11 +6014,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="2">
-        <v>703</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="F169" s="4">
+        <v>0</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6038,10 +6038,10 @@
         <v>120</v>
       </c>
       <c r="F170" s="4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6060,11 +6060,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="2">
-        <v>7654</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>10</v>
+      <c r="F171" s="4">
+        <v>0</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6083,11 +6083,11 @@
       <c r="E172">
         <v>120</v>
       </c>
-      <c r="F172" s="2">
-        <v>2029</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="F172" s="4">
+        <v>0</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6106,11 +6106,11 @@
       <c r="E173">
         <v>1</v>
       </c>
-      <c r="F173" s="2">
-        <v>231</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="F173" s="4">
+        <v>0</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6129,11 +6129,11 @@
       <c r="E174">
         <v>1</v>
       </c>
-      <c r="F174" s="2">
-        <v>135</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="F174" s="4">
+        <v>0</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6153,10 +6153,10 @@
         <v>12</v>
       </c>
       <c r="F175" s="4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6175,11 +6175,11 @@
       <c r="E176">
         <v>12</v>
       </c>
-      <c r="F176" s="6">
-        <v>0</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>23</v>
+      <c r="F176" s="4">
+        <v>0</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6198,11 +6198,11 @@
       <c r="E177">
         <v>12</v>
       </c>
-      <c r="F177" s="6">
-        <v>0</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>23</v>
+      <c r="F177" s="4">
+        <v>0</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6221,11 +6221,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="2">
-        <v>163</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>10</v>
+      <c r="F178" s="4">
+        <v>0</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6245,10 +6245,10 @@
         <v>12</v>
       </c>
       <c r="F179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6267,11 +6267,11 @@
       <c r="E180">
         <v>12</v>
       </c>
-      <c r="F180" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>23</v>
+      <c r="F180" s="4">
+        <v>0</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6290,11 +6290,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="6">
-        <v>0</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>23</v>
+      <c r="F181" s="4">
+        <v>0</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6313,11 +6313,11 @@
       <c r="E182">
         <v>12</v>
       </c>
-      <c r="F182" s="2">
-        <v>211</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="F182" s="4">
+        <v>0</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6337,10 +6337,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -6360,10 +6360,10 @@
         <v>12</v>
       </c>
       <c r="F184" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -6382,11 +6382,11 @@
       <c r="E185">
         <v>12</v>
       </c>
-      <c r="F185" s="2">
-        <v>3022</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>10</v>
+      <c r="F185" s="4">
+        <v>0</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="2">
-        <v>214</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="F186" s="4">
+        <v>0</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="2">
-        <v>157</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="4">
+        <v>0</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6451,11 +6451,11 @@
       <c r="E188">
         <v>12</v>
       </c>
-      <c r="F188" s="2">
-        <v>654</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="F188" s="4">
+        <v>0</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6475,10 +6475,10 @@
         <v>18</v>
       </c>
       <c r="F189" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6497,11 +6497,11 @@
       <c r="E190">
         <v>12</v>
       </c>
-      <c r="F190" s="2">
-        <v>1156</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>10</v>
+      <c r="F190" s="4">
+        <v>0</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -6520,11 +6520,11 @@
       <c r="E191">
         <v>18</v>
       </c>
-      <c r="F191" s="2">
-        <v>1865</v>
-      </c>
-      <c r="G191" s="3" t="s">
-        <v>10</v>
+      <c r="F191" s="4">
+        <v>0</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -6543,11 +6543,11 @@
       <c r="E192">
         <v>12</v>
       </c>
-      <c r="F192" s="2">
-        <v>1913</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>10</v>
+      <c r="F192" s="4">
+        <v>0</v>
+      </c>
+      <c r="G192" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -6566,11 +6566,11 @@
       <c r="E193">
         <v>400</v>
       </c>
-      <c r="F193" s="2">
-        <v>75750</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>10</v>
+      <c r="F193" s="4">
+        <v>0</v>
+      </c>
+      <c r="G193" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -6589,11 +6589,11 @@
       <c r="E194">
         <v>400</v>
       </c>
-      <c r="F194" s="2">
-        <v>70965</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>10</v>
+      <c r="F194" s="4">
+        <v>0</v>
+      </c>
+      <c r="G194" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -6612,11 +6612,11 @@
       <c r="E195">
         <v>120</v>
       </c>
-      <c r="F195" s="2">
-        <v>3607</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>10</v>
+      <c r="F195" s="4">
+        <v>0</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="2">
-        <v>1804</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>10</v>
+      <c r="F196" s="4">
+        <v>0</v>
+      </c>
+      <c r="G196" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6658,11 +6658,11 @@
       <c r="E197">
         <v>120</v>
       </c>
-      <c r="F197" s="2">
-        <v>8964</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>10</v>
+      <c r="F197" s="4">
+        <v>0</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="6">
-        <v>0</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>23</v>
+      <c r="F198" s="4">
+        <v>0</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -6704,11 +6704,11 @@
       <c r="E199">
         <v>120</v>
       </c>
-      <c r="F199" s="2">
-        <v>8040</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>10</v>
+      <c r="F199" s="4">
+        <v>0</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -52,36 +52,39 @@
     <t>FUTBOL CUERO TERMOSELLADA PRECISION #5</t>
   </si>
   <si>
+    <t>016726</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
+  </si>
+  <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>016727</t>
+  </si>
+  <si>
+    <t>7754807167277</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
+  </si>
+  <si>
+    <t>016756</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
+  </si>
+  <si>
+    <t>016755</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
+  </si>
+  <si>
     <t>✗ AGOTADO</t>
   </si>
   <si>
-    <t>016726</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
-  </si>
-  <si>
-    <t>016727</t>
-  </si>
-  <si>
-    <t>7754807167277</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
-  </si>
-  <si>
-    <t>016756</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
-  </si>
-  <si>
-    <t>016755</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
-  </si>
-  <si>
     <t>016757</t>
   </si>
   <si>
@@ -518,9 +521,6 @@
   </si>
   <si>
     <t>BALONMANO GOMA #1</t>
-  </si>
-  <si>
-    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>016765</t>
@@ -1712,12 +1712,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1740,12 +1740,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -2196,11 +2196,11 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>13</v>
+      <c r="F3" s="2">
+        <v>2029</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2208,22 +2208,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>24</v>
       </c>
       <c r="F4" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2242,11 +2242,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>13</v>
+      <c r="F5" s="2">
+        <v>3800</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2265,11 +2265,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
+      <c r="F6" s="2">
+        <v>606</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2288,11 +2288,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>13</v>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2300,22 +2300,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>13</v>
+      <c r="F8" s="2">
+        <v>5320</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2323,22 +2323,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>13</v>
+      <c r="F9" s="2">
+        <v>1463</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2346,22 +2346,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>24</v>
       </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>13</v>
+      <c r="F10" s="2">
+        <v>1492</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2369,22 +2369,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>13</v>
+      <c r="F11" s="2">
+        <v>179</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2392,22 +2392,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>13</v>
+      <c r="F12" s="2">
+        <v>1422</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2415,22 +2415,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>13</v>
+      <c r="F13" s="2">
+        <v>167</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2438,22 +2438,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>13</v>
+      <c r="F14" s="2">
+        <v>182</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2461,22 +2461,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="6">
         <v>0</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>13</v>
+      <c r="G15" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2484,22 +2484,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16">
         <v>36</v>
       </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>13</v>
+      <c r="F16" s="2">
+        <v>1012</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2507,22 +2507,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>24</v>
       </c>
       <c r="F17" s="4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2530,22 +2530,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>36</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="6">
         <v>0</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>13</v>
+      <c r="G18" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2553,22 +2553,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>13</v>
+      <c r="F19" s="2">
+        <v>3828</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2576,22 +2576,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>13</v>
+      <c r="F20" s="2">
+        <v>3206</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2599,22 +2599,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>36</v>
       </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>13</v>
+      <c r="F21" s="2">
+        <v>8227</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2622,22 +2622,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="4">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>13</v>
+      <c r="F22" s="2">
+        <v>1326</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2645,22 +2645,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23">
         <v>48</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="6">
         <v>0</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>13</v>
+      <c r="G23" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2668,22 +2668,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="6">
         <v>0</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>13</v>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2691,22 +2691,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>13</v>
+      <c r="G25" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2714,22 +2714,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26">
         <v>48</v>
       </c>
       <c r="F26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2737,22 +2737,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>36</v>
       </c>
       <c r="F27" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2760,22 +2760,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28">
         <v>36</v>
       </c>
       <c r="F28" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2783,22 +2783,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>13</v>
+      <c r="F29" s="2">
+        <v>3043</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,22 +2806,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="6">
         <v>0</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>13</v>
+      <c r="G30" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2829,22 +2829,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="6">
         <v>0</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>13</v>
+      <c r="G31" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2852,22 +2852,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="4">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>13</v>
+      <c r="F32" s="2">
+        <v>3498</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,22 +2875,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="4">
-        <v>0</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>13</v>
+      <c r="F33" s="2">
+        <v>2901</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,22 +2898,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="4">
-        <v>0</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>13</v>
+      <c r="F34" s="2">
+        <v>257</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2921,22 +2921,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>13</v>
+      <c r="F35" s="2">
+        <v>514</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,22 +2944,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="4">
-        <v>0</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>13</v>
+      <c r="F36" s="2">
+        <v>868</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E37">
         <v>48</v>
       </c>
-      <c r="F37" s="4">
-        <v>0</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>13</v>
+      <c r="F37" s="2">
+        <v>7641</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,22 +2990,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E38">
         <v>48</v>
       </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>13</v>
+      <c r="F38" s="2">
+        <v>1351</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,22 +3013,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39">
         <v>48</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="6">
         <v>0</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>13</v>
+      <c r="G39" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,22 +3036,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E40">
         <v>48</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="6">
         <v>0</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>13</v>
+      <c r="G40" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E41">
         <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,22 +3082,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E42">
         <v>48</v>
       </c>
       <c r="F42" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3105,22 +3105,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E43">
         <v>48</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="6">
         <v>0</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>13</v>
+      <c r="G43" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3128,22 +3128,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="4">
-        <v>0</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>13</v>
+      <c r="F44" s="2">
+        <v>6183</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3151,22 +3151,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E45">
         <v>48</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="6">
         <v>0</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>13</v>
+      <c r="G45" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3174,22 +3174,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E46">
         <v>48</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="6">
         <v>0</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>13</v>
+      <c r="G46" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3197,22 +3197,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="4">
-        <v>0</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>13</v>
+      <c r="F47" s="2">
+        <v>11731</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,22 +3220,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="6">
         <v>0</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>13</v>
+      <c r="G48" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3243,22 +3243,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E49">
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3266,22 +3266,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="4">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>13</v>
+      <c r="F50" s="2">
+        <v>5468</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3289,22 +3289,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E51">
         <v>48</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="6">
         <v>0</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>13</v>
+      <c r="G51" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3312,22 +3312,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E52">
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3335,22 +3335,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="4">
-        <v>0</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>13</v>
+      <c r="F53" s="2">
+        <v>294</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,22 +3358,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E54">
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3381,22 +3381,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E55">
         <v>36</v>
       </c>
-      <c r="F55" s="4">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>13</v>
+      <c r="F55" s="2">
+        <v>2182</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3404,22 +3404,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E56">
         <v>36</v>
       </c>
       <c r="F56" s="4">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3427,22 +3427,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E57">
         <v>36</v>
       </c>
-      <c r="F57" s="4">
-        <v>0</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>13</v>
+      <c r="F57" s="2">
+        <v>2181</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3450,22 +3450,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E58">
         <v>36</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="6">
         <v>0</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>13</v>
+      <c r="G58" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3473,22 +3473,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E59">
         <v>36</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>13</v>
+      <c r="G59" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3496,22 +3496,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E60">
         <v>36</v>
       </c>
-      <c r="F60" s="4">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>13</v>
+      <c r="F60" s="2">
+        <v>1351</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3519,22 +3519,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E61">
         <v>36</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="6">
         <v>0</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>13</v>
+      <c r="G61" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,22 +3542,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E62">
         <v>36</v>
       </c>
-      <c r="F62" s="4">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>13</v>
+      <c r="F62" s="2">
+        <v>915</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3565,22 +3565,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E63">
         <v>36</v>
       </c>
-      <c r="F63" s="4">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>13</v>
+      <c r="F63" s="2">
+        <v>797</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3588,22 +3588,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="6">
-        <v>10</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>169</v>
+      <c r="F64" s="2">
+        <v>418</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3622,11 +3622,11 @@
       <c r="E65">
         <v>48</v>
       </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>13</v>
+      <c r="F65" s="2">
+        <v>1218</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3645,11 +3645,11 @@
       <c r="E66">
         <v>60</v>
       </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>13</v>
+      <c r="F66" s="2">
+        <v>5188</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3668,11 +3668,11 @@
       <c r="E67">
         <v>60</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>13</v>
+      <c r="F67" s="2">
+        <v>1224</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3691,11 +3691,11 @@
       <c r="E68">
         <v>60</v>
       </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>13</v>
+      <c r="F68" s="2">
+        <v>2119</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3714,11 +3714,11 @@
       <c r="E69">
         <v>60</v>
       </c>
-      <c r="F69" s="4">
-        <v>0</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>13</v>
+      <c r="F69" s="2">
+        <v>1118</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3737,11 +3737,11 @@
       <c r="E70">
         <v>60</v>
       </c>
-      <c r="F70" s="4">
-        <v>0</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>13</v>
+      <c r="F70" s="2">
+        <v>4179</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3760,11 +3760,11 @@
       <c r="E71">
         <v>60</v>
       </c>
-      <c r="F71" s="4">
-        <v>0</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>13</v>
+      <c r="F71" s="2">
+        <v>5084</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3783,11 +3783,11 @@
       <c r="E72">
         <v>60</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="6">
         <v>0</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>13</v>
+      <c r="G72" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3806,11 +3806,11 @@
       <c r="E73">
         <v>60</v>
       </c>
-      <c r="F73" s="4">
-        <v>0</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>13</v>
+      <c r="F73" s="2">
+        <v>3152</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3829,11 +3829,11 @@
       <c r="E74">
         <v>60</v>
       </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>13</v>
+      <c r="F74" s="2">
+        <v>1203</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3852,11 +3852,11 @@
       <c r="E75">
         <v>60</v>
       </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>13</v>
+      <c r="F75" s="2">
+        <v>4369</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3875,11 +3875,11 @@
       <c r="E76">
         <v>60</v>
       </c>
-      <c r="F76" s="4">
-        <v>0</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>13</v>
+      <c r="F76" s="2">
+        <v>8491</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3898,11 +3898,11 @@
       <c r="E77">
         <v>60</v>
       </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>13</v>
+      <c r="F77" s="2">
+        <v>3977</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3921,11 +3921,11 @@
       <c r="E78">
         <v>60</v>
       </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>13</v>
+      <c r="F78" s="2">
+        <v>6449</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3944,11 +3944,11 @@
       <c r="E79">
         <v>60</v>
       </c>
-      <c r="F79" s="4">
-        <v>0</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>13</v>
+      <c r="F79" s="2">
+        <v>5172</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3968,10 +3968,10 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3991,10 +3991,10 @@
         <v>60</v>
       </c>
       <c r="F81" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="4">
-        <v>0</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>13</v>
+      <c r="F82" s="2">
+        <v>938</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4036,11 +4036,11 @@
       <c r="E83">
         <v>60</v>
       </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>13</v>
+      <c r="F83" s="2">
+        <v>1013</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4059,11 +4059,11 @@
       <c r="E84">
         <v>60</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="6">
         <v>0</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>13</v>
+      <c r="G84" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4083,10 +4083,10 @@
         <v>60</v>
       </c>
       <c r="F85" s="4">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4105,11 +4105,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="4">
-        <v>0</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>13</v>
+      <c r="F86" s="2">
+        <v>333</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4128,11 +4128,11 @@
       <c r="E87">
         <v>60</v>
       </c>
-      <c r="F87" s="4">
-        <v>0</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>13</v>
+      <c r="F87" s="2">
+        <v>1522</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="6">
         <v>0</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>13</v>
+      <c r="G88" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,11 +4174,11 @@
       <c r="E89">
         <v>60</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="6">
         <v>0</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>13</v>
+      <c r="G89" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,11 +4197,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="4">
-        <v>0</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>13</v>
+      <c r="F90" s="2">
+        <v>727</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="4">
-        <v>0</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>13</v>
+      <c r="F91" s="2">
+        <v>1433</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4243,11 +4243,11 @@
       <c r="E92">
         <v>60</v>
       </c>
-      <c r="F92" s="4">
-        <v>0</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>13</v>
+      <c r="F92" s="2">
+        <v>1349</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="4">
-        <v>0</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>13</v>
+      <c r="F93" s="2">
+        <v>1219</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="4">
-        <v>0</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>13</v>
+      <c r="F94" s="2">
+        <v>1374</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4313,10 +4313,10 @@
         <v>60</v>
       </c>
       <c r="F95" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4335,11 +4335,11 @@
       <c r="E96">
         <v>60</v>
       </c>
-      <c r="F96" s="4">
-        <v>0</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>13</v>
+      <c r="F96" s="2">
+        <v>2455</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4358,11 +4358,11 @@
       <c r="E97">
         <v>60</v>
       </c>
-      <c r="F97" s="4">
-        <v>0</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>13</v>
+      <c r="F97" s="2">
+        <v>5025</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4381,11 +4381,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="4">
-        <v>0</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>13</v>
+      <c r="F98" s="2">
+        <v>3401</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4404,11 +4404,11 @@
       <c r="E99">
         <v>60</v>
       </c>
-      <c r="F99" s="4">
-        <v>0</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>13</v>
+      <c r="F99" s="2">
+        <v>3818</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4427,11 +4427,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="4">
-        <v>0</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>13</v>
+      <c r="F100" s="2">
+        <v>1495</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4450,11 +4450,11 @@
       <c r="E101">
         <v>60</v>
       </c>
-      <c r="F101" s="4">
-        <v>0</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>13</v>
+      <c r="F101" s="2">
+        <v>5801</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -4473,11 +4473,11 @@
       <c r="E102">
         <v>60</v>
       </c>
-      <c r="F102" s="4">
-        <v>0</v>
-      </c>
-      <c r="G102" s="5" t="s">
-        <v>13</v>
+      <c r="F102" s="2">
+        <v>3252</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4496,11 +4496,11 @@
       <c r="E103">
         <v>60</v>
       </c>
-      <c r="F103" s="4">
-        <v>0</v>
-      </c>
-      <c r="G103" s="5" t="s">
-        <v>13</v>
+      <c r="F103" s="2">
+        <v>1816</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4519,11 +4519,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="4">
-        <v>0</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>13</v>
+      <c r="F104" s="2">
+        <v>368</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4542,11 +4542,11 @@
       <c r="E105">
         <v>60</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="6">
         <v>0</v>
       </c>
-      <c r="G105" s="5" t="s">
-        <v>13</v>
+      <c r="G105" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="4">
-        <v>0</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>13</v>
+      <c r="F106" s="2">
+        <v>1386</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4588,11 +4588,11 @@
       <c r="E107">
         <v>60</v>
       </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>13</v>
+      <c r="F107" s="2">
+        <v>5481</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4611,11 +4611,11 @@
       <c r="E108">
         <v>60</v>
       </c>
-      <c r="F108" s="4">
-        <v>0</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>13</v>
+      <c r="F108" s="2">
+        <v>2969</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4634,11 +4634,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="4">
-        <v>0</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>13</v>
+      <c r="F109" s="2">
+        <v>1644</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4657,11 +4657,11 @@
       <c r="E110">
         <v>60</v>
       </c>
-      <c r="F110" s="4">
-        <v>0</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>13</v>
+      <c r="F110" s="2">
+        <v>1889</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4680,11 +4680,11 @@
       <c r="E111">
         <v>60</v>
       </c>
-      <c r="F111" s="4">
-        <v>0</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>13</v>
+      <c r="F111" s="2">
+        <v>6114</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4703,11 +4703,11 @@
       <c r="E112">
         <v>60</v>
       </c>
-      <c r="F112" s="4">
-        <v>0</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>13</v>
+      <c r="F112" s="2">
+        <v>7067</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4726,11 +4726,11 @@
       <c r="E113">
         <v>60</v>
       </c>
-      <c r="F113" s="4">
-        <v>0</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>13</v>
+      <c r="F113" s="2">
+        <v>6549</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4749,11 +4749,11 @@
       <c r="E114">
         <v>60</v>
       </c>
-      <c r="F114" s="4">
-        <v>0</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>13</v>
+      <c r="F114" s="2">
+        <v>10968</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4772,11 +4772,11 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115" s="4">
-        <v>0</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>13</v>
+      <c r="F115" s="2">
+        <v>239</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4795,11 +4795,11 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" s="4">
-        <v>0</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>13</v>
+      <c r="F116" s="2">
+        <v>85</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4818,11 +4818,11 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117" s="4">
-        <v>0</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>13</v>
+      <c r="F117" s="2">
+        <v>273</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4841,11 +4841,11 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="4">
-        <v>0</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>13</v>
+      <c r="F118" s="2">
+        <v>272</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -4864,11 +4864,11 @@
       <c r="E119">
         <v>12</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="6">
         <v>0</v>
       </c>
-      <c r="G119" s="5" t="s">
-        <v>13</v>
+      <c r="G119" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,11 +4887,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="4">
-        <v>0</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>13</v>
+      <c r="F120" s="2">
+        <v>202</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,11 +4910,11 @@
       <c r="E121">
         <v>36</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="6">
         <v>0</v>
       </c>
-      <c r="G121" s="5" t="s">
-        <v>13</v>
+      <c r="G121" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4933,11 +4933,11 @@
       <c r="E122">
         <v>12</v>
       </c>
-      <c r="F122" s="4">
-        <v>0</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>13</v>
+      <c r="F122" s="2">
+        <v>2925</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>36</v>
       </c>
       <c r="F123" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4979,11 +4979,11 @@
       <c r="E124">
         <v>12</v>
       </c>
-      <c r="F124" s="4">
-        <v>0</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>13</v>
+      <c r="F124" s="2">
+        <v>2460</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5002,11 +5002,11 @@
       <c r="E125">
         <v>36</v>
       </c>
-      <c r="F125" s="4">
-        <v>0</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>13</v>
+      <c r="F125" s="2">
+        <v>969</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="4">
-        <v>0</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>13</v>
+      <c r="F126" s="2">
+        <v>2188</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5049,10 +5049,10 @@
         <v>120</v>
       </c>
       <c r="F127" s="4">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,10 +5072,10 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5094,11 +5094,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="4">
-        <v>0</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>13</v>
+      <c r="F129" s="2">
+        <v>1061</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="4">
-        <v>0</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>13</v>
+      <c r="F130" s="2">
+        <v>884</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5141,10 +5141,10 @@
         <v>120</v>
       </c>
       <c r="F131" s="4">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5164,10 +5164,10 @@
         <v>120</v>
       </c>
       <c r="F132" s="4">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5186,11 +5186,11 @@
       <c r="E133">
         <v>120</v>
       </c>
-      <c r="F133" s="4">
-        <v>0</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>13</v>
+      <c r="F133" s="2">
+        <v>6592</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5209,11 +5209,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="4">
-        <v>0</v>
-      </c>
-      <c r="G134" s="5" t="s">
-        <v>13</v>
+      <c r="F134" s="2">
+        <v>1017</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5233,10 +5233,10 @@
         <v>120</v>
       </c>
       <c r="F135" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5255,11 +5255,11 @@
       <c r="E136">
         <v>120</v>
       </c>
-      <c r="F136" s="4">
-        <v>0</v>
-      </c>
-      <c r="G136" s="5" t="s">
-        <v>13</v>
+      <c r="F136" s="2">
+        <v>4015</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5278,11 +5278,11 @@
       <c r="E137">
         <v>120</v>
       </c>
-      <c r="F137" s="4">
-        <v>0</v>
-      </c>
-      <c r="G137" s="5" t="s">
-        <v>13</v>
+      <c r="F137" s="2">
+        <v>1904</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5302,10 +5302,10 @@
         <v>120</v>
       </c>
       <c r="F138" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,11 +5324,11 @@
       <c r="E139">
         <v>120</v>
       </c>
-      <c r="F139" s="4">
-        <v>0</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>13</v>
+      <c r="F139" s="2">
+        <v>4463</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,11 +5347,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="4">
-        <v>0</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>13</v>
+      <c r="F140" s="2">
+        <v>870</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,11 +5370,11 @@
       <c r="E141">
         <v>120</v>
       </c>
-      <c r="F141" s="4">
-        <v>0</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>13</v>
+      <c r="F141" s="2">
+        <v>4091</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5393,11 +5393,11 @@
       <c r="E142">
         <v>120</v>
       </c>
-      <c r="F142" s="4">
-        <v>0</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>13</v>
+      <c r="F142" s="2">
+        <v>3358</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5417,10 +5417,10 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,11 +5439,11 @@
       <c r="E144">
         <v>120</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="5" t="s">
-        <v>13</v>
+      <c r="G144" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5463,10 +5463,10 @@
         <v>120</v>
       </c>
       <c r="F145" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="4">
-        <v>0</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>13</v>
+      <c r="F146" s="2">
+        <v>683</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,11 +5508,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="4">
-        <v>0</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>13</v>
+      <c r="F147" s="2">
+        <v>1964</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5532,10 +5532,10 @@
         <v>120</v>
       </c>
       <c r="F148" s="4">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5555,10 +5555,10 @@
         <v>120</v>
       </c>
       <c r="F149" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5578,10 +5578,10 @@
         <v>120</v>
       </c>
       <c r="F150" s="4">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -5600,11 +5600,11 @@
       <c r="E151">
         <v>120</v>
       </c>
-      <c r="F151" s="4">
-        <v>0</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>13</v>
+      <c r="F151" s="2">
+        <v>1995</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -5624,10 +5624,10 @@
         <v>120</v>
       </c>
       <c r="F152" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,11 +5646,11 @@
       <c r="E153">
         <v>120</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="6">
         <v>0</v>
       </c>
-      <c r="G153" s="5" t="s">
-        <v>13</v>
+      <c r="G153" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5669,11 +5669,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="4">
-        <v>0</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>13</v>
+      <c r="F154" s="2">
+        <v>3265</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5692,11 +5692,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="4">
-        <v>0</v>
-      </c>
-      <c r="G155" s="5" t="s">
-        <v>13</v>
+      <c r="F155" s="2">
+        <v>908</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5716,10 +5716,10 @@
         <v>120</v>
       </c>
       <c r="F156" s="4">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5738,11 +5738,11 @@
       <c r="E157">
         <v>120</v>
       </c>
-      <c r="F157" s="4">
-        <v>0</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>13</v>
+      <c r="F157" s="2">
+        <v>3114</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="4">
-        <v>0</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>13</v>
+      <c r="F158" s="2">
+        <v>1101</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5784,11 +5784,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="4">
-        <v>0</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>13</v>
+      <c r="F159" s="2">
+        <v>3978</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5807,11 +5807,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="4">
+      <c r="F160" s="6">
         <v>0</v>
       </c>
-      <c r="G160" s="5" t="s">
-        <v>13</v>
+      <c r="G160" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="4">
-        <v>0</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>13</v>
+      <c r="F161" s="2">
+        <v>1914</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5853,11 +5853,11 @@
       <c r="E162">
         <v>120</v>
       </c>
-      <c r="F162" s="4">
-        <v>0</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>13</v>
+      <c r="F162" s="2">
+        <v>4636</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5876,11 +5876,11 @@
       <c r="E163">
         <v>120</v>
       </c>
-      <c r="F163" s="4">
-        <v>0</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>13</v>
+      <c r="F163" s="2">
+        <v>4562</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5900,10 +5900,10 @@
         <v>120</v>
       </c>
       <c r="F164" s="4">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5922,11 +5922,11 @@
       <c r="E165">
         <v>120</v>
       </c>
-      <c r="F165" s="4">
-        <v>0</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>13</v>
+      <c r="F165" s="2">
+        <v>1260</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5945,11 +5945,11 @@
       <c r="E166">
         <v>120</v>
       </c>
-      <c r="F166" s="4">
-        <v>0</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>13</v>
+      <c r="F166" s="2">
+        <v>3735</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5968,11 +5968,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="4">
-        <v>0</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>13</v>
+      <c r="F167" s="2">
+        <v>764</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,10 +5992,10 @@
         <v>120</v>
       </c>
       <c r="F168" s="4">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6014,11 +6014,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="4">
-        <v>0</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>13</v>
+      <c r="F169" s="2">
+        <v>703</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6038,10 +6038,10 @@
         <v>120</v>
       </c>
       <c r="F170" s="4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6060,11 +6060,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="4">
-        <v>0</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>13</v>
+      <c r="F171" s="2">
+        <v>7654</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6083,11 +6083,11 @@
       <c r="E172">
         <v>120</v>
       </c>
-      <c r="F172" s="4">
-        <v>0</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>13</v>
+      <c r="F172" s="2">
+        <v>2029</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6106,11 +6106,11 @@
       <c r="E173">
         <v>1</v>
       </c>
-      <c r="F173" s="4">
-        <v>0</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>13</v>
+      <c r="F173" s="2">
+        <v>231</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6129,11 +6129,11 @@
       <c r="E174">
         <v>1</v>
       </c>
-      <c r="F174" s="4">
-        <v>0</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>13</v>
+      <c r="F174" s="2">
+        <v>135</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6153,10 +6153,10 @@
         <v>12</v>
       </c>
       <c r="F175" s="4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6175,11 +6175,11 @@
       <c r="E176">
         <v>12</v>
       </c>
-      <c r="F176" s="4">
+      <c r="F176" s="6">
         <v>0</v>
       </c>
-      <c r="G176" s="5" t="s">
-        <v>13</v>
+      <c r="G176" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6198,11 +6198,11 @@
       <c r="E177">
         <v>12</v>
       </c>
-      <c r="F177" s="4">
+      <c r="F177" s="6">
         <v>0</v>
       </c>
-      <c r="G177" s="5" t="s">
-        <v>13</v>
+      <c r="G177" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6221,11 +6221,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="4">
-        <v>0</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>13</v>
+      <c r="F178" s="2">
+        <v>163</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6245,10 +6245,10 @@
         <v>12</v>
       </c>
       <c r="F179" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6267,11 +6267,11 @@
       <c r="E180">
         <v>12</v>
       </c>
-      <c r="F180" s="4">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="5" t="s">
-        <v>13</v>
+      <c r="G180" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6290,11 +6290,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="4">
+      <c r="F181" s="6">
         <v>0</v>
       </c>
-      <c r="G181" s="5" t="s">
-        <v>13</v>
+      <c r="G181" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6313,11 +6313,11 @@
       <c r="E182">
         <v>12</v>
       </c>
-      <c r="F182" s="4">
-        <v>0</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>13</v>
+      <c r="F182" s="2">
+        <v>211</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6337,10 +6337,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -6360,10 +6360,10 @@
         <v>12</v>
       </c>
       <c r="F184" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -6382,11 +6382,11 @@
       <c r="E185">
         <v>12</v>
       </c>
-      <c r="F185" s="4">
-        <v>0</v>
-      </c>
-      <c r="G185" s="5" t="s">
-        <v>13</v>
+      <c r="F185" s="2">
+        <v>3022</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="4">
-        <v>0</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>13</v>
+      <c r="F186" s="2">
+        <v>214</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="4">
-        <v>0</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>13</v>
+      <c r="F187" s="2">
+        <v>157</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6451,11 +6451,11 @@
       <c r="E188">
         <v>12</v>
       </c>
-      <c r="F188" s="4">
-        <v>0</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>13</v>
+      <c r="F188" s="2">
+        <v>654</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6475,10 +6475,10 @@
         <v>18</v>
       </c>
       <c r="F189" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6497,11 +6497,11 @@
       <c r="E190">
         <v>12</v>
       </c>
-      <c r="F190" s="4">
-        <v>0</v>
-      </c>
-      <c r="G190" s="5" t="s">
-        <v>13</v>
+      <c r="F190" s="2">
+        <v>1156</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -6520,11 +6520,11 @@
       <c r="E191">
         <v>18</v>
       </c>
-      <c r="F191" s="4">
-        <v>0</v>
-      </c>
-      <c r="G191" s="5" t="s">
-        <v>13</v>
+      <c r="F191" s="2">
+        <v>1865</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -6543,11 +6543,11 @@
       <c r="E192">
         <v>12</v>
       </c>
-      <c r="F192" s="4">
-        <v>0</v>
-      </c>
-      <c r="G192" s="5" t="s">
-        <v>13</v>
+      <c r="F192" s="2">
+        <v>1913</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -6566,11 +6566,11 @@
       <c r="E193">
         <v>400</v>
       </c>
-      <c r="F193" s="4">
-        <v>0</v>
-      </c>
-      <c r="G193" s="5" t="s">
-        <v>13</v>
+      <c r="F193" s="2">
+        <v>75750</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -6589,11 +6589,11 @@
       <c r="E194">
         <v>400</v>
       </c>
-      <c r="F194" s="4">
-        <v>0</v>
-      </c>
-      <c r="G194" s="5" t="s">
-        <v>13</v>
+      <c r="F194" s="2">
+        <v>70965</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -6612,11 +6612,11 @@
       <c r="E195">
         <v>120</v>
       </c>
-      <c r="F195" s="4">
-        <v>0</v>
-      </c>
-      <c r="G195" s="5" t="s">
-        <v>13</v>
+      <c r="F195" s="2">
+        <v>3607</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="4">
-        <v>0</v>
-      </c>
-      <c r="G196" s="5" t="s">
-        <v>13</v>
+      <c r="F196" s="2">
+        <v>1804</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6658,11 +6658,11 @@
       <c r="E197">
         <v>120</v>
       </c>
-      <c r="F197" s="4">
-        <v>0</v>
-      </c>
-      <c r="G197" s="5" t="s">
-        <v>13</v>
+      <c r="F197" s="2">
+        <v>8964</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="4">
+      <c r="F198" s="6">
         <v>0</v>
       </c>
-      <c r="G198" s="5" t="s">
-        <v>13</v>
+      <c r="G198" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -6704,11 +6704,11 @@
       <c r="E199">
         <v>120</v>
       </c>
-      <c r="F199" s="4">
-        <v>0</v>
-      </c>
-      <c r="G199" s="5" t="s">
-        <v>13</v>
+      <c r="F199" s="2">
+        <v>8040</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -52,36 +52,39 @@
     <t>FUTBOL CUERO TERMOSELLADA PRECISION #5</t>
   </si>
   <si>
+    <t>016726</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
+  </si>
+  <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>016727</t>
+  </si>
+  <si>
+    <t>7754807167277</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
+  </si>
+  <si>
+    <t>016756</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
+  </si>
+  <si>
+    <t>016755</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
+  </si>
+  <si>
     <t>✗ AGOTADO</t>
   </si>
   <si>
-    <t>016726</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
-  </si>
-  <si>
-    <t>016727</t>
-  </si>
-  <si>
-    <t>7754807167277</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
-  </si>
-  <si>
-    <t>016756</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
-  </si>
-  <si>
-    <t>016755</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
-  </si>
-  <si>
     <t>016757</t>
   </si>
   <si>
@@ -518,9 +521,6 @@
   </si>
   <si>
     <t>BALONMANO GOMA #1</t>
-  </si>
-  <si>
-    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>016765</t>
@@ -1712,12 +1712,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1740,12 +1740,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -2196,11 +2196,11 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>13</v>
+      <c r="F3" s="2">
+        <v>2029</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2208,22 +2208,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>24</v>
       </c>
       <c r="F4" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2242,11 +2242,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>13</v>
+      <c r="F5" s="2">
+        <v>3800</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2265,11 +2265,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
+      <c r="F6" s="2">
+        <v>606</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2288,11 +2288,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>13</v>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2300,22 +2300,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>13</v>
+      <c r="F8" s="2">
+        <v>5278</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2323,22 +2323,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>13</v>
+      <c r="F9" s="2">
+        <v>1463</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2346,22 +2346,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>24</v>
       </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>13</v>
+      <c r="F10" s="2">
+        <v>1492</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2369,22 +2369,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>13</v>
+      <c r="F11" s="2">
+        <v>179</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2392,22 +2392,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>13</v>
+      <c r="F12" s="2">
+        <v>1422</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2415,22 +2415,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>13</v>
+      <c r="F13" s="2">
+        <v>167</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2438,22 +2438,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>13</v>
+      <c r="F14" s="2">
+        <v>182</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2461,22 +2461,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="6">
         <v>0</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>13</v>
+      <c r="G15" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2484,22 +2484,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16">
         <v>36</v>
       </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>13</v>
+      <c r="F16" s="2">
+        <v>1012</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2507,22 +2507,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>24</v>
       </c>
       <c r="F17" s="4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2530,22 +2530,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>36</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="6">
         <v>0</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>13</v>
+      <c r="G18" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2553,22 +2553,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>13</v>
+      <c r="F19" s="2">
+        <v>3828</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2576,22 +2576,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>13</v>
+      <c r="F20" s="2">
+        <v>3206</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2599,22 +2599,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>36</v>
       </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>13</v>
+      <c r="F21" s="2">
+        <v>8227</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2622,22 +2622,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="4">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>13</v>
+      <c r="F22" s="2">
+        <v>1326</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2645,22 +2645,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23">
         <v>48</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="6">
         <v>0</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>13</v>
+      <c r="G23" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2668,22 +2668,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="6">
         <v>0</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>13</v>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2691,22 +2691,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>13</v>
+      <c r="G25" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2714,22 +2714,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26">
         <v>48</v>
       </c>
       <c r="F26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2737,22 +2737,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>36</v>
       </c>
       <c r="F27" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2760,22 +2760,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28">
         <v>36</v>
       </c>
       <c r="F28" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2783,22 +2783,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>13</v>
+      <c r="F29" s="2">
+        <v>3043</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,22 +2806,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="6">
         <v>0</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>13</v>
+      <c r="G30" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2829,22 +2829,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="6">
         <v>0</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>13</v>
+      <c r="G31" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2852,22 +2852,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="4">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>13</v>
+      <c r="F32" s="2">
+        <v>3498</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,22 +2875,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="4">
-        <v>0</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>13</v>
+      <c r="F33" s="2">
+        <v>2901</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,22 +2898,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="4">
-        <v>0</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>13</v>
+      <c r="F34" s="2">
+        <v>257</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2921,22 +2921,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>13</v>
+      <c r="F35" s="2">
+        <v>514</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,22 +2944,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="4">
-        <v>0</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>13</v>
+      <c r="F36" s="2">
+        <v>868</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E37">
         <v>48</v>
       </c>
-      <c r="F37" s="4">
-        <v>0</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>13</v>
+      <c r="F37" s="2">
+        <v>7641</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,22 +2990,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E38">
         <v>48</v>
       </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>13</v>
+      <c r="F38" s="2">
+        <v>1351</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,22 +3013,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39">
         <v>48</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="6">
         <v>0</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>13</v>
+      <c r="G39" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,22 +3036,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E40">
         <v>48</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="6">
         <v>0</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>13</v>
+      <c r="G40" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E41">
         <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,22 +3082,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E42">
         <v>48</v>
       </c>
       <c r="F42" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3105,22 +3105,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E43">
         <v>48</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="6">
         <v>0</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>13</v>
+      <c r="G43" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3128,22 +3128,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="4">
-        <v>0</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>13</v>
+      <c r="F44" s="2">
+        <v>6051</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3151,22 +3151,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E45">
         <v>48</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="6">
         <v>0</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>13</v>
+      <c r="G45" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3174,22 +3174,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E46">
         <v>48</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="6">
         <v>0</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>13</v>
+      <c r="G46" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3197,22 +3197,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="4">
-        <v>0</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>13</v>
+      <c r="F47" s="2">
+        <v>11731</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,22 +3220,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="6">
         <v>0</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>13</v>
+      <c r="G48" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3243,22 +3243,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E49">
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3266,22 +3266,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="4">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>13</v>
+      <c r="F50" s="2">
+        <v>5468</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3289,22 +3289,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E51">
         <v>48</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="6">
         <v>0</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>13</v>
+      <c r="G51" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3312,22 +3312,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E52">
         <v>48</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="6">
         <v>0</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>13</v>
+      <c r="G52" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3335,22 +3335,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="4">
-        <v>0</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>13</v>
+      <c r="F53" s="2">
+        <v>294</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,22 +3358,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E54">
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3381,22 +3381,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E55">
         <v>36</v>
       </c>
-      <c r="F55" s="4">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>13</v>
+      <c r="F55" s="2">
+        <v>2182</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3404,22 +3404,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="6">
         <v>0</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>13</v>
+      <c r="G56" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3427,22 +3427,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E57">
         <v>36</v>
       </c>
-      <c r="F57" s="4">
-        <v>0</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>13</v>
+      <c r="F57" s="2">
+        <v>2181</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3450,22 +3450,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E58">
         <v>36</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="6">
         <v>0</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>13</v>
+      <c r="G58" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3473,22 +3473,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E59">
         <v>36</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>13</v>
+      <c r="G59" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3496,22 +3496,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E60">
         <v>36</v>
       </c>
-      <c r="F60" s="4">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>13</v>
+      <c r="F60" s="2">
+        <v>1351</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3519,22 +3519,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E61">
         <v>36</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="6">
         <v>0</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>13</v>
+      <c r="G61" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,22 +3542,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E62">
         <v>36</v>
       </c>
-      <c r="F62" s="4">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>13</v>
+      <c r="F62" s="2">
+        <v>915</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3565,22 +3565,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E63">
         <v>36</v>
       </c>
-      <c r="F63" s="4">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>13</v>
+      <c r="F63" s="2">
+        <v>797</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3588,22 +3588,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="6">
-        <v>10</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>169</v>
+      <c r="F64" s="2">
+        <v>418</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3622,11 +3622,11 @@
       <c r="E65">
         <v>48</v>
       </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>13</v>
+      <c r="F65" s="2">
+        <v>1218</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3645,11 +3645,11 @@
       <c r="E66">
         <v>60</v>
       </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>13</v>
+      <c r="F66" s="2">
+        <v>5188</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3668,11 +3668,11 @@
       <c r="E67">
         <v>60</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>13</v>
+      <c r="F67" s="2">
+        <v>1224</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3691,11 +3691,11 @@
       <c r="E68">
         <v>60</v>
       </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>13</v>
+      <c r="F68" s="2">
+        <v>2119</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3714,11 +3714,11 @@
       <c r="E69">
         <v>60</v>
       </c>
-      <c r="F69" s="4">
-        <v>0</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>13</v>
+      <c r="F69" s="2">
+        <v>1118</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3737,11 +3737,11 @@
       <c r="E70">
         <v>60</v>
       </c>
-      <c r="F70" s="4">
-        <v>0</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>13</v>
+      <c r="F70" s="2">
+        <v>4179</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3760,11 +3760,11 @@
       <c r="E71">
         <v>60</v>
       </c>
-      <c r="F71" s="4">
-        <v>0</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>13</v>
+      <c r="F71" s="2">
+        <v>5084</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3783,11 +3783,11 @@
       <c r="E72">
         <v>60</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="6">
         <v>0</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>13</v>
+      <c r="G72" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3806,11 +3806,11 @@
       <c r="E73">
         <v>60</v>
       </c>
-      <c r="F73" s="4">
-        <v>0</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>13</v>
+      <c r="F73" s="2">
+        <v>3152</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3829,11 +3829,11 @@
       <c r="E74">
         <v>60</v>
       </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>13</v>
+      <c r="F74" s="2">
+        <v>1203</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3852,11 +3852,11 @@
       <c r="E75">
         <v>60</v>
       </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>13</v>
+      <c r="F75" s="2">
+        <v>4369</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3875,11 +3875,11 @@
       <c r="E76">
         <v>60</v>
       </c>
-      <c r="F76" s="4">
-        <v>0</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>13</v>
+      <c r="F76" s="2">
+        <v>8491</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3898,11 +3898,11 @@
       <c r="E77">
         <v>60</v>
       </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>13</v>
+      <c r="F77" s="2">
+        <v>3905</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3921,11 +3921,11 @@
       <c r="E78">
         <v>60</v>
       </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>13</v>
+      <c r="F78" s="2">
+        <v>6449</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3944,11 +3944,11 @@
       <c r="E79">
         <v>60</v>
       </c>
-      <c r="F79" s="4">
-        <v>0</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>13</v>
+      <c r="F79" s="2">
+        <v>5172</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3968,10 +3968,10 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3991,10 +3991,10 @@
         <v>60</v>
       </c>
       <c r="F81" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="4">
-        <v>0</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>13</v>
+      <c r="F82" s="2">
+        <v>938</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4036,11 +4036,11 @@
       <c r="E83">
         <v>60</v>
       </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>13</v>
+      <c r="F83" s="2">
+        <v>1013</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4059,11 +4059,11 @@
       <c r="E84">
         <v>60</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="6">
         <v>0</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>13</v>
+      <c r="G84" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4083,10 +4083,10 @@
         <v>60</v>
       </c>
       <c r="F85" s="4">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4105,11 +4105,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="4">
-        <v>0</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>13</v>
+      <c r="F86" s="2">
+        <v>333</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4128,11 +4128,11 @@
       <c r="E87">
         <v>60</v>
       </c>
-      <c r="F87" s="4">
-        <v>0</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>13</v>
+      <c r="F87" s="2">
+        <v>1426</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="6">
         <v>0</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>13</v>
+      <c r="G88" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,11 +4174,11 @@
       <c r="E89">
         <v>60</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="6">
         <v>0</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>13</v>
+      <c r="G89" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,11 +4197,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="4">
-        <v>0</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>13</v>
+      <c r="F90" s="2">
+        <v>631</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="4">
-        <v>0</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>13</v>
+      <c r="F91" s="2">
+        <v>1337</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4243,11 +4243,11 @@
       <c r="E92">
         <v>60</v>
       </c>
-      <c r="F92" s="4">
-        <v>0</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>13</v>
+      <c r="F92" s="2">
+        <v>1253</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="4">
-        <v>0</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>13</v>
+      <c r="F93" s="2">
+        <v>895</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="4">
-        <v>0</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>13</v>
+      <c r="F94" s="2">
+        <v>1266</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4313,10 +4313,10 @@
         <v>60</v>
       </c>
       <c r="F95" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4335,11 +4335,11 @@
       <c r="E96">
         <v>60</v>
       </c>
-      <c r="F96" s="4">
-        <v>0</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>13</v>
+      <c r="F96" s="2">
+        <v>2299</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4358,11 +4358,11 @@
       <c r="E97">
         <v>60</v>
       </c>
-      <c r="F97" s="4">
-        <v>0</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>13</v>
+      <c r="F97" s="2">
+        <v>5013</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4381,11 +4381,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="4">
-        <v>0</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>13</v>
+      <c r="F98" s="2">
+        <v>3101</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4404,11 +4404,11 @@
       <c r="E99">
         <v>60</v>
       </c>
-      <c r="F99" s="4">
-        <v>0</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>13</v>
+      <c r="F99" s="2">
+        <v>3506</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4427,11 +4427,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="4">
-        <v>0</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>13</v>
+      <c r="F100" s="2">
+        <v>1339</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4450,11 +4450,11 @@
       <c r="E101">
         <v>60</v>
       </c>
-      <c r="F101" s="4">
-        <v>0</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>13</v>
+      <c r="F101" s="2">
+        <v>5645</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -4473,11 +4473,11 @@
       <c r="E102">
         <v>60</v>
       </c>
-      <c r="F102" s="4">
-        <v>0</v>
-      </c>
-      <c r="G102" s="5" t="s">
-        <v>13</v>
+      <c r="F102" s="2">
+        <v>3096</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4496,11 +4496,11 @@
       <c r="E103">
         <v>60</v>
       </c>
-      <c r="F103" s="4">
-        <v>0</v>
-      </c>
-      <c r="G103" s="5" t="s">
-        <v>13</v>
+      <c r="F103" s="2">
+        <v>1816</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4519,11 +4519,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="4">
-        <v>0</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>13</v>
+      <c r="F104" s="2">
+        <v>368</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4542,11 +4542,11 @@
       <c r="E105">
         <v>60</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="6">
         <v>0</v>
       </c>
-      <c r="G105" s="5" t="s">
-        <v>13</v>
+      <c r="G105" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="4">
-        <v>0</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>13</v>
+      <c r="F106" s="2">
+        <v>1230</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4588,11 +4588,11 @@
       <c r="E107">
         <v>60</v>
       </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>13</v>
+      <c r="F107" s="2">
+        <v>5325</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4611,11 +4611,11 @@
       <c r="E108">
         <v>60</v>
       </c>
-      <c r="F108" s="4">
-        <v>0</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>13</v>
+      <c r="F108" s="2">
+        <v>2801</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4634,11 +4634,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="4">
-        <v>0</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>13</v>
+      <c r="F109" s="2">
+        <v>1476</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4657,11 +4657,11 @@
       <c r="E110">
         <v>60</v>
       </c>
-      <c r="F110" s="4">
-        <v>0</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>13</v>
+      <c r="F110" s="2">
+        <v>1733</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4680,11 +4680,11 @@
       <c r="E111">
         <v>60</v>
       </c>
-      <c r="F111" s="4">
-        <v>0</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>13</v>
+      <c r="F111" s="2">
+        <v>5946</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4703,11 +4703,11 @@
       <c r="E112">
         <v>60</v>
       </c>
-      <c r="F112" s="4">
-        <v>0</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>13</v>
+      <c r="F112" s="2">
+        <v>6899</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4726,11 +4726,11 @@
       <c r="E113">
         <v>60</v>
       </c>
-      <c r="F113" s="4">
-        <v>0</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>13</v>
+      <c r="F113" s="2">
+        <v>6393</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4749,11 +4749,11 @@
       <c r="E114">
         <v>60</v>
       </c>
-      <c r="F114" s="4">
-        <v>0</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>13</v>
+      <c r="F114" s="2">
+        <v>10800</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4772,11 +4772,11 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115" s="4">
-        <v>0</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>13</v>
+      <c r="F115" s="2">
+        <v>239</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4795,11 +4795,11 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" s="4">
-        <v>0</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>13</v>
+      <c r="F116" s="2">
+        <v>85</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4818,11 +4818,11 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117" s="4">
-        <v>0</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>13</v>
+      <c r="F117" s="2">
+        <v>273</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4841,11 +4841,11 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="4">
-        <v>0</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>13</v>
+      <c r="F118" s="2">
+        <v>272</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -4864,11 +4864,11 @@
       <c r="E119">
         <v>12</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="6">
         <v>0</v>
       </c>
-      <c r="G119" s="5" t="s">
-        <v>13</v>
+      <c r="G119" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,11 +4887,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="4">
-        <v>0</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>13</v>
+      <c r="F120" s="2">
+        <v>202</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,11 +4910,11 @@
       <c r="E121">
         <v>36</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="6">
         <v>0</v>
       </c>
-      <c r="G121" s="5" t="s">
-        <v>13</v>
+      <c r="G121" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4933,11 +4933,11 @@
       <c r="E122">
         <v>12</v>
       </c>
-      <c r="F122" s="4">
-        <v>0</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>13</v>
+      <c r="F122" s="2">
+        <v>2925</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>36</v>
       </c>
       <c r="F123" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4979,11 +4979,11 @@
       <c r="E124">
         <v>12</v>
       </c>
-      <c r="F124" s="4">
-        <v>0</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>13</v>
+      <c r="F124" s="2">
+        <v>2460</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5002,11 +5002,11 @@
       <c r="E125">
         <v>36</v>
       </c>
-      <c r="F125" s="4">
-        <v>0</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>13</v>
+      <c r="F125" s="2">
+        <v>969</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="4">
-        <v>0</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>13</v>
+      <c r="F126" s="2">
+        <v>1936</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5049,10 +5049,10 @@
         <v>120</v>
       </c>
       <c r="F127" s="4">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,10 +5072,10 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5094,11 +5094,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="4">
-        <v>0</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>13</v>
+      <c r="F129" s="2">
+        <v>989</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="4">
-        <v>0</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>13</v>
+      <c r="F130" s="2">
+        <v>812</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5141,10 +5141,10 @@
         <v>120</v>
       </c>
       <c r="F131" s="4">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5164,10 +5164,10 @@
         <v>120</v>
       </c>
       <c r="F132" s="4">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5186,11 +5186,11 @@
       <c r="E133">
         <v>120</v>
       </c>
-      <c r="F133" s="4">
-        <v>0</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>13</v>
+      <c r="F133" s="2">
+        <v>6592</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5209,11 +5209,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="4">
-        <v>0</v>
-      </c>
-      <c r="G134" s="5" t="s">
-        <v>13</v>
+      <c r="F134" s="2">
+        <v>1017</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5233,10 +5233,10 @@
         <v>120</v>
       </c>
       <c r="F135" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5255,11 +5255,11 @@
       <c r="E136">
         <v>120</v>
       </c>
-      <c r="F136" s="4">
-        <v>0</v>
-      </c>
-      <c r="G136" s="5" t="s">
-        <v>13</v>
+      <c r="F136" s="2">
+        <v>4015</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5278,11 +5278,11 @@
       <c r="E137">
         <v>120</v>
       </c>
-      <c r="F137" s="4">
-        <v>0</v>
-      </c>
-      <c r="G137" s="5" t="s">
-        <v>13</v>
+      <c r="F137" s="2">
+        <v>1904</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5302,10 +5302,10 @@
         <v>120</v>
       </c>
       <c r="F138" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,11 +5324,11 @@
       <c r="E139">
         <v>120</v>
       </c>
-      <c r="F139" s="4">
-        <v>0</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>13</v>
+      <c r="F139" s="2">
+        <v>4463</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,11 +5347,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="4">
-        <v>0</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>13</v>
+      <c r="F140" s="2">
+        <v>870</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,11 +5370,11 @@
       <c r="E141">
         <v>120</v>
       </c>
-      <c r="F141" s="4">
-        <v>0</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>13</v>
+      <c r="F141" s="2">
+        <v>4091</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5393,11 +5393,11 @@
       <c r="E142">
         <v>120</v>
       </c>
-      <c r="F142" s="4">
-        <v>0</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>13</v>
+      <c r="F142" s="2">
+        <v>3358</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5417,10 +5417,10 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,11 +5439,11 @@
       <c r="E144">
         <v>120</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="5" t="s">
-        <v>13</v>
+      <c r="G144" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5463,10 +5463,10 @@
         <v>120</v>
       </c>
       <c r="F145" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="4">
-        <v>0</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>13</v>
+      <c r="F146" s="2">
+        <v>683</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,11 +5508,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="4">
-        <v>0</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>13</v>
+      <c r="F147" s="2">
+        <v>1964</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5532,10 +5532,10 @@
         <v>120</v>
       </c>
       <c r="F148" s="4">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5555,10 +5555,10 @@
         <v>120</v>
       </c>
       <c r="F149" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5578,10 +5578,10 @@
         <v>120</v>
       </c>
       <c r="F150" s="4">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -5600,11 +5600,11 @@
       <c r="E151">
         <v>120</v>
       </c>
-      <c r="F151" s="4">
-        <v>0</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>13</v>
+      <c r="F151" s="2">
+        <v>1995</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -5624,10 +5624,10 @@
         <v>120</v>
       </c>
       <c r="F152" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,11 +5646,11 @@
       <c r="E153">
         <v>120</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="6">
         <v>0</v>
       </c>
-      <c r="G153" s="5" t="s">
-        <v>13</v>
+      <c r="G153" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5669,11 +5669,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="4">
-        <v>0</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>13</v>
+      <c r="F154" s="2">
+        <v>3265</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5692,11 +5692,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="4">
-        <v>0</v>
-      </c>
-      <c r="G155" s="5" t="s">
-        <v>13</v>
+      <c r="F155" s="2">
+        <v>908</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5716,10 +5716,10 @@
         <v>120</v>
       </c>
       <c r="F156" s="4">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5738,11 +5738,11 @@
       <c r="E157">
         <v>120</v>
       </c>
-      <c r="F157" s="4">
-        <v>0</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>13</v>
+      <c r="F157" s="2">
+        <v>3114</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="4">
-        <v>0</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>13</v>
+      <c r="F158" s="2">
+        <v>981</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5784,11 +5784,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="4">
-        <v>0</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>13</v>
+      <c r="F159" s="2">
+        <v>3978</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5807,11 +5807,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="4">
+      <c r="F160" s="6">
         <v>0</v>
       </c>
-      <c r="G160" s="5" t="s">
-        <v>13</v>
+      <c r="G160" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="4">
-        <v>0</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>13</v>
+      <c r="F161" s="2">
+        <v>1782</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5853,11 +5853,11 @@
       <c r="E162">
         <v>120</v>
       </c>
-      <c r="F162" s="4">
-        <v>0</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>13</v>
+      <c r="F162" s="2">
+        <v>4636</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5876,11 +5876,11 @@
       <c r="E163">
         <v>120</v>
       </c>
-      <c r="F163" s="4">
-        <v>0</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>13</v>
+      <c r="F163" s="2">
+        <v>4562</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5900,10 +5900,10 @@
         <v>120</v>
       </c>
       <c r="F164" s="4">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5922,11 +5922,11 @@
       <c r="E165">
         <v>120</v>
       </c>
-      <c r="F165" s="4">
-        <v>0</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>13</v>
+      <c r="F165" s="2">
+        <v>1260</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5945,11 +5945,11 @@
       <c r="E166">
         <v>120</v>
       </c>
-      <c r="F166" s="4">
-        <v>0</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>13</v>
+      <c r="F166" s="2">
+        <v>3735</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5968,11 +5968,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="4">
-        <v>0</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>13</v>
+      <c r="F167" s="2">
+        <v>764</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,10 +5992,10 @@
         <v>120</v>
       </c>
       <c r="F168" s="4">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6014,11 +6014,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="4">
-        <v>0</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>13</v>
+      <c r="F169" s="2">
+        <v>703</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6038,10 +6038,10 @@
         <v>120</v>
       </c>
       <c r="F170" s="4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6060,11 +6060,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="4">
-        <v>0</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>13</v>
+      <c r="F171" s="2">
+        <v>7654</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6083,11 +6083,11 @@
       <c r="E172">
         <v>120</v>
       </c>
-      <c r="F172" s="4">
-        <v>0</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>13</v>
+      <c r="F172" s="2">
+        <v>2029</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6106,11 +6106,11 @@
       <c r="E173">
         <v>1</v>
       </c>
-      <c r="F173" s="4">
-        <v>0</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>13</v>
+      <c r="F173" s="2">
+        <v>231</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6129,11 +6129,11 @@
       <c r="E174">
         <v>1</v>
       </c>
-      <c r="F174" s="4">
-        <v>0</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>13</v>
+      <c r="F174" s="2">
+        <v>135</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6153,10 +6153,10 @@
         <v>12</v>
       </c>
       <c r="F175" s="4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6175,11 +6175,11 @@
       <c r="E176">
         <v>12</v>
       </c>
-      <c r="F176" s="4">
+      <c r="F176" s="6">
         <v>0</v>
       </c>
-      <c r="G176" s="5" t="s">
-        <v>13</v>
+      <c r="G176" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6198,11 +6198,11 @@
       <c r="E177">
         <v>12</v>
       </c>
-      <c r="F177" s="4">
+      <c r="F177" s="6">
         <v>0</v>
       </c>
-      <c r="G177" s="5" t="s">
-        <v>13</v>
+      <c r="G177" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6221,11 +6221,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="4">
-        <v>0</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>13</v>
+      <c r="F178" s="2">
+        <v>163</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6245,10 +6245,10 @@
         <v>12</v>
       </c>
       <c r="F179" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6267,11 +6267,11 @@
       <c r="E180">
         <v>12</v>
       </c>
-      <c r="F180" s="4">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="5" t="s">
-        <v>13</v>
+      <c r="G180" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6290,11 +6290,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="4">
+      <c r="F181" s="6">
         <v>0</v>
       </c>
-      <c r="G181" s="5" t="s">
-        <v>13</v>
+      <c r="G181" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6313,11 +6313,11 @@
       <c r="E182">
         <v>12</v>
       </c>
-      <c r="F182" s="4">
-        <v>0</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>13</v>
+      <c r="F182" s="2">
+        <v>211</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6337,10 +6337,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -6360,10 +6360,10 @@
         <v>12</v>
       </c>
       <c r="F184" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -6382,11 +6382,11 @@
       <c r="E185">
         <v>12</v>
       </c>
-      <c r="F185" s="4">
-        <v>0</v>
-      </c>
-      <c r="G185" s="5" t="s">
-        <v>13</v>
+      <c r="F185" s="2">
+        <v>3022</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="4">
-        <v>0</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>13</v>
+      <c r="F186" s="2">
+        <v>214</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="4">
-        <v>0</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>13</v>
+      <c r="F187" s="2">
+        <v>157</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6451,11 +6451,11 @@
       <c r="E188">
         <v>12</v>
       </c>
-      <c r="F188" s="4">
-        <v>0</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>13</v>
+      <c r="F188" s="2">
+        <v>654</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6475,10 +6475,10 @@
         <v>18</v>
       </c>
       <c r="F189" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6497,11 +6497,11 @@
       <c r="E190">
         <v>12</v>
       </c>
-      <c r="F190" s="4">
-        <v>0</v>
-      </c>
-      <c r="G190" s="5" t="s">
-        <v>13</v>
+      <c r="F190" s="2">
+        <v>1156</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -6520,11 +6520,11 @@
       <c r="E191">
         <v>18</v>
       </c>
-      <c r="F191" s="4">
-        <v>0</v>
-      </c>
-      <c r="G191" s="5" t="s">
-        <v>13</v>
+      <c r="F191" s="2">
+        <v>1865</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -6543,11 +6543,11 @@
       <c r="E192">
         <v>12</v>
       </c>
-      <c r="F192" s="4">
-        <v>0</v>
-      </c>
-      <c r="G192" s="5" t="s">
-        <v>13</v>
+      <c r="F192" s="2">
+        <v>1913</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -6566,11 +6566,11 @@
       <c r="E193">
         <v>400</v>
       </c>
-      <c r="F193" s="4">
-        <v>0</v>
-      </c>
-      <c r="G193" s="5" t="s">
-        <v>13</v>
+      <c r="F193" s="2">
+        <v>75750</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -6589,11 +6589,11 @@
       <c r="E194">
         <v>400</v>
       </c>
-      <c r="F194" s="4">
-        <v>0</v>
-      </c>
-      <c r="G194" s="5" t="s">
-        <v>13</v>
+      <c r="F194" s="2">
+        <v>70965</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -6612,11 +6612,11 @@
       <c r="E195">
         <v>120</v>
       </c>
-      <c r="F195" s="4">
-        <v>0</v>
-      </c>
-      <c r="G195" s="5" t="s">
-        <v>13</v>
+      <c r="F195" s="2">
+        <v>3607</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="4">
-        <v>0</v>
-      </c>
-      <c r="G196" s="5" t="s">
-        <v>13</v>
+      <c r="F196" s="2">
+        <v>1804</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6658,11 +6658,11 @@
       <c r="E197">
         <v>120</v>
       </c>
-      <c r="F197" s="4">
-        <v>0</v>
-      </c>
-      <c r="G197" s="5" t="s">
-        <v>13</v>
+      <c r="F197" s="2">
+        <v>8964</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="4">
+      <c r="F198" s="6">
         <v>0</v>
       </c>
-      <c r="G198" s="5" t="s">
-        <v>13</v>
+      <c r="G198" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -6704,11 +6704,11 @@
       <c r="E199">
         <v>120</v>
       </c>
-      <c r="F199" s="4">
-        <v>0</v>
-      </c>
-      <c r="G199" s="5" t="s">
-        <v>13</v>
+      <c r="F199" s="2">
+        <v>8040</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2174,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3800</v>
+        <v>3794</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3206</v>
+        <v>3203</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>8226</v>
+        <v>8223</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -3600,7 +3600,7 @@
         <v>48</v>
       </c>
       <c r="F64" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>4369</v>
+        <v>4357</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="2">
-        <v>2454</v>
+        <v>2430</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5325,7 +5325,7 @@
         <v>120</v>
       </c>
       <c r="F139" s="2">
-        <v>4463</v>
+        <v>4451</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1609</v>
+        <v>1549</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>5820</v>
+        <v>5700</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>10722</v>
+        <v>10662</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>5620</v>
+        <v>5619</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3415,11 +3415,11 @@
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>23</v>
+      <c r="F56" s="4">
+        <v>3</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>10981</v>
+        <v>10885</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>4994</v>
+        <v>4946</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8474</v>
+        <v>8462</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>6309</v>
+        <v>6297</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>5596</v>
+        <v>5584</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>10551</v>
+        <v>10539</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2174,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2022</v>
+        <v>1968</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2519,7 +2519,7 @@
         <v>24</v>
       </c>
       <c r="F17" s="4">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>15</v>
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3786</v>
+        <v>3750</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3203</v>
+        <v>3167</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>8180</v>
+        <v>8144</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3495</v>
+        <v>3480</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1249</v>
+        <v>1045</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>10720</v>
+        <v>10504</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>4934</v>
+        <v>4898</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3600,7 +3600,7 @@
         <v>48</v>
       </c>
       <c r="F64" s="2">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -3623,7 +3623,7 @@
         <v>48</v>
       </c>
       <c r="F65" s="2">
-        <v>1218</v>
+        <v>1194</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>3075</v>
+        <v>3057</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>994</v>
+        <v>970</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8450</v>
+        <v>8426</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3967,11 +3967,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="6">
-        <v>0</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>23</v>
+      <c r="F80" s="2">
+        <v>348</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4037,7 +4037,7 @@
         <v>60</v>
       </c>
       <c r="F83" s="2">
-        <v>1013</v>
+        <v>989</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>784</v>
+        <v>724</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>2955</v>
+        <v>2931</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3432</v>
+        <v>3396</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>1144</v>
+        <v>1126</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>5570</v>
+        <v>5534</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>5240</v>
+        <v>5216</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>10471</v>
+        <v>10459</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>10</v>
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="F117" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>10</v>
@@ -5026,7 +5026,7 @@
         <v>120</v>
       </c>
       <c r="F126" s="2">
-        <v>1366</v>
+        <v>1246</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>10</v>
@@ -5118,7 +5118,7 @@
         <v>120</v>
       </c>
       <c r="F130" s="2">
-        <v>788</v>
+        <v>668</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>10</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="2">
-        <v>897</v>
+        <v>777</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5279,7 +5279,7 @@
         <v>120</v>
       </c>
       <c r="F137" s="2">
-        <v>1772</v>
+        <v>1652</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5325,7 +5325,7 @@
         <v>120</v>
       </c>
       <c r="F139" s="2">
-        <v>4451</v>
+        <v>4415</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>4052</v>
+        <v>4040</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>3205</v>
+        <v>3193</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5854,7 +5854,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="2">
-        <v>4624</v>
+        <v>4612</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -5877,7 +5877,7 @@
         <v>120</v>
       </c>
       <c r="F163" s="2">
-        <v>4562</v>
+        <v>4526</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
@@ -5900,7 +5900,7 @@
         <v>120</v>
       </c>
       <c r="F164" s="4">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>15</v>
@@ -5992,7 +5992,7 @@
         <v>120</v>
       </c>
       <c r="F168" s="4">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="G168" s="5" t="s">
         <v>15</v>
@@ -6038,7 +6038,7 @@
         <v>120</v>
       </c>
       <c r="F170" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G170" s="5" t="s">
         <v>15</v>
@@ -6061,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>7642</v>
+        <v>7630</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>1801</v>
+        <v>1789</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>75350</v>
+        <v>74950</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>70565</v>
+        <v>70165</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -5991,11 +5991,11 @@
       <c r="E168">
         <v>120</v>
       </c>
-      <c r="F168" s="6">
-        <v>0</v>
-      </c>
-      <c r="G168" s="7" t="s">
-        <v>23</v>
+      <c r="F168" s="2">
+        <v>2049</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -5992,7 +5992,7 @@
         <v>120</v>
       </c>
       <c r="F168" s="2">
-        <v>2049</v>
+        <v>4093</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3731</v>
+        <v>3728</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5237</v>
+        <v>5235</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>8144</v>
+        <v>8142</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2910,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="4">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>15</v>
@@ -2933,7 +2933,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>5087</v>
+        <v>5060</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>10066</v>
+        <v>10039</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>4424</v>
+        <v>4397</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7982</v>
+        <v>7978</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>6258</v>
+        <v>6245</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5072</v>
+        <v>5068</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4312,11 +4312,11 @@
       <c r="E95">
         <v>60</v>
       </c>
-      <c r="F95" s="4">
-        <v>1</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>15</v>
+      <c r="F95" s="6">
+        <v>0</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>2090</v>
+        <v>2084</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4359,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="F97" s="2">
-        <v>5013</v>
+        <v>5011</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>2419</v>
+        <v>2406</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3112</v>
+        <v>3104</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4971</v>
+        <v>4964</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2912</v>
+        <v>2905</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4872</v>
+        <v>4862</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>4998</v>
+        <v>4995</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6668</v>
+        <v>6666</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>6273</v>
+        <v>6272</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>10198</v>
+        <v>10173</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5026,7 +5026,7 @@
         <v>120</v>
       </c>
       <c r="F126" s="2">
-        <v>1246</v>
+        <v>1204</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>10</v>
@@ -5417,7 +5417,7 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>15</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>74950</v>
+        <v>74550</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>70165</v>
+        <v>69765</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -5118,7 +5118,7 @@
         <v>120</v>
       </c>
       <c r="F130" s="4">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>15</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2826</v>
+        <v>2824</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2174,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3582</v>
+        <v>3558</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3640</v>
+        <v>3622</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>8026</v>
+        <v>8008</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2910,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="4">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>15</v>
@@ -2933,7 +2933,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>589</v>
+        <v>517</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>4688</v>
+        <v>4478</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>9724</v>
+        <v>9604</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>3956</v>
+        <v>3803</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>2031</v>
+        <v>1995</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>2017</v>
+        <v>1980</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1250</v>
+        <v>1214</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>652</v>
+        <v>633</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3646,7 +3646,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="2">
-        <v>5188</v>
+        <v>5152</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>2439</v>
+        <v>2409</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>6239</v>
+        <v>6236</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>1696</v>
+        <v>1574</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4359,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="F97" s="2">
-        <v>5011</v>
+        <v>4951</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>2395</v>
+        <v>2328</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3073</v>
+        <v>3006</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>975</v>
+        <v>891</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4956</v>
+        <v>4893</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2898</v>
+        <v>2835</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4566,7 +4566,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="2">
-        <v>836</v>
+        <v>776</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4856</v>
+        <v>4732</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>2577</v>
+        <v>2517</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>980</v>
+        <v>947</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1530</v>
+        <v>1437</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>4807</v>
+        <v>4625</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6659</v>
+        <v>6538</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>6092</v>
+        <v>6062</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>10141</v>
+        <v>9978</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5026,7 +5026,7 @@
         <v>120</v>
       </c>
       <c r="F126" s="2">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>10</v>
@@ -5118,7 +5118,7 @@
         <v>120</v>
       </c>
       <c r="F130" s="4">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>15</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="2">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3646,7 +3646,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="2">
-        <v>5152</v>
+        <v>5092</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1212</v>
+        <v>1164</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="2">
-        <v>2112</v>
+        <v>2064</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -3738,7 +3738,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="2">
-        <v>4169</v>
+        <v>4121</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -3761,7 +3761,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="2">
-        <v>5075</v>
+        <v>5027</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>3832</v>
+        <v>3796</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3899,7 +3899,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="2">
-        <v>3902</v>
+        <v>3890</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -4566,7 +4566,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="2">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>10</v>
@@ -5348,7 +5348,7 @@
         <v>120</v>
       </c>
       <c r="F140" s="4">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>15</v>
@@ -5624,7 +5624,7 @@
         <v>120</v>
       </c>
       <c r="F152" s="2">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>10</v>
@@ -5831,7 +5831,7 @@
         <v>120</v>
       </c>
       <c r="F161" s="2">
-        <v>1218</v>
+        <v>1194</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -5969,7 +5969,7 @@
         <v>120</v>
       </c>
       <c r="F167" s="4">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>15</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2266,7 +2266,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2381,7 +2381,7 @@
         <v>24</v>
       </c>
       <c r="F11" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7522</v>
+        <v>7517</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1288</v>
+        <v>1277</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2910,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="4">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>15</v>
@@ -2933,7 +2933,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="4">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>15</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>3795</v>
+        <v>3774</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>9268</v>
+        <v>9232</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>3466</v>
+        <v>3442</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3370,7 +3370,7 @@
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>15</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>2033</v>
+        <v>1984</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>687</v>
+        <v>638</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3623,7 +3623,7 @@
         <v>48</v>
       </c>
       <c r="F65" s="2">
-        <v>825</v>
+        <v>729</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>6627</v>
+        <v>6625</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>4273</v>
+        <v>4271</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7915</v>
+        <v>7909</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>6160</v>
+        <v>6148</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4359,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="F97" s="2">
-        <v>4951</v>
+        <v>4949</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>2260</v>
+        <v>2254</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3003</v>
+        <v>2997</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>885</v>
+        <v>581</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4887</v>
+        <v>4884</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2835</v>
+        <v>2832</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4566,7 +4566,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4729</v>
+        <v>4723</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>4589</v>
+        <v>4587</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6477</v>
+        <v>6475</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9916</v>
+        <v>9907</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="2">
-        <v>1071</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4">
+        <v>465</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5095,7 +5095,7 @@
         <v>120</v>
       </c>
       <c r="F129" s="2">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -5486,7 +5486,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="2">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>10</v>
@@ -6383,7 +6383,7 @@
         <v>12</v>
       </c>
       <c r="F185" s="2">
-        <v>2815</v>
+        <v>2659</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6429,7 +6429,7 @@
         <v>12</v>
       </c>
       <c r="F187" s="4">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G187" s="5" t="s">
         <v>15</v>
@@ -6452,7 +6452,7 @@
         <v>12</v>
       </c>
       <c r="F188" s="2">
-        <v>592</v>
+        <v>532</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>10</v>
@@ -6521,7 +6521,7 @@
         <v>18</v>
       </c>
       <c r="F191" s="2">
-        <v>1630</v>
+        <v>1504</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6544,7 +6544,7 @@
         <v>12</v>
       </c>
       <c r="F192" s="2">
-        <v>1829</v>
+        <v>1805</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>3367</v>
+        <v>3355</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>120</v>
       </c>
       <c r="F196" s="2">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3630</v>
+        <v>3627</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2266,7 +2266,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7517</v>
+        <v>7510</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="4">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>15</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>3774</v>
+        <v>3758</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>9232</v>
+        <v>9203</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>3442</v>
+        <v>3423</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3370,7 +3370,7 @@
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>15</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3623,7 +3623,7 @@
         <v>48</v>
       </c>
       <c r="F65" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="2">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -3738,7 +3738,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="2">
-        <v>4115</v>
+        <v>4112</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -3761,7 +3761,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="2">
-        <v>5021</v>
+        <v>5017</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>2254</v>
+        <v>2248</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4884</v>
+        <v>4883</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>4587</v>
+        <v>4584</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6475</v>
+        <v>6474</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9907</v>
+        <v>9894</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5026,7 +5026,7 @@
         <v>120</v>
       </c>
       <c r="F126" s="4">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>15</v>
@@ -5187,7 +5187,7 @@
         <v>120</v>
       </c>
       <c r="F133" s="2">
-        <v>6586</v>
+        <v>6583</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>10</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5256,7 +5256,7 @@
         <v>120</v>
       </c>
       <c r="F136" s="2">
-        <v>3891</v>
+        <v>3888</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>3355</v>
+        <v>3343</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>120</v>
       </c>
       <c r="F196" s="2">
-        <v>1216</v>
+        <v>1204</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2266,7 +2266,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>3758</v>
+        <v>3746</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>9203</v>
+        <v>9197</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>3423</v>
+        <v>3417</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9894</v>
+        <v>9890</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5138</v>
+        <v>5126</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2979,7 +2979,7 @@
         <v>48</v>
       </c>
       <c r="F37" s="2">
-        <v>7641</v>
+        <v>7593</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>387</v>
+        <v>351</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5002</v>
+        <v>4870</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>1270</v>
+        <v>1186</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6474</v>
+        <v>6366</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>6152</v>
+        <v>6020</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -5026,7 +5026,7 @@
         <v>120</v>
       </c>
       <c r="F126" s="4">
-        <v>453</v>
+        <v>345</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>15</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="2">
-        <v>768</v>
+        <v>672</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5348,7 +5348,7 @@
         <v>120</v>
       </c>
       <c r="F140" s="4">
-        <v>258</v>
+        <v>150</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>15</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>3558</v>
+        <v>3510</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5394,7 +5394,7 @@
         <v>120</v>
       </c>
       <c r="F142" s="2">
-        <v>3280</v>
+        <v>3208</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>10</v>
@@ -5486,7 +5486,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="2">
-        <v>495</v>
+        <v>319</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>10</v>
@@ -5601,7 +5601,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="2">
-        <v>1815</v>
+        <v>1779</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>2647</v>
+        <v>2635</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5716,7 +5716,7 @@
         <v>120</v>
       </c>
       <c r="F156" s="4">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>15</v>
@@ -5762,7 +5762,7 @@
         <v>120</v>
       </c>
       <c r="F158" s="2">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>10</v>
@@ -5831,7 +5831,7 @@
         <v>120</v>
       </c>
       <c r="F161" s="2">
-        <v>1194</v>
+        <v>1110</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -5992,7 +5992,7 @@
         <v>120</v>
       </c>
       <c r="F168" s="2">
-        <v>4093</v>
+        <v>4009</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>1555</v>
+        <v>1399</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>3343</v>
+        <v>3115</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>120</v>
       </c>
       <c r="F196" s="2">
-        <v>1204</v>
+        <v>1036</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>1939</v>
+        <v>1923</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3348</v>
+        <v>3336</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="4">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>15</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>9101</v>
+        <v>9083</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>3465</v>
+        <v>3453</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3623,7 +3623,7 @@
         <v>48</v>
       </c>
       <c r="F65" s="2">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11774</v>
+        <v>11758</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>5938</v>
+        <v>5922</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>4870</v>
+        <v>4869</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -4037,7 +4037,7 @@
         <v>60</v>
       </c>
       <c r="F83" s="4">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>15</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2725</v>
+        <v>2713</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4723</v>
+        <v>4707</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6156</v>
+        <v>6155</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9890</v>
+        <v>9877</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5325,7 +5325,7 @@
         <v>120</v>
       </c>
       <c r="F139" s="2">
-        <v>3941</v>
+        <v>3929</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>3510</v>
+        <v>3498</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5417,7 +5417,7 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>15</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>2635</v>
+        <v>2623</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>7558</v>
+        <v>7546</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>120</v>
       </c>
       <c r="F196" s="2">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3651</v>
+        <v>3603</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3712</v>
+        <v>3622</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3164</v>
+        <v>3074</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1271</v>
+        <v>1163</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="4">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>15</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>3578</v>
+        <v>1226</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>9083</v>
+        <v>7595</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>3453</v>
+        <v>2469</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="2">
-        <v>2060</v>
+        <v>2048</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -3738,7 +3738,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="2">
-        <v>4112</v>
+        <v>4100</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -3761,7 +3761,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="2">
-        <v>5017</v>
+        <v>5005</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11758</v>
+        <v>11578</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>8857</v>
+        <v>8677</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>4271</v>
+        <v>4091</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7909</v>
+        <v>7765</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3899,7 +3899,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="2">
-        <v>3626</v>
+        <v>3602</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>5922</v>
+        <v>5718</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>4869</v>
+        <v>4749</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>1931</v>
+        <v>1811</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4037,7 +4037,7 @@
         <v>60</v>
       </c>
       <c r="F83" s="4">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>15</v>
@@ -4083,7 +4083,7 @@
         <v>60</v>
       </c>
       <c r="F85" s="4">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>15</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>544</v>
+        <v>424</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>865</v>
+        <v>745</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>1189</v>
+        <v>1069</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="2">
-        <v>360</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>10</v>
+      <c r="F93" s="4">
+        <v>240</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1083</v>
+        <v>963</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>1721</v>
+        <v>1397</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>1936</v>
+        <v>1636</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2713</v>
+        <v>2389</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4427,11 +4427,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="2">
-        <v>415</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>10</v>
+      <c r="F100" s="4">
+        <v>31</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4733</v>
+        <v>4373</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2801</v>
+        <v>2417</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4520,7 +4520,7 @@
         <v>60</v>
       </c>
       <c r="F104" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>10</v>
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="2">
-        <v>578</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="4">
+        <v>278</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4707</v>
+        <v>4407</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>2367</v>
+        <v>2007</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>834</v>
+        <v>510</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1432</v>
+        <v>1132</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>4314</v>
+        <v>4014</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6155</v>
+        <v>5831</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>6020</v>
+        <v>5720</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9877</v>
+        <v>9493</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="F117" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>10</v>
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>73349</v>
+        <v>72549</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>68165</v>
+        <v>67365</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2449,11 +2449,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="2">
-        <v>181</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>179</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>7590</v>
+        <v>7587</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>1811</v>
+        <v>3551</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11546</v>
+        <v>11486</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>8645</v>
+        <v>8585</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>4059</v>
+        <v>3999</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>5718</v>
+        <v>5658</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>3539</v>
+        <v>3479</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>745</v>
+        <v>685</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="4">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>15</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>962</v>
+        <v>902</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>1337</v>
+        <v>1277</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>1606</v>
+        <v>1546</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2389</v>
+        <v>2329</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4313</v>
+        <v>4253</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4566,7 +4566,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="4">
-        <v>278</v>
+        <v>218</v>
       </c>
       <c r="G106" s="5" t="s">
         <v>15</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4407</v>
+        <v>4347</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>1977</v>
+        <v>1917</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>1102</v>
+        <v>1042</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9263</v>
+        <v>9203</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>72549</v>
+        <v>72149</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2174,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2329</v>
+        <v>2269</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4155</v>
+        <v>4095</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>1893</v>
+        <v>1833</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>3760</v>
+        <v>3700</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9179</v>
+        <v>9119</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2979,7 +2979,7 @@
         <v>48</v>
       </c>
       <c r="F37" s="2">
-        <v>7592</v>
+        <v>7595</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>1921</v>
+        <v>5855</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3139,11 +3139,11 @@
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="6">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>23</v>
+      <c r="F44" s="4">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>4420</v>
+        <v>4421</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>15</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -5071,11 +5071,11 @@
       <c r="E128">
         <v>120</v>
       </c>
-      <c r="F128" s="6">
-        <v>0</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>23</v>
+      <c r="F128" s="4">
+        <v>1</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5118,7 +5118,7 @@
         <v>120</v>
       </c>
       <c r="F130" s="4">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>15</v>
@@ -5509,7 +5509,7 @@
         <v>120</v>
       </c>
       <c r="F147" s="2">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>72149</v>
+        <v>72150</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>5855</v>
+        <v>7824</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>4421</v>
+        <v>4373</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="4">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>15</v>
@@ -4197,11 +4197,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="2">
-        <v>300</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="F90" s="4">
+        <v>288</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="4">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>15</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>1683</v>
+        <v>1653</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="4">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>15</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>952</v>
+        <v>922</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>5608</v>
+        <v>5578</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9064</v>
+        <v>9034</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5071,11 +5071,11 @@
       <c r="E128">
         <v>120</v>
       </c>
-      <c r="F128" s="4">
-        <v>1</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>15</v>
+      <c r="F128" s="6">
+        <v>0</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -4888,7 +4888,7 @@
         <v>36</v>
       </c>
       <c r="F120" s="4">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>15</v>
@@ -5486,7 +5486,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="2">
-        <v>319</v>
+        <v>2815</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>10</v>
@@ -6222,7 +6222,7 @@
         <v>12</v>
       </c>
       <c r="F178" s="2">
-        <v>1363</v>
+        <v>97</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>97365</v>
+        <v>108165</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>1919</v>
+        <v>1915</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7537</v>
+        <v>7531</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2795,7 +2795,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2910,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="4">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>15</v>
@@ -2933,7 +2933,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>4373</v>
+        <v>4320</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3277,11 +3277,11 @@
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="4">
-        <v>21</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>15</v>
+      <c r="F50" s="6">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3370,7 +3370,7 @@
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>15</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1976</v>
+        <v>1971</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="2">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -3715,7 +3715,7 @@
         <v>60</v>
       </c>
       <c r="F69" s="2">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3738,7 +3738,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="2">
-        <v>4081</v>
+        <v>4078</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -3761,7 +3761,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="2">
-        <v>4966</v>
+        <v>4964</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11426</v>
+        <v>11423</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>8505</v>
+        <v>8502</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3931</v>
+        <v>3926</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>5474</v>
+        <v>5469</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7764</v>
+        <v>7755</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>7613</v>
+        <v>7609</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="6">
-        <v>0</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>23</v>
+      <c r="F82" s="4">
+        <v>3</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>15</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="4">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>15</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2268</v>
+        <v>2264</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G100" s="5" t="s">
         <v>15</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4158</v>
+        <v>4156</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>4088</v>
+        <v>4079</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>3607</v>
+        <v>3543</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>5578</v>
+        <v>5516</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>5630</v>
+        <v>5628</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>9034</v>
+        <v>9005</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4796,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="4">
-        <v>9</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>15</v>
+      <c r="F126" s="6">
+        <v>0</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>3115</v>
+        <v>3091</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>120</v>
       </c>
       <c r="F196" s="2">
-        <v>710</v>
+        <v>686</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="2">
-        <v>2647</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="6">
+        <v>0</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11423</v>
+        <v>11411</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>8370</v>
+        <v>8358</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3926</v>
+        <v>3914</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7755</v>
+        <v>7743</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>7609</v>
+        <v>7597</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>1213</v>
+        <v>1183</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>1421</v>
+        <v>1391</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>3543</v>
+        <v>3513</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>5405</v>
+        <v>5375</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4796,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -4842,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="F118" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -5095,7 +5095,7 @@
         <v>120</v>
       </c>
       <c r="F129" s="2">
-        <v>960</v>
+        <v>920</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -5118,7 +5118,7 @@
         <v>120</v>
       </c>
       <c r="F130" s="4">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>15</v>
@@ -5141,7 +5141,7 @@
         <v>120</v>
       </c>
       <c r="F131" s="4">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>15</v>
@@ -5164,7 +5164,7 @@
         <v>120</v>
       </c>
       <c r="F132" s="4">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>15</v>
@@ -5187,7 +5187,7 @@
         <v>120</v>
       </c>
       <c r="F133" s="2">
-        <v>6580</v>
+        <v>6540</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>10</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="4">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>15</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7531</v>
+        <v>7525</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>4320</v>
+        <v>2880</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3277,11 +3277,11 @@
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="6">
-        <v>0</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>23</v>
+      <c r="F50" s="4">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3323,11 +3323,11 @@
       <c r="E52">
         <v>48</v>
       </c>
-      <c r="F52" s="6">
-        <v>0</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>23</v>
+      <c r="F52" s="4">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -4037,7 +4037,7 @@
         <v>60</v>
       </c>
       <c r="F83" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>15</v>
@@ -4106,7 +4106,7 @@
         <v>60</v>
       </c>
       <c r="F86" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>3513</v>
+        <v>3507</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3554,7 +3554,7 @@
         <v>36</v>
       </c>
       <c r="F62" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>5449</v>
+        <v>7435</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -5071,11 +5071,11 @@
       <c r="E128">
         <v>120</v>
       </c>
-      <c r="F128" s="6">
-        <v>0</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>23</v>
+      <c r="F128" s="2">
+        <v>6323</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,11 +5347,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="6">
-        <v>0</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>23</v>
+      <c r="F140" s="2">
+        <v>6299</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5531,11 +5531,11 @@
       <c r="E148">
         <v>120</v>
       </c>
-      <c r="F148" s="4">
-        <v>360</v>
-      </c>
-      <c r="G148" s="5" t="s">
-        <v>15</v>
+      <c r="F148" s="2">
+        <v>3877</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>177</v>
+        <v>475</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7512</v>
+        <v>7404</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2979,7 +2979,7 @@
         <v>48</v>
       </c>
       <c r="F37" s="2">
-        <v>7562</v>
+        <v>7418</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>1131</v>
+        <v>987</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="4">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>15</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1965</v>
+        <v>1929</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>659</v>
+        <v>623</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>11870</v>
+        <v>11810</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>7428</v>
+        <v>7368</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2078</v>
+        <v>2018</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>3941</v>
+        <v>3881</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>1299</v>
+        <v>1239</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>3325</v>
+        <v>3205</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>5283</v>
+        <v>5163</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>8655</v>
+        <v>8595</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="4">
-        <v>405</v>
+        <v>285</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>15</v>
@@ -5325,7 +5325,7 @@
         <v>120</v>
       </c>
       <c r="F139" s="2">
-        <v>3919</v>
+        <v>3799</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>3332</v>
+        <v>3212</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2174,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>1911</v>
+        <v>1905</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3480</v>
+        <v>3474</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>4701</v>
+        <v>4695</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="4">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>15</v>
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3607</v>
+        <v>3601</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3060</v>
+        <v>3054</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7399</v>
+        <v>7393</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3331</v>
+        <v>3325</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>804</v>
+        <v>780</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1884</v>
+        <v>1878</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1925</v>
+        <v>1919</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11308</v>
+        <v>11296</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>14050</v>
+        <v>14032</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7692</v>
+        <v>7680</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5955</v>
+        <v>5943</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7409</v>
+        <v>7391</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>1967</v>
+        <v>1955</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>4000</v>
+        <v>3988</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4520,7 +4520,7 @@
         <v>60</v>
       </c>
       <c r="F104" s="2">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>3842</v>
+        <v>3824</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>1210</v>
+        <v>1192</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>5133</v>
+        <v>5115</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>8531</v>
+        <v>8495</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="2">
-        <v>2062</v>
+        <v>2002</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -5187,7 +5187,7 @@
         <v>120</v>
       </c>
       <c r="F133" s="2">
-        <v>6506</v>
+        <v>6494</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>10</v>
@@ -5279,7 +5279,7 @@
         <v>120</v>
       </c>
       <c r="F137" s="2">
-        <v>1503</v>
+        <v>1491</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5325,7 +5325,7 @@
         <v>120</v>
       </c>
       <c r="F139" s="2">
-        <v>3799</v>
+        <v>3787</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5348,7 +5348,7 @@
         <v>120</v>
       </c>
       <c r="F140" s="2">
-        <v>6293</v>
+        <v>6281</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>3212</v>
+        <v>3200</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5394,7 +5394,7 @@
         <v>120</v>
       </c>
       <c r="F142" s="2">
-        <v>2958</v>
+        <v>2946</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>10</v>
@@ -5532,7 +5532,7 @@
         <v>120</v>
       </c>
       <c r="F148" s="2">
-        <v>3877</v>
+        <v>3865</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -5601,7 +5601,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="2">
-        <v>1622</v>
+        <v>1610</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>2571</v>
+        <v>2559</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5739,7 +5739,7 @@
         <v>120</v>
       </c>
       <c r="F157" s="2">
-        <v>3114</v>
+        <v>3102</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
@@ -5785,7 +5785,7 @@
         <v>120</v>
       </c>
       <c r="F159" s="2">
-        <v>3978</v>
+        <v>3954</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>10</v>
@@ -5854,7 +5854,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="2">
-        <v>4337</v>
+        <v>4325</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -5877,7 +5877,7 @@
         <v>120</v>
       </c>
       <c r="F163" s="2">
-        <v>3973</v>
+        <v>3961</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
@@ -5923,7 +5923,7 @@
         <v>120</v>
       </c>
       <c r="F165" s="2">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
@@ -5946,7 +5946,7 @@
         <v>120</v>
       </c>
       <c r="F166" s="2">
-        <v>3722</v>
+        <v>3710</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>10</v>
@@ -5992,7 +5992,7 @@
         <v>120</v>
       </c>
       <c r="F168" s="2">
-        <v>3973</v>
+        <v>3961</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -6015,7 +6015,7 @@
         <v>120</v>
       </c>
       <c r="F169" s="2">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>7496</v>
+        <v>7484</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -6314,7 +6314,7 @@
         <v>12</v>
       </c>
       <c r="F182" s="2">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>780</v>
+        <v>588</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -4083,7 +4083,7 @@
         <v>60</v>
       </c>
       <c r="F85" s="4">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>15</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>1008</v>
+        <v>948</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>1226</v>
+        <v>1166</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2173</v>
+        <v>2143</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>3804</v>
+        <v>3744</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -6359,11 +6359,11 @@
       <c r="E184">
         <v>12</v>
       </c>
-      <c r="F184" s="4">
-        <v>8</v>
-      </c>
-      <c r="G184" s="5" t="s">
-        <v>15</v>
+      <c r="F184" s="6">
+        <v>0</v>
+      </c>
+      <c r="G184" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7391</v>
+        <v>7367</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3139,11 +3139,11 @@
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="6">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>23</v>
+      <c r="F44" s="4">
+        <v>12</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>23</v>
+      <c r="F88" s="4">
+        <v>48</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="6">
-        <v>0</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>23</v>
+      <c r="F158" s="4">
+        <v>60</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="6">
-        <v>0</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>23</v>
+      <c r="F161" s="4">
+        <v>108</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>4688</v>
+        <v>4604</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="4">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>15</v>
@@ -2518,11 +2518,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="4">
-        <v>10</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>15</v>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7399</v>
+        <v>7398</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>1036</v>
+        <v>940</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1734</v>
+        <v>1698</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11262</v>
+        <v>11242</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>13997</v>
+        <v>13821</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3675</v>
+        <v>3655</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12907</v>
+        <v>12887</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5913</v>
+        <v>5733</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7265</v>
+        <v>7245</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>7528</v>
+        <v>7508</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>958</v>
+        <v>815</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="6">
-        <v>0</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>23</v>
+      <c r="F93" s="4">
+        <v>1</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="6">
-        <v>0</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>23</v>
+      <c r="F94" s="4">
+        <v>6</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4313,7 +4313,7 @@
         <v>60</v>
       </c>
       <c r="F95" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>15</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>898</v>
+        <v>818</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>1881</v>
+        <v>1761</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>3918</v>
+        <v>3858</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>1110</v>
+        <v>970</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>568</v>
+        <v>488</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>2978</v>
+        <v>2838</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>5057</v>
+        <v>4817</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>5339</v>
+        <v>5151</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>8403</v>
+        <v>8103</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="2">
-        <v>5875</v>
+        <v>5695</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="4">
-        <v>256</v>
+        <v>124</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>15</v>
@@ -5348,7 +5348,7 @@
         <v>120</v>
       </c>
       <c r="F140" s="2">
-        <v>5993</v>
+        <v>5825</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>3171</v>
+        <v>3087</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5394,7 +5394,7 @@
         <v>120</v>
       </c>
       <c r="F142" s="2">
-        <v>2928</v>
+        <v>2808</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>10</v>
@@ -5601,7 +5601,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="2">
-        <v>1610</v>
+        <v>1442</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>2559</v>
+        <v>2523</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5992,7 +5992,7 @@
         <v>120</v>
       </c>
       <c r="F168" s="2">
-        <v>3961</v>
+        <v>3901</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>1330</v>
+        <v>1186</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>
@@ -6383,7 +6383,7 @@
         <v>12</v>
       </c>
       <c r="F185" s="2">
-        <v>2535</v>
+        <v>2379</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="6">
-        <v>0</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>23</v>
+      <c r="F186" s="4">
+        <v>4</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6521,7 +6521,7 @@
         <v>18</v>
       </c>
       <c r="F191" s="2">
-        <v>1335</v>
+        <v>1263</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6544,7 +6544,7 @@
         <v>12</v>
       </c>
       <c r="F192" s="2">
-        <v>1733</v>
+        <v>1697</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>109750</v>
+        <v>109350</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>104965</v>
+        <v>104565</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>2803</v>
+        <v>2575</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>120</v>
       </c>
       <c r="F196" s="4">
-        <v>358</v>
+        <v>178</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>15</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>4598</v>
+        <v>5598</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2335,7 +2335,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="2">
-        <v>311</v>
+        <v>1311</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>964</v>
+        <v>1964</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>932</v>
+        <v>1932</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7362</v>
+        <v>7902</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2748,11 +2748,11 @@
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>23</v>
+      <c r="F27" s="4">
+        <v>56</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3070,11 +3070,11 @@
       <c r="E41">
         <v>48</v>
       </c>
-      <c r="F41" s="6">
-        <v>0</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>23</v>
+      <c r="F41" s="2">
+        <v>792</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3139,11 +3139,11 @@
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="6">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>23</v>
+      <c r="F44" s="2">
+        <v>461</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3208,11 +3208,11 @@
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="2">
-        <v>316</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="4">
+        <v>28</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3231,11 +3231,11 @@
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="6">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>23</v>
+      <c r="F48" s="2">
+        <v>372</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3323,11 +3323,11 @@
       <c r="E52">
         <v>48</v>
       </c>
-      <c r="F52" s="6">
-        <v>0</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>23</v>
+      <c r="F52" s="2">
+        <v>672</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1663</v>
+        <v>1763</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>976</v>
+        <v>1552</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>13822</v>
+        <v>14849</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3899,7 +3899,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="2">
-        <v>3450</v>
+        <v>4950</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5705</v>
+        <v>8805</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7215</v>
+        <v>8048</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="6">
-        <v>0</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>23</v>
+      <c r="F82" s="4">
+        <v>293</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>23</v>
+      <c r="F88" s="2">
+        <v>509</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="4">
-        <v>154</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>15</v>
+      <c r="F91" s="2">
+        <v>854</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="6">
-        <v>0</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>23</v>
+      <c r="F93" s="4">
+        <v>296</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="6">
-        <v>0</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>23</v>
+      <c r="F94" s="2">
+        <v>791</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>818</v>
+        <v>758</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4359,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="F97" s="2">
-        <v>4888</v>
+        <v>6088</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>1017</v>
+        <v>3456</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>1761</v>
+        <v>2221</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>3860</v>
+        <v>3800</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="6">
-        <v>0</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>23</v>
+      <c r="F106" s="2">
+        <v>3046</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>940</v>
+        <v>2972</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4634,11 +4634,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="6">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>23</v>
+      <c r="F109" s="4">
+        <v>5</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>2808</v>
+        <v>2748</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>4817</v>
+        <v>6270</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>5151</v>
+        <v>6421</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>8096</v>
+        <v>8036</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="6">
-        <v>0</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>23</v>
+      <c r="F126" s="2">
+        <v>2995</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="2">
-        <v>5695</v>
+        <v>6405</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -5095,7 +5095,7 @@
         <v>120</v>
       </c>
       <c r="F129" s="2">
-        <v>888</v>
+        <v>3432</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="4">
-        <v>172</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>15</v>
+      <c r="F130" s="2">
+        <v>3272</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5163,11 +5163,11 @@
       <c r="E132">
         <v>120</v>
       </c>
-      <c r="F132" s="6">
-        <v>0</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>23</v>
+      <c r="F132" s="4">
+        <v>1</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="4">
-        <v>124</v>
+        <v>523</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>15</v>
@@ -5417,7 +5417,7 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>15</v>
@@ -5509,7 +5509,7 @@
         <v>120</v>
       </c>
       <c r="F147" s="2">
-        <v>656</v>
+        <v>1662</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>10</v>
@@ -5555,7 +5555,7 @@
         <v>120</v>
       </c>
       <c r="F149" s="2">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5578,7 +5578,7 @@
         <v>120</v>
       </c>
       <c r="F150" s="2">
-        <v>1254</v>
+        <v>2019</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5601,7 +5601,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="2">
-        <v>1442</v>
+        <v>1942</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>2523</v>
+        <v>3027</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5693,7 +5693,7 @@
         <v>120</v>
       </c>
       <c r="F155" s="4">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>15</v>
@@ -5715,11 +5715,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="6">
-        <v>0</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>23</v>
+      <c r="F156" s="4">
+        <v>12</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="6">
-        <v>0</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>23</v>
+      <c r="F158" s="4">
+        <v>188</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5807,11 +5807,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="6">
-        <v>0</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>23</v>
+      <c r="F160" s="4">
+        <v>2</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="6">
-        <v>0</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>23</v>
+      <c r="F161" s="4">
+        <v>279</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,7 +5992,7 @@
         <v>120</v>
       </c>
       <c r="F168" s="2">
-        <v>3901</v>
+        <v>4403</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>1186</v>
+        <v>1686</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -6383,7 +6383,7 @@
         <v>12</v>
       </c>
       <c r="F185" s="2">
-        <v>2379</v>
+        <v>2679</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="6">
-        <v>0</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>23</v>
+      <c r="F186" s="4">
+        <v>4</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="6">
-        <v>0</v>
-      </c>
-      <c r="G187" s="7" t="s">
-        <v>23</v>
+      <c r="F187" s="2">
+        <v>270</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6452,7 +6452,7 @@
         <v>12</v>
       </c>
       <c r="F188" s="2">
-        <v>481</v>
+        <v>981</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>10</v>
@@ -6521,7 +6521,7 @@
         <v>18</v>
       </c>
       <c r="F191" s="2">
-        <v>1263</v>
+        <v>1863</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6544,7 +6544,7 @@
         <v>12</v>
       </c>
       <c r="F192" s="2">
-        <v>1697</v>
+        <v>2297</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>2575</v>
+        <v>3375</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="4">
-        <v>178</v>
-      </c>
-      <c r="G196" s="5" t="s">
-        <v>15</v>
+      <c r="F196" s="2">
+        <v>978</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="6">
-        <v>0</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>23</v>
+      <c r="F198" s="4">
+        <v>77</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5598</v>
+        <v>4598</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2335,7 +2335,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="2">
-        <v>1311</v>
+        <v>311</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>1964</v>
+        <v>964</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>1932</v>
+        <v>932</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7902</v>
+        <v>7362</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2748,11 +2748,11 @@
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="F27" s="4">
-        <v>56</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>15</v>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3070,11 +3070,11 @@
       <c r="E41">
         <v>48</v>
       </c>
-      <c r="F41" s="2">
-        <v>792</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3139,11 +3139,11 @@
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="2">
-        <v>461</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="6">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3231,11 +3231,11 @@
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="2">
-        <v>372</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3323,11 +3323,11 @@
       <c r="E52">
         <v>48</v>
       </c>
-      <c r="F52" s="2">
-        <v>672</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="F52" s="6">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1763</v>
+        <v>1663</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1552</v>
+        <v>976</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>14849</v>
+        <v>13821</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7619</v>
+        <v>7618</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3899,7 +3899,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="2">
-        <v>4950</v>
+        <v>3450</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>8805</v>
+        <v>5705</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>8048</v>
+        <v>7215</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="4">
-        <v>293</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>15</v>
+      <c r="F82" s="6">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="2">
-        <v>509</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="F88" s="6">
+        <v>0</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="2">
-        <v>854</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="F91" s="4">
+        <v>154</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="4">
-        <v>296</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>15</v>
+      <c r="F93" s="6">
+        <v>0</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="2">
-        <v>791</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>10</v>
+      <c r="F94" s="6">
+        <v>0</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4359,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="F97" s="2">
-        <v>6088</v>
+        <v>4888</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>3456</v>
+        <v>1017</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>2221</v>
+        <v>1761</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="2">
-        <v>3046</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="6">
+        <v>0</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>2972</v>
+        <v>880</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>459</v>
+        <v>4101</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>6270</v>
+        <v>4817</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>6421</v>
+        <v>5151</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>8036</v>
+        <v>8033</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4842,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="F118" s="2">
-        <v>361</v>
+        <v>538</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="2">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="2">
-        <v>2995</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="6">
+        <v>0</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="2">
-        <v>6405</v>
+        <v>5695</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -5095,7 +5095,7 @@
         <v>120</v>
       </c>
       <c r="F129" s="2">
-        <v>3432</v>
+        <v>888</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="2">
-        <v>3272</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="F130" s="4">
+        <v>172</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="4">
-        <v>523</v>
+        <v>124</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>15</v>
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="6">
-        <v>0</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>23</v>
+      <c r="F146" s="4">
+        <v>1</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5509,7 +5509,7 @@
         <v>120</v>
       </c>
       <c r="F147" s="2">
-        <v>1662</v>
+        <v>662</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>10</v>
@@ -5578,7 +5578,7 @@
         <v>120</v>
       </c>
       <c r="F150" s="2">
-        <v>2019</v>
+        <v>1254</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5601,7 +5601,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="2">
-        <v>1942</v>
+        <v>1442</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>3027</v>
+        <v>2527</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="4">
-        <v>188</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>15</v>
+      <c r="F158" s="6">
+        <v>0</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="4">
-        <v>279</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>15</v>
+      <c r="F161" s="6">
+        <v>0</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,7 +5992,7 @@
         <v>120</v>
       </c>
       <c r="F168" s="2">
-        <v>4403</v>
+        <v>3903</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>1686</v>
+        <v>1186</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>
@@ -6383,7 +6383,7 @@
         <v>12</v>
       </c>
       <c r="F185" s="2">
-        <v>2679</v>
+        <v>2379</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="2">
-        <v>270</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="6">
+        <v>0</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6452,7 +6452,7 @@
         <v>12</v>
       </c>
       <c r="F188" s="2">
-        <v>981</v>
+        <v>481</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>10</v>
@@ -6521,7 +6521,7 @@
         <v>18</v>
       </c>
       <c r="F191" s="2">
-        <v>1863</v>
+        <v>1263</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6544,7 +6544,7 @@
         <v>12</v>
       </c>
       <c r="F192" s="2">
-        <v>2297</v>
+        <v>1697</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>3375</v>
+        <v>2575</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="2">
-        <v>978</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>10</v>
+      <c r="F196" s="4">
+        <v>178</v>
+      </c>
+      <c r="G196" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="4">
-        <v>77</v>
-      </c>
-      <c r="G198" s="5" t="s">
-        <v>15</v>
+      <c r="F198" s="6">
+        <v>0</v>
+      </c>
+      <c r="G198" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2795,7 +2795,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>3039</v>
+        <v>3014</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3317</v>
+        <v>3292</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1662</v>
+        <v>1626</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1663</v>
+        <v>1591</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>964</v>
+        <v>928</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>507</v>
+        <v>435</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3595</v>
+        <v>3585</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7618</v>
+        <v>7608</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12838</v>
+        <v>12828</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5705</v>
+        <v>5695</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7161</v>
+        <v>7151</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>7448</v>
+        <v>7438</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4888,7 +4888,7 @@
         <v>36</v>
       </c>
       <c r="F120" s="4">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>15</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>7362</v>
+        <v>6930</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>4071</v>
+        <v>7720</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="6">
-        <v>0</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>23</v>
+      <c r="F146" s="2">
+        <v>420</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6222,7 +6222,7 @@
         <v>12</v>
       </c>
       <c r="F178" s="2">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="2">
-        <v>420</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="4">
+        <v>169</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6221,11 +6221,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="2">
-        <v>116</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>10</v>
+      <c r="F178" s="4">
+        <v>44</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2795,7 +2795,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>3014</v>
+        <v>3039</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3292</v>
+        <v>3317</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1626</v>
+        <v>1662</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1591</v>
+        <v>1663</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>928</v>
+        <v>964</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>435</v>
+        <v>507</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3585</v>
+        <v>3595</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7608</v>
+        <v>7618</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12828</v>
+        <v>12838</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5695</v>
+        <v>5705</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7151</v>
+        <v>7161</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>7438</v>
+        <v>7448</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4842,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="F118" s="2">
-        <v>538</v>
+        <v>717</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4888,7 +4888,7 @@
         <v>36</v>
       </c>
       <c r="F120" s="4">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>15</v>
@@ -5486,7 +5486,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="4">
-        <v>169</v>
+        <v>291</v>
       </c>
       <c r="G146" s="5" t="s">
         <v>15</v>
@@ -6222,7 +6222,7 @@
         <v>12</v>
       </c>
       <c r="F178" s="4">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>15</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2496,7 +2496,7 @@
         <v>36</v>
       </c>
       <c r="F16" s="2">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>880</v>
+        <v>808</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2174,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2174,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>1905</v>
+        <v>1881</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3287</v>
+        <v>3263</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>4598</v>
+        <v>4586</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3564</v>
+        <v>3528</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3049</v>
+        <v>3013</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>6930</v>
+        <v>6858</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3317</v>
+        <v>3293</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2811</v>
+        <v>2787</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>15</v>
@@ -3254,11 +3254,11 @@
       <c r="E49">
         <v>48</v>
       </c>
-      <c r="F49" s="4">
-        <v>5</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>15</v>
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>13791</v>
+        <v>13731</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3595</v>
+        <v>3475</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12838</v>
+        <v>12718</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7161</v>
+        <v>7041</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>997</v>
+        <v>865</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>1761</v>
+        <v>1749</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>3800</v>
+        <v>3680</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>808</v>
+        <v>688</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>2718</v>
+        <v>2586</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>4787</v>
+        <v>4667</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>5131</v>
+        <v>5119</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>8003</v>
+        <v>7871</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4796,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="2">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>108150</v>
+        <v>106150</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>103365</v>
+        <v>101365</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>6858</v>
+        <v>6853</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2910,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="4">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>15</v>
@@ -2933,7 +2933,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -2979,7 +2979,7 @@
         <v>48</v>
       </c>
       <c r="F37" s="2">
-        <v>7407</v>
+        <v>7403</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -3208,11 +3208,11 @@
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="4">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>15</v>
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11217</v>
+        <v>11216</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>13731</v>
+        <v>13730</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3475</v>
+        <v>3472</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3899,7 +3899,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="2">
-        <v>3450</v>
+        <v>3447</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12718</v>
+        <v>12715</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="4">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>15</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="4">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>15</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4313,7 +4313,7 @@
         <v>60</v>
       </c>
       <c r="F95" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>15</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>3659</v>
+        <v>3655</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>4667</v>
+        <v>4666</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>7871</v>
+        <v>7867</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4888,7 +4888,7 @@
         <v>36</v>
       </c>
       <c r="F120" s="4">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>15</v>
@@ -4980,7 +4980,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="2">
-        <v>2020</v>
+        <v>1984</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -5187,7 +5187,7 @@
         <v>120</v>
       </c>
       <c r="F133" s="2">
-        <v>6475</v>
+        <v>6472</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>10</v>
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="4">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>15</v>
@@ -5417,7 +5417,7 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>15</v>
@@ -6153,7 +6153,7 @@
         <v>12</v>
       </c>
       <c r="F175" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G175" s="5" t="s">
         <v>15</v>
@@ -6222,7 +6222,7 @@
         <v>12</v>
       </c>
       <c r="F178" s="4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>15</v>
@@ -6383,7 +6383,7 @@
         <v>12</v>
       </c>
       <c r="F185" s="2">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>2575</v>
+        <v>2551</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>120</v>
       </c>
       <c r="F196" s="4">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>15</v>
@@ -6705,7 +6705,7 @@
         <v>120</v>
       </c>
       <c r="F199" s="2">
-        <v>8028</v>
+        <v>7992</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2795,7 +2795,7 @@
         <v>50</v>
       </c>
       <c r="F29" s="2">
-        <v>3039</v>
+        <v>3014</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3293</v>
+        <v>3268</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1662</v>
+        <v>1626</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1663</v>
+        <v>1591</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>964</v>
+        <v>916</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>507</v>
+        <v>435</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>3472</v>
+        <v>3462</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>7618</v>
+        <v>7608</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12715</v>
+        <v>12705</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5705</v>
+        <v>5695</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>7041</v>
+        <v>6551</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>60</v>
       </c>
       <c r="F81" s="2">
-        <v>7448</v>
+        <v>7438</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="4">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>15</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>688</v>
+        <v>592</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="F117" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>10</v>
@@ -4888,7 +4888,7 @@
         <v>36</v>
       </c>
       <c r="F120" s="4">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>15</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2335,7 +2335,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -2427,7 +2427,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3692,7 +3692,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2334,11 +2334,11 @@
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="2">
-        <v>310</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="4">
+        <v>22</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2933,7 +2933,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -3139,11 +3139,11 @@
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="6">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>23</v>
+      <c r="F44" s="4">
+        <v>5</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1626</v>
+        <v>1434</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3623,7 +3623,7 @@
         <v>48</v>
       </c>
       <c r="F65" s="2">
-        <v>707</v>
+        <v>683</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11216</v>
+        <v>11156</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>13730</v>
+        <v>13670</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3899,7 +3899,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="2">
-        <v>3447</v>
+        <v>3099</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12705</v>
+        <v>12645</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="6">
-        <v>0</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>23</v>
+      <c r="F93" s="4">
+        <v>8</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4381,11 +4381,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="2">
-        <v>863</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="F98" s="4">
+        <v>167</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>1747</v>
+        <v>1267</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>3655</v>
+        <v>3595</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="4">
-        <v>291</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>15</v>
+      <c r="F146" s="6">
+        <v>0</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,11 +5508,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="2">
-        <v>662</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="F147" s="4">
+        <v>350</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5578,7 +5578,7 @@
         <v>120</v>
       </c>
       <c r="F150" s="2">
-        <v>1254</v>
+        <v>870</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="6">
-        <v>0</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>23</v>
+      <c r="F158" s="4">
+        <v>8</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="6">
-        <v>0</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>23</v>
+      <c r="F161" s="4">
+        <v>3</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2979,7 +2979,7 @@
         <v>48</v>
       </c>
       <c r="F37" s="2">
-        <v>7403</v>
+        <v>7355</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>13670</v>
+        <v>13646</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>6551</v>
+        <v>6515</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>813</v>
+        <v>777</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4359,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="F97" s="2">
-        <v>4888</v>
+        <v>4864</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>3680</v>
+        <v>3656</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2093</v>
+        <v>2045</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>7867</v>
+        <v>7843</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5118,7 +5118,7 @@
         <v>120</v>
       </c>
       <c r="F130" s="4">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>15</v>
@@ -5532,7 +5532,7 @@
         <v>120</v>
       </c>
       <c r="F148" s="2">
-        <v>3865</v>
+        <v>3829</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -5555,7 +5555,7 @@
         <v>120</v>
       </c>
       <c r="F149" s="2">
-        <v>4362</v>
+        <v>2338</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1434</v>
+        <v>1254</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>916</v>
+        <v>844</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>2583</v>
+        <v>2283</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -4980,7 +4980,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="2">
-        <v>1984</v>
+        <v>1972</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3528</v>
+        <v>3529</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -3208,11 +3208,11 @@
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="6">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>23</v>
+      <c r="F47" s="4">
+        <v>144</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -5210,7 +5210,7 @@
         <v>120</v>
       </c>
       <c r="F134" s="4">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>15</v>
@@ -5394,7 +5394,7 @@
         <v>120</v>
       </c>
       <c r="F142" s="2">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>3262</v>
+        <v>3226</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>4586</v>
+        <v>4574</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3529</v>
+        <v>3493</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>6853</v>
+        <v>6817</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2787</v>
+        <v>2751</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -58,49 +58,49 @@
     <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
   </si>
   <si>
+    <t>✗ AGOTADO</t>
+  </si>
+  <si>
+    <t>016727</t>
+  </si>
+  <si>
+    <t>7754807167277</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
+  </si>
+  <si>
+    <t>016756</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
+  </si>
+  <si>
+    <t>016755</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
+  </si>
+  <si>
+    <t>016757</t>
+  </si>
+  <si>
+    <t>7754807167574</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
+  </si>
+  <si>
+    <t>016760</t>
+  </si>
+  <si>
+    <t>7754807167604</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
-  </si>
-  <si>
-    <t>016727</t>
-  </si>
-  <si>
-    <t>7754807167277</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
-  </si>
-  <si>
-    <t>016756</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
-  </si>
-  <si>
-    <t>016755</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>016757</t>
-  </si>
-  <si>
-    <t>7754807167574</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
-  </si>
-  <si>
-    <t>016760</t>
-  </si>
-  <si>
-    <t>7754807167604</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
   </si>
   <si>
     <t>016758</t>
@@ -1712,12 +1712,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1740,12 +1740,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -2220,7 +2220,7 @@
         <v>24</v>
       </c>
       <c r="F4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>15</v>
@@ -2288,11 +2288,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
+      <c r="G7" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2300,13 +2300,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
       </c>
       <c r="E8">
         <v>24</v>
@@ -2323,22 +2323,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
       </c>
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="4">
-        <v>22</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>15</v>
+      <c r="F9" s="6">
+        <v>20</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2449,11 +2449,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="4">
-        <v>171</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>15</v>
+      <c r="F14" s="6">
+        <v>169</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2472,11 +2472,11 @@
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
+      <c r="G15" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2518,11 +2518,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>23</v>
+      <c r="G17" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2541,11 +2541,11 @@
       <c r="E18">
         <v>36</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>23</v>
+      <c r="G18" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2565,7 +2565,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>3493</v>
+        <v>3488</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>6817</v>
+        <v>6810</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>1136</v>
+        <v>1119</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2656,11 +2656,11 @@
       <c r="E23">
         <v>48</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="4">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
+      <c r="G23" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2679,11 +2679,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2702,11 +2702,11 @@
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2725,11 +2725,11 @@
       <c r="E26">
         <v>48</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="4">
         <v>0</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>23</v>
+      <c r="G26" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2748,11 +2748,11 @@
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>23</v>
+      <c r="G27" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2771,11 +2771,11 @@
       <c r="E28">
         <v>36</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>23</v>
+      <c r="G28" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2817,11 +2817,11 @@
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>23</v>
+      <c r="G30" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2840,11 +2840,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>23</v>
+      <c r="G31" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2909,11 +2909,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="4">
-        <v>149</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>15</v>
+      <c r="F34" s="6">
+        <v>141</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2933,7 +2933,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -2979,7 +2979,7 @@
         <v>48</v>
       </c>
       <c r="F37" s="2">
-        <v>7355</v>
+        <v>7349</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -3001,11 +3001,11 @@
       <c r="E38">
         <v>48</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="6">
         <v>2</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>15</v>
+      <c r="G38" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3024,11 +3024,11 @@
       <c r="E39">
         <v>48</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="4">
         <v>0</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>23</v>
+      <c r="G39" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3047,11 +3047,11 @@
       <c r="E40">
         <v>48</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="4">
         <v>0</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>23</v>
+      <c r="G40" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3070,11 +3070,11 @@
       <c r="E41">
         <v>48</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="4">
         <v>0</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>23</v>
+      <c r="G41" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3093,11 +3093,11 @@
       <c r="E42">
         <v>48</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="4">
         <v>0</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>23</v>
+      <c r="G42" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3116,11 +3116,11 @@
       <c r="E43">
         <v>48</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="7" t="s">
-        <v>23</v>
+      <c r="G43" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3139,11 +3139,11 @@
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="6">
         <v>5</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>15</v>
+      <c r="G44" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3162,11 +3162,11 @@
       <c r="E45">
         <v>48</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45" s="4">
         <v>0</v>
       </c>
-      <c r="G45" s="7" t="s">
-        <v>23</v>
+      <c r="G45" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3185,11 +3185,11 @@
       <c r="E46">
         <v>48</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46" s="4">
         <v>0</v>
       </c>
-      <c r="G46" s="7" t="s">
-        <v>23</v>
+      <c r="G46" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3208,11 +3208,11 @@
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="4">
-        <v>144</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>15</v>
+      <c r="F47" s="6">
+        <v>94</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3231,11 +3231,11 @@
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="4">
         <v>0</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>23</v>
+      <c r="G48" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3254,11 +3254,11 @@
       <c r="E49">
         <v>48</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="4">
         <v>0</v>
       </c>
-      <c r="G49" s="7" t="s">
-        <v>23</v>
+      <c r="G49" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3277,11 +3277,11 @@
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="4">
         <v>0</v>
       </c>
-      <c r="G50" s="7" t="s">
-        <v>23</v>
+      <c r="G50" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3300,11 +3300,11 @@
       <c r="E51">
         <v>48</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="4">
         <v>0</v>
       </c>
-      <c r="G51" s="7" t="s">
-        <v>23</v>
+      <c r="G51" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3323,11 +3323,11 @@
       <c r="E52">
         <v>48</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="4">
         <v>0</v>
       </c>
-      <c r="G52" s="7" t="s">
-        <v>23</v>
+      <c r="G52" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3346,11 +3346,11 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="4">
         <v>0</v>
       </c>
-      <c r="G53" s="7" t="s">
-        <v>23</v>
+      <c r="G53" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3369,11 +3369,11 @@
       <c r="E54">
         <v>48</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="6">
         <v>4</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>15</v>
+      <c r="G54" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3415,11 +3415,11 @@
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="4">
         <v>0</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>23</v>
+      <c r="G56" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3461,11 +3461,11 @@
       <c r="E58">
         <v>36</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="4">
         <v>0</v>
       </c>
-      <c r="G58" s="7" t="s">
-        <v>23</v>
+      <c r="G58" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3484,11 +3484,11 @@
       <c r="E59">
         <v>36</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="4">
         <v>0</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>23</v>
+      <c r="G59" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3530,11 +3530,11 @@
       <c r="E61">
         <v>36</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="4">
         <v>0</v>
       </c>
-      <c r="G61" s="7" t="s">
-        <v>23</v>
+      <c r="G61" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3577,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3599,11 +3599,11 @@
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="4">
         <v>0</v>
       </c>
-      <c r="G64" s="7" t="s">
-        <v>23</v>
+      <c r="G64" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="2">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -3738,7 +3738,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="2">
-        <v>4057</v>
+        <v>4055</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -3761,7 +3761,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="2">
-        <v>4949</v>
+        <v>4947</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>10</v>
@@ -3783,11 +3783,11 @@
       <c r="E72">
         <v>60</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="4">
         <v>0</v>
       </c>
-      <c r="G72" s="7" t="s">
-        <v>23</v>
+      <c r="G72" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>11156</v>
+        <v>11153</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>13646</v>
+        <v>13643</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12645</v>
+        <v>12639</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -4014,10 +4014,10 @@
         <v>60</v>
       </c>
       <c r="F82" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4036,11 +4036,11 @@
       <c r="E83">
         <v>60</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="6">
         <v>9</v>
       </c>
-      <c r="G83" s="5" t="s">
-        <v>15</v>
+      <c r="G83" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4059,11 +4059,11 @@
       <c r="E84">
         <v>60</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="4">
         <v>0</v>
       </c>
-      <c r="G84" s="7" t="s">
-        <v>23</v>
+      <c r="G84" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4082,11 +4082,11 @@
       <c r="E85">
         <v>60</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="6">
         <v>111</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>15</v>
+      <c r="G85" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="4">
         <v>0</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>23</v>
+      <c r="G88" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,11 +4174,11 @@
       <c r="E89">
         <v>60</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="4">
         <v>0</v>
       </c>
-      <c r="G89" s="7" t="s">
-        <v>23</v>
+      <c r="G89" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,11 +4197,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="4">
-        <v>217</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>15</v>
+      <c r="F90" s="6">
+        <v>206</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="4">
-        <v>102</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>15</v>
+      <c r="F91" s="6">
+        <v>96</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="6">
         <v>8</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>15</v>
+      <c r="G93" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="4">
         <v>0</v>
       </c>
-      <c r="G94" s="7" t="s">
-        <v>23</v>
+      <c r="G94" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4312,11 +4312,11 @@
       <c r="E95">
         <v>60</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="6">
         <v>2</v>
       </c>
-      <c r="G95" s="5" t="s">
-        <v>15</v>
+      <c r="G95" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4381,11 +4381,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="4">
-        <v>167</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>15</v>
+      <c r="F98" s="6">
+        <v>162</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4427,11 +4427,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="4">
         <v>0</v>
       </c>
-      <c r="G100" s="7" t="s">
-        <v>23</v>
+      <c r="G100" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4542,11 +4542,11 @@
       <c r="E105">
         <v>60</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="4">
         <v>0</v>
       </c>
-      <c r="G105" s="7" t="s">
-        <v>23</v>
+      <c r="G105" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="4">
         <v>0</v>
       </c>
-      <c r="G106" s="7" t="s">
-        <v>23</v>
+      <c r="G106" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>3595</v>
+        <v>3592</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4634,11 +4634,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="6">
         <v>5</v>
       </c>
-      <c r="G109" s="5" t="s">
-        <v>15</v>
+      <c r="G109" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>4666</v>
+        <v>4665</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>7843</v>
+        <v>7831</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4864,11 +4864,11 @@
       <c r="E119">
         <v>12</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="6">
         <v>8</v>
       </c>
-      <c r="G119" s="5" t="s">
-        <v>15</v>
+      <c r="G119" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,11 +4887,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="6">
         <v>4</v>
       </c>
-      <c r="G120" s="5" t="s">
-        <v>15</v>
+      <c r="G120" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,11 +4910,11 @@
       <c r="E121">
         <v>36</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="4">
         <v>0</v>
       </c>
-      <c r="G121" s="7" t="s">
-        <v>23</v>
+      <c r="G121" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4956,11 +4956,11 @@
       <c r="E123">
         <v>36</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="4">
         <v>0</v>
       </c>
-      <c r="G123" s="7" t="s">
-        <v>23</v>
+      <c r="G123" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5003,7 +5003,7 @@
         <v>36</v>
       </c>
       <c r="F125" s="2">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>10</v>
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="4">
         <v>0</v>
       </c>
-      <c r="G126" s="7" t="s">
-        <v>23</v>
+      <c r="G126" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5048,11 +5048,11 @@
       <c r="E127">
         <v>120</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F127" s="4">
         <v>0</v>
       </c>
-      <c r="G127" s="7" t="s">
-        <v>23</v>
+      <c r="G127" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5095,7 +5095,7 @@
         <v>120</v>
       </c>
       <c r="F129" s="2">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="6">
         <v>119</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>15</v>
+      <c r="G130" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5140,11 +5140,11 @@
       <c r="E131">
         <v>120</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="6">
         <v>9</v>
       </c>
-      <c r="G131" s="5" t="s">
-        <v>15</v>
+      <c r="G131" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5163,11 +5163,11 @@
       <c r="E132">
         <v>120</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="6">
         <v>1</v>
       </c>
-      <c r="G132" s="5" t="s">
-        <v>15</v>
+      <c r="G132" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5187,7 +5187,7 @@
         <v>120</v>
       </c>
       <c r="F133" s="2">
-        <v>6472</v>
+        <v>6471</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>10</v>
@@ -5209,11 +5209,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="6">
         <v>122</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>15</v>
+      <c r="G134" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5232,11 +5232,11 @@
       <c r="E135">
         <v>120</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="6">
         <v>2</v>
       </c>
-      <c r="G135" s="5" t="s">
-        <v>15</v>
+      <c r="G135" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5301,11 +5301,11 @@
       <c r="E138">
         <v>120</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F138" s="4">
         <v>0</v>
       </c>
-      <c r="G138" s="7" t="s">
-        <v>23</v>
+      <c r="G138" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5416,11 +5416,11 @@
       <c r="E143">
         <v>120</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="6">
         <v>481</v>
       </c>
-      <c r="G143" s="5" t="s">
-        <v>15</v>
+      <c r="G143" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,11 +5439,11 @@
       <c r="E144">
         <v>120</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="4">
         <v>0</v>
       </c>
-      <c r="G144" s="7" t="s">
-        <v>23</v>
+      <c r="G144" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5462,11 +5462,11 @@
       <c r="E145">
         <v>120</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="6">
         <v>1</v>
       </c>
-      <c r="G145" s="5" t="s">
-        <v>15</v>
+      <c r="G145" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="4">
         <v>0</v>
       </c>
-      <c r="G146" s="7" t="s">
-        <v>23</v>
+      <c r="G146" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,11 +5508,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="6">
         <v>350</v>
       </c>
-      <c r="G147" s="5" t="s">
-        <v>15</v>
+      <c r="G147" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5623,11 +5623,11 @@
       <c r="E152">
         <v>120</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F152" s="6">
         <v>319</v>
       </c>
-      <c r="G152" s="5" t="s">
-        <v>15</v>
+      <c r="G152" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,11 +5646,11 @@
       <c r="E153">
         <v>120</v>
       </c>
-      <c r="F153" s="6">
+      <c r="F153" s="4">
         <v>0</v>
       </c>
-      <c r="G153" s="7" t="s">
-        <v>23</v>
+      <c r="G153" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5692,11 +5692,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="6">
         <v>128</v>
       </c>
-      <c r="G155" s="5" t="s">
-        <v>15</v>
+      <c r="G155" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5715,11 +5715,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="6">
         <v>12</v>
       </c>
-      <c r="G156" s="5" t="s">
-        <v>15</v>
+      <c r="G156" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="4">
+      <c r="F158" s="6">
         <v>8</v>
       </c>
-      <c r="G158" s="5" t="s">
-        <v>15</v>
+      <c r="G158" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5807,11 +5807,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="4">
+      <c r="F160" s="6">
         <v>2</v>
       </c>
-      <c r="G160" s="5" t="s">
-        <v>15</v>
+      <c r="G160" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="4">
+      <c r="F161" s="6">
         <v>3</v>
       </c>
-      <c r="G161" s="5" t="s">
-        <v>15</v>
+      <c r="G161" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5899,11 +5899,11 @@
       <c r="E164">
         <v>120</v>
       </c>
-      <c r="F164" s="6">
+      <c r="F164" s="4">
         <v>0</v>
       </c>
-      <c r="G164" s="7" t="s">
-        <v>23</v>
+      <c r="G164" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5968,11 +5968,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="6">
         <v>20</v>
       </c>
-      <c r="G167" s="5" t="s">
-        <v>15</v>
+      <c r="G167" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6037,11 +6037,11 @@
       <c r="E170">
         <v>120</v>
       </c>
-      <c r="F170" s="4">
+      <c r="F170" s="6">
         <v>1</v>
       </c>
-      <c r="G170" s="5" t="s">
-        <v>15</v>
+      <c r="G170" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -6152,11 +6152,11 @@
       <c r="E175">
         <v>12</v>
       </c>
-      <c r="F175" s="4">
+      <c r="F175" s="6">
         <v>5</v>
       </c>
-      <c r="G175" s="5" t="s">
-        <v>15</v>
+      <c r="G175" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6175,11 +6175,11 @@
       <c r="E176">
         <v>12</v>
       </c>
-      <c r="F176" s="6">
+      <c r="F176" s="4">
         <v>0</v>
       </c>
-      <c r="G176" s="7" t="s">
-        <v>23</v>
+      <c r="G176" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6198,11 +6198,11 @@
       <c r="E177">
         <v>12</v>
       </c>
-      <c r="F177" s="6">
+      <c r="F177" s="4">
         <v>0</v>
       </c>
-      <c r="G177" s="7" t="s">
-        <v>23</v>
+      <c r="G177" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6221,11 +6221,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="4">
+      <c r="F178" s="6">
         <v>38</v>
       </c>
-      <c r="G178" s="5" t="s">
-        <v>15</v>
+      <c r="G178" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6244,11 +6244,11 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="4">
+      <c r="F179" s="6">
         <v>1</v>
       </c>
-      <c r="G179" s="5" t="s">
-        <v>15</v>
+      <c r="G179" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6267,11 +6267,11 @@
       <c r="E180">
         <v>12</v>
       </c>
-      <c r="F180" s="6">
+      <c r="F180" s="4">
         <v>0</v>
       </c>
-      <c r="G180" s="7" t="s">
-        <v>23</v>
+      <c r="G180" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6290,11 +6290,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="6">
+      <c r="F181" s="4">
         <v>0</v>
       </c>
-      <c r="G181" s="7" t="s">
-        <v>23</v>
+      <c r="G181" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6336,11 +6336,11 @@
       <c r="E183">
         <v>12</v>
       </c>
-      <c r="F183" s="4">
+      <c r="F183" s="6">
         <v>51</v>
       </c>
-      <c r="G183" s="5" t="s">
-        <v>15</v>
+      <c r="G183" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -6359,11 +6359,11 @@
       <c r="E184">
         <v>12</v>
       </c>
-      <c r="F184" s="6">
+      <c r="F184" s="4">
         <v>0</v>
       </c>
-      <c r="G184" s="7" t="s">
-        <v>23</v>
+      <c r="G184" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="4">
+      <c r="F186" s="6">
         <v>4</v>
       </c>
-      <c r="G186" s="5" t="s">
-        <v>15</v>
+      <c r="G186" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="6">
+      <c r="F187" s="4">
         <v>0</v>
       </c>
-      <c r="G187" s="7" t="s">
-        <v>23</v>
+      <c r="G187" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6474,11 +6474,11 @@
       <c r="E189">
         <v>18</v>
       </c>
-      <c r="F189" s="4">
+      <c r="F189" s="6">
         <v>1</v>
       </c>
-      <c r="G189" s="5" t="s">
-        <v>15</v>
+      <c r="G189" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="4">
+      <c r="F196" s="6">
         <v>154</v>
       </c>
-      <c r="G196" s="5" t="s">
-        <v>15</v>
+      <c r="G196" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="6">
+      <c r="F198" s="4">
         <v>0</v>
       </c>
-      <c r="G198" s="7" t="s">
-        <v>23</v>
+      <c r="G198" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_PELOTAS.xlsx
+++ b/reports/StockPulse_PELOTAS.xlsx
@@ -2588,7 +2588,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>3012</v>
+        <v>2988</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -3369,11 +3369,11 @@
       <c r="E54">
         <v>48</v>
       </c>
-      <c r="F54" s="6">
-        <v>4</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>29</v>
+      <c r="F54" s="4">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>1248</v>
+        <v>1236</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>1586</v>
+        <v>1574</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="2">
-        <v>2018</v>
+        <v>2006</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -3715,7 +3715,7 @@
         <v>60</v>
       </c>
       <c r="F69" s="2">
-        <v>1080</v>
+        <v>1068</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3738,7 +3738,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="2">
-        <v>4055</v>
+        <v>4043</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -3761,7 +3761,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="2">
-        <v>4947</v>
+        <v>4935</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>10</v>
@@ -3922,7 +3922,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="2">
-        <v>12639</v>
+        <v>12627</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="2">
-        <v>6515</v>
+        <v>6491</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="6">
-        <v>2</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>29</v>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4129,7 +4129,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="2">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="6">
-        <v>8</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>29</v>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>758</v>
+        <v>734</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4451,7 +4451,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="2">
-        <v>3656</v>
+        <v>3644</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="2">
-        <v>2045</v>
+        <v>2033</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="2">
-        <v>7720</v>
+        <v>7696</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="2">
-        <v>2281</v>
+        <v>2257</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>4665</v>
+        <v>4653</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>5119</v>
+        <v>5083</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>7831</v>
+        <v>7807</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
